--- a/인천 2026 기록.xlsx
+++ b/인천 2026 기록.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://familyinter-my.sharepoint.com/personal/hwlee_familyinter_onmicrosoft_com/Documents/바탕 화면/프로젝트300/대시보드/인천 대시보드/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1065" documentId="11_8673CE99959C043A6D95B170604D1DCFD5B90D48" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{965D7F8E-F92F-4A1C-AC21-9527C0239A3B}"/>
+  <xr:revisionPtr revIDLastSave="2150" documentId="11_8673CE99959C043A6D95B170604D1DCFD5B90D48" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23400A68-04B9-4BBE-A10F-2B4BC21D2A4D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8830" yWindow="1450" windowWidth="9600" windowHeight="5450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 토탈" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6018" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6036" uniqueCount="397">
   <si>
     <t>리그</t>
   </si>
@@ -1291,11 +1291,17 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>K리그1 2026 리그순위   (2026-09-09 - 28R 종료)</t>
+    <t>인천</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>인천</t>
+    <t>Kim Yeon-Soo</t>
+  </si>
+  <si>
+    <t>Leandro</t>
+  </si>
+  <si>
+    <t>K리그1 2026 리그순위   (2026-09-12 - 29R 진행 중)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -4961,6 +4967,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="기록표" displayName="기록표" ref="A42:E57" totalsRowShown="0" headerRowDxfId="84" headerRowBorderDxfId="83" tableBorderDxfId="82" totalsRowBorderDxfId="81">
   <tableColumns count="5">
@@ -5326,7 +5336,7 @@
         <v>1</v>
       </c>
       <c r="BI1" s="478" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="BJ1" s="477"/>
       <c r="BK1" s="477"/>
@@ -5593,11 +5603,11 @@
       </c>
       <c r="Y3" s="332">
         <f t="shared" ref="Y3:Y43" si="0">Z3+AA3</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z3" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X3)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA3" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X3)</f>
@@ -5605,7 +5615,7 @@
       </c>
       <c r="AB3" s="333">
         <f t="shared" ref="AB3:AB43" si="1">COUNTIF($M$3:$P$40,$X3)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC3" s="334">
         <f t="shared" ref="AC3:AC43" si="2">COUNTIF($Q$3:$T$40,$X3)</f>
@@ -5613,15 +5623,15 @@
       </c>
       <c r="AD3" s="335">
         <f t="shared" ref="AD3:AD43" si="3">AB3+AC3</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE3" s="332">
         <f t="shared" ref="AE3:AE43" si="4">AF3+AG3</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF3" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X3)+Z3</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG3" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X3)+AA3</f>
@@ -5629,7 +5639,7 @@
       </c>
       <c r="AH3" s="333">
         <f t="shared" ref="AH3:AH43" si="5">COUNTIF($M$3:$P$41,$X3)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI3" s="334">
         <f t="shared" ref="AI3:AI43" si="6">COUNTIF($Q$3:$T$41,$X3)</f>
@@ -5637,7 +5647,7 @@
       </c>
       <c r="AJ3" s="335">
         <f t="shared" ref="AJ3:AJ43" si="7">AH3+AI3</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM3" s="2" t="s">
         <v>45</v>
@@ -5724,10 +5734,10 @@
         <v>341</v>
       </c>
       <c r="BK3" s="469">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BL3" s="469">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BM3" s="469">
         <v>5</v>
@@ -5736,17 +5746,17 @@
         <v>5</v>
       </c>
       <c r="BO3" s="469">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="BP3" s="469">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BQ3" s="469">
         <f>BO3-BP3</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BR3" s="469">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:77">
@@ -5856,7 +5866,7 @@
       </c>
       <c r="AN4" s="2">
         <f>SUM(AO4:AQ4)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO4" s="243">
         <f t="shared" si="8"/>
@@ -5868,7 +5878,7 @@
       </c>
       <c r="AQ4" s="342">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR4" s="352">
         <f>AO4*3+AP4</f>
@@ -5876,31 +5886,31 @@
       </c>
       <c r="AS4" s="23">
         <f>IFERROR(AO4/AN4,0)</f>
-        <v>0.38461538461538464</v>
+        <v>0.35714285714285715</v>
       </c>
       <c r="AT4" s="2">
         <f>SUMIFS($G$3:$G$40,$A$3:$A$40,"K리그",$F$3:$F$40,$AM4)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU4" s="2">
         <f>SUMIFS($H$3:$H$40,$A$3:$A$40,"K리그",$F$3:$F$40,$AM4)</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AV4" s="2">
         <f>AT4-AU4</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW4" s="434">
         <f>IFERROR(AR4/AN4,0)</f>
-        <v>1.4615384615384615</v>
+        <v>1.3571428571428572</v>
       </c>
       <c r="AX4" s="434">
         <f>IFERROR(AT4/AN4,0)</f>
-        <v>1.3846153846153846</v>
+        <v>1.3571428571428572</v>
       </c>
       <c r="AY4" s="434">
         <f>IFERROR(AU4/AN4,0)</f>
-        <v>1.1538461538461537</v>
+        <v>1.2142857142857142</v>
       </c>
       <c r="BA4" s="464" t="s">
         <v>53</v>
@@ -5936,10 +5946,10 @@
         <v>360</v>
       </c>
       <c r="BK4" s="470">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BL4" s="470">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BM4" s="470">
         <v>5</v>
@@ -5948,17 +5958,17 @@
         <v>10</v>
       </c>
       <c r="BO4" s="470">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BP4" s="470">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BQ4" s="470">
         <f>BO4-BP4</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BR4" s="470">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:77">
@@ -6011,7 +6021,7 @@
       </c>
       <c r="Y5" s="332">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z5" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X5)</f>
@@ -6019,7 +6029,7 @@
       </c>
       <c r="AA5" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X5)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB5" s="333">
         <f t="shared" si="1"/>
@@ -6035,7 +6045,7 @@
       </c>
       <c r="AE5" s="332">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF5" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X5)+Z5</f>
@@ -6043,7 +6053,7 @@
       </c>
       <c r="AG5" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X5)+AA5</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH5" s="333">
         <f t="shared" si="5"/>
@@ -6062,7 +6072,7 @@
       </c>
       <c r="AN5" s="337">
         <f>SUM(AN3:AN4)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO5" s="337">
         <f>SUM(AO3:AO4)</f>
@@ -6074,7 +6084,7 @@
       </c>
       <c r="AQ5" s="337">
         <f>SUM(AQ3:AQ4)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR5" s="337">
         <f>SUM(AR3:AR4)</f>
@@ -6082,31 +6092,31 @@
       </c>
       <c r="AS5" s="349">
         <f>IFERROR(AO5/AN5,0)</f>
-        <v>0.37037037037037035</v>
+        <v>0.35714285714285715</v>
       </c>
       <c r="AT5" s="337">
         <f>SUM(AT3:AT4)</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AU5" s="337">
         <f>SUM(AU3:AU4)</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AV5" s="337">
         <f>SUM(AV3:AV4)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW5" s="435">
         <f>IFERROR(AR5/AN5,0)</f>
-        <v>1.3703703703703705</v>
+        <v>1.3214285714285714</v>
       </c>
       <c r="AX5" s="435">
         <f>IFERROR(AT5/AN5,0)</f>
-        <v>1.2592592592592593</v>
+        <v>1.25</v>
       </c>
       <c r="AY5" s="435">
         <f>IFERROR(AU5/AN5,0)</f>
-        <v>1.1111111111111112</v>
+        <v>1.1428571428571428</v>
       </c>
       <c r="BA5" s="464" t="s">
         <v>58</v>
@@ -6142,7 +6152,7 @@
         <v>365</v>
       </c>
       <c r="BK5" s="470">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BL5" s="470">
         <v>11</v>
@@ -6151,17 +6161,17 @@
         <v>10</v>
       </c>
       <c r="BN5" s="470">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BO5" s="470">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="BP5" s="470">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BQ5" s="470">
         <f>BO5-BP5</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BR5" s="470">
         <v>43</v>
@@ -6221,7 +6231,7 @@
       </c>
       <c r="Y6" s="332">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z6" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X6)</f>
@@ -6229,7 +6239,7 @@
       </c>
       <c r="AA6" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X6)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB6" s="333">
         <f t="shared" si="1"/>
@@ -6245,7 +6255,7 @@
       </c>
       <c r="AE6" s="332">
         <f t="shared" si="4"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF6" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X6)+Z6</f>
@@ -6253,7 +6263,7 @@
       </c>
       <c r="AG6" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X6)+AA6</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH6" s="333">
         <f t="shared" si="5"/>
@@ -6302,7 +6312,7 @@
       </c>
       <c r="BB6" s="464">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC6" s="243">
         <f t="shared" si="10"/>
@@ -6314,7 +6324,7 @@
       </c>
       <c r="BE6" s="342">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BF6" s="89">
         <f t="shared" si="11"/>
@@ -6322,7 +6332,7 @@
       </c>
       <c r="BG6" s="11">
         <f t="shared" si="12"/>
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BI6" s="479">
         <v>4</v>
@@ -6331,29 +6341,29 @@
         <v>367</v>
       </c>
       <c r="BK6" s="479">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BL6" s="479">
         <v>11</v>
       </c>
       <c r="BM6" s="479">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BN6" s="479">
         <v>8</v>
       </c>
       <c r="BO6" s="479">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BP6" s="479">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BQ6" s="479">
         <f>BO6-BP6</f>
         <v>5</v>
       </c>
       <c r="BR6" s="479">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:77">
@@ -6406,11 +6416,11 @@
       </c>
       <c r="Y7" s="332">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z7" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X7)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA7" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X7)</f>
@@ -6430,11 +6440,11 @@
       </c>
       <c r="AE7" s="332">
         <f t="shared" si="4"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF7" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X7)+Z7</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG7" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X7)+AA7</f>
@@ -6609,11 +6619,11 @@
       </c>
       <c r="Y8" s="332">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z8" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X8)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA8" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X8)</f>
@@ -6633,11 +6643,11 @@
       </c>
       <c r="AE8" s="332">
         <f t="shared" si="4"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF8" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X8)+Z8</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG8" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X8)+AA8</f>
@@ -6731,29 +6741,29 @@
         <v>353</v>
       </c>
       <c r="BK8" s="479">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BL8" s="479">
         <v>10</v>
       </c>
       <c r="BM8" s="479">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BN8" s="479">
         <v>10</v>
       </c>
       <c r="BO8" s="479">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="BP8" s="479">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BQ8" s="479">
         <f>BO8-BP8</f>
         <v>9</v>
       </c>
       <c r="BR8" s="479">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:77">
@@ -6810,11 +6820,11 @@
       </c>
       <c r="Y9" s="332">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z9" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X9)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA9" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X9)</f>
@@ -6834,11 +6844,11 @@
       </c>
       <c r="AE9" s="332">
         <f t="shared" si="4"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF9" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X9)+Z9</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG9" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X9)+AA9</f>
@@ -6929,10 +6939,10 @@
         <v>7</v>
       </c>
       <c r="BJ9" s="471" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="BK9" s="471">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BL9" s="471">
         <v>10</v>
@@ -6941,17 +6951,17 @@
         <v>7</v>
       </c>
       <c r="BN9" s="471">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BO9" s="471">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="BP9" s="471">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BQ9" s="471">
         <f>BO9-BP9</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BR9" s="471">
         <v>37</v>
@@ -7133,29 +7143,29 @@
         <v>349</v>
       </c>
       <c r="BK10" s="479">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BL10" s="479">
         <v>10</v>
       </c>
       <c r="BM10" s="479">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BN10" s="479">
         <v>12</v>
       </c>
       <c r="BO10" s="479">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BP10" s="479">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="BQ10" s="479">
         <f>BO10-BP10</f>
         <v>-7</v>
       </c>
       <c r="BR10" s="479">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:77">
@@ -7212,11 +7222,11 @@
       </c>
       <c r="Y11" s="332">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z11" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X11)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA11" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X11)</f>
@@ -7236,11 +7246,11 @@
       </c>
       <c r="AE11" s="332">
         <f t="shared" si="4"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF11" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X11)+Z11</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG11" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X11)+AA11</f>
@@ -7413,7 +7423,7 @@
       </c>
       <c r="Y12" s="332">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z12" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X12)</f>
@@ -7421,7 +7431,7 @@
       </c>
       <c r="AA12" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X12)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB12" s="333">
         <f t="shared" si="1"/>
@@ -7437,7 +7447,7 @@
       </c>
       <c r="AE12" s="332">
         <f t="shared" si="4"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF12" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X12)+Z12</f>
@@ -7445,7 +7455,7 @@
       </c>
       <c r="AG12" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X12)+AA12</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH12" s="333">
         <f t="shared" si="5"/>
@@ -7532,29 +7542,29 @@
         <v>362</v>
       </c>
       <c r="BK12" s="479">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BL12" s="479">
         <v>7</v>
       </c>
       <c r="BM12" s="479">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN12" s="479">
         <v>11</v>
       </c>
       <c r="BO12" s="479">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="BP12" s="479">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BQ12" s="479">
         <f>BO12-BP12</f>
         <v>-7</v>
       </c>
       <c r="BR12" s="479">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:77">
@@ -7802,7 +7812,7 @@
       </c>
       <c r="Y14" s="332">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z14" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X14)</f>
@@ -7810,7 +7820,7 @@
       </c>
       <c r="AA14" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X14)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB14" s="333">
         <f t="shared" si="1"/>
@@ -7826,7 +7836,7 @@
       </c>
       <c r="AE14" s="332">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF14" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X14)+Z14</f>
@@ -7834,7 +7844,7 @@
       </c>
       <c r="AG14" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X14)+AA14</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH14" s="333">
         <f t="shared" si="5"/>
@@ -8059,7 +8069,7 @@
       </c>
       <c r="AN15" s="89">
         <f t="shared" si="13"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO15" s="243">
         <f t="shared" si="14"/>
@@ -8071,7 +8081,7 @@
       </c>
       <c r="AQ15" s="351">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR15" s="352">
         <f t="shared" si="17"/>
@@ -8079,26 +8089,26 @@
       </c>
       <c r="AS15" s="23">
         <f>AO15/AN15</f>
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AT15" s="2">
         <f t="shared" si="18"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU15" s="2">
         <f t="shared" si="19"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV15" s="2">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BA15" s="466" t="s">
         <v>60</v>
       </c>
       <c r="BB15" s="466">
         <f>SUM(BB3:BB14)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC15" s="243">
         <f>SUM(BC3:BC14)</f>
@@ -8110,7 +8120,7 @@
       </c>
       <c r="BE15" s="468">
         <f>SUM(BE3:BE14)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF15" s="89">
         <f>SUM(BF3:BF14)</f>
@@ -8118,7 +8128,7 @@
       </c>
       <c r="BG15" s="11">
         <f t="shared" si="12"/>
-        <v>0.37037037037037035</v>
+        <v>0.35714285714285715</v>
       </c>
       <c r="BI15" s="476" t="s">
         <v>91</v>
@@ -8871,11 +8881,11 @@
       </c>
       <c r="Y22" s="332">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z22" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X22)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA22" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X22)</f>
@@ -8895,11 +8905,11 @@
       </c>
       <c r="AE22" s="332">
         <f t="shared" si="4"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF22" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X22)+Z22</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG22" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X22)+AA22</f>
@@ -8978,11 +8988,11 @@
       </c>
       <c r="Y23" s="332">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z23" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X23)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA23" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X23)</f>
@@ -9002,11 +9012,11 @@
       </c>
       <c r="AE23" s="332">
         <f t="shared" si="4"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF23" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X23)+Z23</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG23" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X23)+AA23</f>
@@ -9065,11 +9075,11 @@
       </c>
       <c r="Y24" s="332">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z24" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X24)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA24" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X24)</f>
@@ -9089,11 +9099,11 @@
       </c>
       <c r="AE24" s="332">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF24" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X24)+Z24</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG24" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X24)+AA24</f>
@@ -9727,13 +9737,21 @@
       <c r="F31" s="267" t="s">
         <v>346</v>
       </c>
-      <c r="G31" s="266"/>
-      <c r="H31" s="266"/>
-      <c r="I31" s="380"/>
+      <c r="G31" s="266">
+        <v>1</v>
+      </c>
+      <c r="H31" s="266">
+        <v>2</v>
+      </c>
+      <c r="I31" s="380" t="s">
+        <v>33</v>
+      </c>
       <c r="J31" s="374"/>
       <c r="K31" s="266"/>
       <c r="L31" s="269"/>
-      <c r="M31" s="246"/>
+      <c r="M31" s="246" t="s">
+        <v>46</v>
+      </c>
       <c r="N31" s="270"/>
       <c r="O31" s="270"/>
       <c r="P31" s="271"/>
@@ -9742,7 +9760,9 @@
       <c r="S31" s="270"/>
       <c r="T31" s="270"/>
       <c r="U31" s="273"/>
-      <c r="V31" s="274"/>
+      <c r="V31" s="274" t="s">
+        <v>65</v>
+      </c>
       <c r="X31" s="329" t="s">
         <v>104</v>
       </c>
@@ -9922,11 +9942,11 @@
       </c>
       <c r="Y33" s="332">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z33" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X33)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA33" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X33)</f>
@@ -9946,11 +9966,11 @@
       </c>
       <c r="AE33" s="332">
         <f t="shared" si="4"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF33" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X33)+Z33</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG33" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X33)+AA33</f>
@@ -36957,21 +36977,51 @@
       <c r="B30" s="264" t="s">
         <v>360</v>
       </c>
-      <c r="C30" s="297"/>
-      <c r="D30" s="243"/>
-      <c r="E30" s="243"/>
-      <c r="F30" s="243"/>
-      <c r="G30" s="243"/>
-      <c r="H30" s="243"/>
-      <c r="I30" s="243"/>
-      <c r="J30" s="243"/>
-      <c r="K30" s="243"/>
-      <c r="L30" s="243"/>
-      <c r="M30" s="298"/>
-      <c r="N30" s="110"/>
-      <c r="O30" s="2"/>
-      <c r="P30" s="2"/>
-      <c r="Q30" s="159"/>
+      <c r="C30" s="297" t="s">
+        <v>106</v>
+      </c>
+      <c r="D30" s="243" t="s">
+        <v>89</v>
+      </c>
+      <c r="E30" s="243" t="s">
+        <v>394</v>
+      </c>
+      <c r="F30" s="243" t="s">
+        <v>64</v>
+      </c>
+      <c r="G30" s="243" t="s">
+        <v>52</v>
+      </c>
+      <c r="H30" s="243" t="s">
+        <v>74</v>
+      </c>
+      <c r="I30" s="243" t="s">
+        <v>71</v>
+      </c>
+      <c r="J30" s="243" t="s">
+        <v>51</v>
+      </c>
+      <c r="K30" s="243" t="s">
+        <v>395</v>
+      </c>
+      <c r="L30" s="243" t="s">
+        <v>46</v>
+      </c>
+      <c r="M30" s="298" t="s">
+        <v>81</v>
+      </c>
+      <c r="N30" s="110" t="s">
+        <v>59</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q30" s="159" t="s">
+        <v>66</v>
+      </c>
       <c r="R30" s="159"/>
       <c r="S30" s="51"/>
       <c r="T30" s="1"/>

--- a/인천 2026 기록.xlsx
+++ b/인천 2026 기록.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://familyinter-my.sharepoint.com/personal/hwlee_familyinter_onmicrosoft_com/Documents/바탕 화면/프로젝트300/대시보드/인천 대시보드/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2150" documentId="11_8673CE99959C043A6D95B170604D1DCFD5B90D48" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23400A68-04B9-4BBE-A10F-2B4BC21D2A4D}"/>
+  <xr:revisionPtr revIDLastSave="1110" documentId="11_54A2C5EF959CB4B30F95B27560762D485FE60CF6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6BDC7E4-95AC-44AF-A38B-1C2F08F079EC}"/>
   <bookViews>
-    <workbookView xWindow="8830" yWindow="1450" windowWidth="9600" windowHeight="5450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1770" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 토탈" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6036" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6054" uniqueCount="395">
   <si>
     <t>리그</t>
   </si>
@@ -240,7 +240,7 @@
     <t>총합</t>
   </si>
   <si>
-    <t>전북</t>
+    <t>제주</t>
   </si>
   <si>
     <t>수</t>
@@ -261,7 +261,7 @@
     <t>팀명</t>
   </si>
   <si>
-    <t>제주</t>
+    <t>전북</t>
   </si>
   <si>
     <t>안양</t>
@@ -288,9 +288,6 @@
     <t>송민석</t>
   </si>
   <si>
-    <t>인천</t>
-  </si>
-  <si>
     <t>부천</t>
   </si>
   <si>
@@ -304,6 +301,9 @@
   </si>
   <si>
     <t>고형진</t>
+  </si>
+  <si>
+    <t>인천</t>
   </si>
   <si>
     <t>정치인</t>
@@ -1291,17 +1291,11 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>인천</t>
+    <t>K리그1 2026 리그순위   (2026-09-20 - 30R 종료)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Kim Yeon-Soo</t>
-  </si>
-  <si>
-    <t>Leandro</t>
-  </si>
-  <si>
-    <t>K리그1 2026 리그순위   (2026-09-12 - 29R 진행 중)</t>
+    <t>인천</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -4967,10 +4961,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="기록표" displayName="기록표" ref="A42:E57" totalsRowShown="0" headerRowDxfId="84" headerRowBorderDxfId="83" tableBorderDxfId="82" totalsRowBorderDxfId="81">
   <tableColumns count="5">
@@ -5336,7 +5326,7 @@
         <v>1</v>
       </c>
       <c r="BI1" s="478" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="BJ1" s="477"/>
       <c r="BK1" s="477"/>
@@ -5603,11 +5593,11 @@
       </c>
       <c r="Y3" s="332">
         <f t="shared" ref="Y3:Y43" si="0">Z3+AA3</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z3" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X3)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA3" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X3)</f>
@@ -5627,11 +5617,11 @@
       </c>
       <c r="AE3" s="332">
         <f t="shared" ref="AE3:AE43" si="4">AF3+AG3</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF3" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X3)+Z3</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG3" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X3)+AA3</f>
@@ -5654,7 +5644,7 @@
       </c>
       <c r="AN3" s="2">
         <f>SUM(AO3:AQ3)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO3" s="243">
         <f t="shared" ref="AO3:AQ4" si="8">COUNTIFS($A$3:$A$40,"K리그",$F$3:$F$40,$AM3,$I$3:$I$40,AO$2)</f>
@@ -5662,7 +5652,7 @@
       </c>
       <c r="AP3" s="58">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ3" s="342">
         <f t="shared" si="8"/>
@@ -5670,19 +5660,19 @@
       </c>
       <c r="AR3" s="352">
         <f>AO3*3+AP3</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS3" s="10">
         <f>IFERROR(AO3/AN3,0)</f>
-        <v>0.35714285714285715</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AT3" s="2">
         <f>SUMIFS($G$3:$G$40,$A$3:$A$40,"K리그",$F$3:$F$40,$AM3)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU3" s="2">
         <f>SUMIFS($H$3:$H$40,$A$3:$A$40,"K리그",$F$3:$F$40,$AM3)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV3" s="2">
         <f>AT3-AU3</f>
@@ -5690,15 +5680,15 @@
       </c>
       <c r="AW3" s="434">
         <f>IFERROR(AR3/AN3,0)</f>
-        <v>1.2857142857142858</v>
+        <v>1.2666666666666666</v>
       </c>
       <c r="AX3" s="434">
         <f>IFERROR(AT3/AN3,0)</f>
-        <v>1.1428571428571428</v>
+        <v>1.1333333333333333</v>
       </c>
       <c r="AY3" s="434">
         <f>IFERROR(AU3/AN3,0)</f>
-        <v>1.0714285714285714</v>
+        <v>1.0666666666666667</v>
       </c>
       <c r="BA3" s="464" t="s">
         <v>47</v>
@@ -5734,7 +5724,7 @@
         <v>341</v>
       </c>
       <c r="BK3" s="469">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BL3" s="469">
         <v>19</v>
@@ -5743,17 +5733,17 @@
         <v>5</v>
       </c>
       <c r="BN3" s="469">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BO3" s="469">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="BP3" s="469">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BQ3" s="469">
         <f>BO3-BP3</f>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="BR3" s="469">
         <v>62</v>
@@ -5917,7 +5907,7 @@
       </c>
       <c r="BB4" s="464">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC4" s="243">
         <f t="shared" si="10"/>
@@ -5925,7 +5915,7 @@
       </c>
       <c r="BD4" s="465">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE4" s="342">
         <f t="shared" si="10"/>
@@ -5933,11 +5923,11 @@
       </c>
       <c r="BF4" s="89">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BG4" s="11">
         <f t="shared" si="12"/>
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="BI4" s="470">
         <v>2</v>
@@ -5946,7 +5936,7 @@
         <v>360</v>
       </c>
       <c r="BK4" s="470">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BL4" s="470">
         <v>14</v>
@@ -5955,17 +5945,17 @@
         <v>5</v>
       </c>
       <c r="BN4" s="470">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BO4" s="470">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BP4" s="470">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BQ4" s="470">
         <f>BO4-BP4</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BR4" s="470">
         <v>47</v>
@@ -6072,7 +6062,7 @@
       </c>
       <c r="AN5" s="337">
         <f>SUM(AN3:AN4)</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO5" s="337">
         <f>SUM(AO3:AO4)</f>
@@ -6080,7 +6070,7 @@
       </c>
       <c r="AP5" s="337">
         <f>SUM(AP3:AP4)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ5" s="337">
         <f>SUM(AQ3:AQ4)</f>
@@ -6088,19 +6078,19 @@
       </c>
       <c r="AR5" s="337">
         <f>SUM(AR3:AR4)</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AS5" s="349">
         <f>IFERROR(AO5/AN5,0)</f>
-        <v>0.35714285714285715</v>
+        <v>0.34482758620689657</v>
       </c>
       <c r="AT5" s="337">
         <f>SUM(AT3:AT4)</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AU5" s="337">
         <f>SUM(AU3:AU4)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AV5" s="337">
         <f>SUM(AV3:AV4)</f>
@@ -6108,15 +6098,15 @@
       </c>
       <c r="AW5" s="435">
         <f>IFERROR(AR5/AN5,0)</f>
-        <v>1.3214285714285714</v>
+        <v>1.3103448275862069</v>
       </c>
       <c r="AX5" s="435">
         <f>IFERROR(AT5/AN5,0)</f>
-        <v>1.25</v>
+        <v>1.2413793103448276</v>
       </c>
       <c r="AY5" s="435">
         <f>IFERROR(AU5/AN5,0)</f>
-        <v>1.1428571428571428</v>
+        <v>1.1379310344827587</v>
       </c>
       <c r="BA5" s="464" t="s">
         <v>58</v>
@@ -6149,13 +6139,13 @@
         <v>3</v>
       </c>
       <c r="BJ5" s="470" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="BK5" s="470">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BL5" s="470">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BM5" s="470">
         <v>10</v>
@@ -6164,17 +6154,17 @@
         <v>8</v>
       </c>
       <c r="BO5" s="470">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="BP5" s="470">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BQ5" s="470">
         <f>BO5-BP5</f>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BR5" s="470">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:77">
@@ -6231,11 +6221,11 @@
       </c>
       <c r="Y6" s="332">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z6" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X6)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA6" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X6)</f>
@@ -6243,7 +6233,7 @@
       </c>
       <c r="AB6" s="333">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC6" s="334">
         <f t="shared" si="2"/>
@@ -6251,15 +6241,15 @@
       </c>
       <c r="AD6" s="335">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE6" s="332">
         <f t="shared" si="4"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF6" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X6)+Z6</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG6" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X6)+AA6</f>
@@ -6267,7 +6257,7 @@
       </c>
       <c r="AH6" s="333">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI6" s="334">
         <f t="shared" si="6"/>
@@ -6275,7 +6265,7 @@
       </c>
       <c r="AJ6" s="335">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM6" s="337" t="s">
         <v>67</v>
@@ -6338,32 +6328,32 @@
         <v>4</v>
       </c>
       <c r="BJ6" s="479" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="BK6" s="479">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BL6" s="479">
         <v>11</v>
       </c>
       <c r="BM6" s="479">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN6" s="479">
         <v>8</v>
       </c>
       <c r="BO6" s="479">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BP6" s="479">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BQ6" s="479">
         <f>BO6-BP6</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BR6" s="479">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:77">
@@ -6416,7 +6406,7 @@
       </c>
       <c r="Y7" s="332">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z7" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X7)</f>
@@ -6424,7 +6414,7 @@
       </c>
       <c r="AA7" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X7)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB7" s="333">
         <f t="shared" si="1"/>
@@ -6440,7 +6430,7 @@
       </c>
       <c r="AE7" s="332">
         <f t="shared" si="4"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF7" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X7)+Z7</f>
@@ -6448,7 +6438,7 @@
       </c>
       <c r="AG7" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X7)+AA7</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH7" s="333">
         <f t="shared" si="5"/>
@@ -6466,7 +6456,7 @@
         <v>42</v>
       </c>
       <c r="AM7" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="AN7" s="89">
         <f t="shared" ref="AN7:AN17" si="13">SUM(AO7:AQ7)</f>
@@ -6538,29 +6528,29 @@
         <v>369</v>
       </c>
       <c r="BK7" s="479">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BL7" s="479">
         <v>10</v>
       </c>
       <c r="BM7" s="479">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN7" s="479">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BO7" s="479">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BP7" s="479">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BQ7" s="479">
         <f>BO7-BP7</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BR7" s="479">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:77">
@@ -6619,11 +6609,11 @@
       </c>
       <c r="Y8" s="332">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z8" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X8)</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA8" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X8)</f>
@@ -6643,11 +6633,11 @@
       </c>
       <c r="AE8" s="332">
         <f t="shared" si="4"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF8" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X8)+Z8</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG8" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X8)+AA8</f>
@@ -6673,7 +6663,7 @@
       </c>
       <c r="AN8" s="89">
         <f t="shared" si="13"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO8" s="243">
         <f t="shared" si="14"/>
@@ -6681,7 +6671,7 @@
       </c>
       <c r="AP8" s="243">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ8" s="351">
         <f t="shared" si="16"/>
@@ -6689,7 +6679,7 @@
       </c>
       <c r="AR8" s="352">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS8" s="23">
         <f>AO8/AN8</f>
@@ -6697,11 +6687,11 @@
       </c>
       <c r="AT8" s="2">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU8" s="2">
         <f t="shared" si="19"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV8" s="2">
         <f t="shared" si="20"/>
@@ -6741,29 +6731,29 @@
         <v>353</v>
       </c>
       <c r="BK8" s="479">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BL8" s="479">
         <v>10</v>
       </c>
       <c r="BM8" s="479">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BN8" s="479">
         <v>10</v>
       </c>
       <c r="BO8" s="479">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="BP8" s="479">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="BQ8" s="479">
         <f>BO8-BP8</f>
         <v>9</v>
       </c>
       <c r="BR8" s="479">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:77">
@@ -6820,11 +6810,11 @@
       </c>
       <c r="Y9" s="332">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z9" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X9)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA9" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X9)</f>
@@ -6844,11 +6834,11 @@
       </c>
       <c r="AE9" s="332">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF9" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X9)+Z9</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG9" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X9)+AA9</f>
@@ -6935,36 +6925,36 @@
         <f t="shared" si="12"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="BI9" s="471">
+      <c r="BI9" s="479">
         <v>7</v>
       </c>
-      <c r="BJ9" s="471" t="s">
-        <v>393</v>
-      </c>
-      <c r="BK9" s="471">
+      <c r="BJ9" s="479" t="s">
+        <v>349</v>
+      </c>
+      <c r="BK9" s="479">
+        <v>30</v>
+      </c>
+      <c r="BL9" s="479">
+        <v>11</v>
+      </c>
+      <c r="BM9" s="479">
+        <v>7</v>
+      </c>
+      <c r="BN9" s="479">
+        <v>12</v>
+      </c>
+      <c r="BO9" s="479">
         <v>28</v>
       </c>
-      <c r="BL9" s="471">
-        <v>10</v>
-      </c>
-      <c r="BM9" s="471">
-        <v>7</v>
-      </c>
-      <c r="BN9" s="471">
-        <v>11</v>
-      </c>
-      <c r="BO9" s="471">
-        <v>35</v>
-      </c>
-      <c r="BP9" s="471">
-        <v>32</v>
-      </c>
-      <c r="BQ9" s="471">
+      <c r="BP9" s="479">
+        <v>34</v>
+      </c>
+      <c r="BQ9" s="479">
         <f>BO9-BP9</f>
-        <v>3</v>
-      </c>
-      <c r="BR9" s="471">
-        <v>37</v>
+        <v>-6</v>
+      </c>
+      <c r="BR9" s="479">
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:77">
@@ -7014,7 +7004,7 @@
       <c r="T10" s="270"/>
       <c r="U10" s="273"/>
       <c r="V10" s="274" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="X10" s="327" t="s">
         <v>50</v>
@@ -7110,7 +7100,7 @@
         <v>-3</v>
       </c>
       <c r="BA10" s="464" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BB10" s="464">
         <f t="shared" si="9"/>
@@ -7140,32 +7130,32 @@
         <v>8</v>
       </c>
       <c r="BJ10" s="479" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="BK10" s="479">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BL10" s="479">
+        <v>9</v>
+      </c>
+      <c r="BM10" s="479">
+        <v>11</v>
+      </c>
+      <c r="BN10" s="479">
         <v>10</v>
       </c>
-      <c r="BM10" s="479">
-        <v>7</v>
-      </c>
-      <c r="BN10" s="479">
-        <v>12</v>
-      </c>
       <c r="BO10" s="479">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="BP10" s="479">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="BQ10" s="479">
         <f>BO10-BP10</f>
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="BR10" s="479">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:77">
@@ -7208,7 +7198,7 @@
       <c r="O11" s="270"/>
       <c r="P11" s="271"/>
       <c r="Q11" s="272" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R11" s="270"/>
       <c r="S11" s="270"/>
@@ -7218,15 +7208,15 @@
         <v>65</v>
       </c>
       <c r="X11" s="358" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Y11" s="332">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z11" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X11)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA11" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X11)</f>
@@ -7246,11 +7236,11 @@
       </c>
       <c r="AE11" s="332">
         <f t="shared" si="4"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF11" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X11)+Z11</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG11" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X11)+AA11</f>
@@ -7311,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="BA11" s="464" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="BB11" s="464">
         <f t="shared" si="9"/>
@@ -7337,36 +7327,36 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BI11" s="479">
+      <c r="BI11" s="471">
         <v>9</v>
       </c>
-      <c r="BJ11" s="479" t="s">
-        <v>355</v>
-      </c>
-      <c r="BK11" s="479">
-        <v>28</v>
-      </c>
-      <c r="BL11" s="479">
+      <c r="BJ11" s="471" t="s">
+        <v>394</v>
+      </c>
+      <c r="BK11" s="471">
+        <v>29</v>
+      </c>
+      <c r="BL11" s="471">
+        <v>10</v>
+      </c>
+      <c r="BM11" s="471">
         <v>8</v>
       </c>
-      <c r="BM11" s="479">
-        <v>10</v>
-      </c>
-      <c r="BN11" s="479">
-        <v>10</v>
-      </c>
-      <c r="BO11" s="479">
-        <v>35</v>
-      </c>
-      <c r="BP11" s="479">
-        <v>45</v>
-      </c>
-      <c r="BQ11" s="479">
+      <c r="BN11" s="471">
+        <v>11</v>
+      </c>
+      <c r="BO11" s="471">
+        <v>36</v>
+      </c>
+      <c r="BP11" s="471">
+        <v>33</v>
+      </c>
+      <c r="BQ11" s="471">
         <f>BO11-BP11</f>
-        <v>-10</v>
-      </c>
-      <c r="BR11" s="479">
-        <v>34</v>
+        <v>3</v>
+      </c>
+      <c r="BR11" s="471">
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:77">
@@ -7423,7 +7413,7 @@
       </c>
       <c r="Y12" s="332">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z12" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X12)</f>
@@ -7431,7 +7421,7 @@
       </c>
       <c r="AA12" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X12)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AB12" s="333">
         <f t="shared" si="1"/>
@@ -7447,7 +7437,7 @@
       </c>
       <c r="AE12" s="332">
         <f t="shared" si="4"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF12" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X12)+Z12</f>
@@ -7455,7 +7445,7 @@
       </c>
       <c r="AG12" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X12)+AA12</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH12" s="333">
         <f t="shared" si="5"/>
@@ -7539,32 +7529,32 @@
         <v>10</v>
       </c>
       <c r="BJ12" s="479" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="BK12" s="479">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BL12" s="479">
+        <v>5</v>
+      </c>
+      <c r="BM12" s="479">
+        <v>18</v>
+      </c>
+      <c r="BN12" s="479">
         <v>7</v>
       </c>
-      <c r="BM12" s="479">
-        <v>11</v>
-      </c>
-      <c r="BN12" s="479">
-        <v>11</v>
-      </c>
       <c r="BO12" s="479">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="BP12" s="479">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BQ12" s="479">
         <f>BO12-BP12</f>
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="BR12" s="479">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:77">
@@ -7610,7 +7600,7 @@
         <v>11404</v>
       </c>
       <c r="V13" s="274" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="X13" s="327" t="s">
         <v>85</v>
@@ -7736,32 +7726,32 @@
         <v>11</v>
       </c>
       <c r="BJ13" s="479" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="BK13" s="479">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BL13" s="479">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BM13" s="479">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="BN13" s="479">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BO13" s="479">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="BP13" s="479">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BQ13" s="479">
         <f>BO13-BP13</f>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="BR13" s="479">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:77" ht="17.5" customHeight="1">
@@ -7934,29 +7924,29 @@
         <v>345</v>
       </c>
       <c r="BK14" s="472">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BL14" s="472">
         <v>1</v>
       </c>
       <c r="BM14" s="472">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BN14" s="472">
         <v>17</v>
       </c>
       <c r="BO14" s="472">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BP14" s="472">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="BQ14" s="472">
         <f>BO14-BP14</f>
         <v>-42</v>
       </c>
       <c r="BR14" s="472">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:77" ht="17.5" customHeight="1">
@@ -8008,7 +7998,7 @@
       <c r="T15" s="320"/>
       <c r="U15" s="402"/>
       <c r="V15" s="403" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="X15" s="358" t="s">
         <v>90</v>
@@ -8108,7 +8098,7 @@
       </c>
       <c r="BB15" s="466">
         <f>SUM(BB3:BB14)</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC15" s="243">
         <f>SUM(BC3:BC14)</f>
@@ -8116,7 +8106,7 @@
       </c>
       <c r="BD15" s="467">
         <f>SUM(BD3:BD14)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BE15" s="468">
         <f>SUM(BE3:BE14)</f>
@@ -8124,11 +8114,11 @@
       </c>
       <c r="BF15" s="89">
         <f>SUM(BF3:BF14)</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BG15" s="11">
         <f t="shared" si="12"/>
-        <v>0.35714285714285715</v>
+        <v>0.34482758620689657</v>
       </c>
       <c r="BI15" s="476" t="s">
         <v>91</v>
@@ -8243,7 +8233,7 @@
         <v>42</v>
       </c>
       <c r="AM16" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="AN16" s="89">
         <f t="shared" si="13"/>
@@ -8323,13 +8313,13 @@
         <v>71</v>
       </c>
       <c r="P17" s="368" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q17" s="363" t="s">
         <v>64</v>
       </c>
       <c r="R17" s="320" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S17" s="320" t="s">
         <v>59</v>
@@ -8396,7 +8386,7 @@
         <v>42</v>
       </c>
       <c r="AM17" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AN17" s="89">
         <f t="shared" si="13"/>
@@ -8476,7 +8466,7 @@
       <c r="T18" s="320"/>
       <c r="U18" s="400"/>
       <c r="V18" s="312" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="X18" s="327" t="s">
         <v>94</v>
@@ -8780,11 +8770,11 @@
       </c>
       <c r="Y21" s="332">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Z21" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X21)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA21" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X21)</f>
@@ -8804,11 +8794,11 @@
       </c>
       <c r="AE21" s="332">
         <f t="shared" si="4"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF21" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X21)+Z21</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG21" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X21)+AA21</f>
@@ -8881,11 +8871,11 @@
       </c>
       <c r="Y22" s="332">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z22" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X22)</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA22" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X22)</f>
@@ -8905,11 +8895,11 @@
       </c>
       <c r="AE22" s="332">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF22" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X22)+Z22</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG22" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X22)+AA22</f>
@@ -8976,7 +8966,7 @@
         <v>64</v>
       </c>
       <c r="S23" s="320" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="T23" s="320"/>
       <c r="U23" s="400"/>
@@ -8988,11 +8978,11 @@
       </c>
       <c r="Y23" s="332">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z23" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X23)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA23" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X23)</f>
@@ -9012,11 +9002,11 @@
       </c>
       <c r="AE23" s="332">
         <f t="shared" si="4"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF23" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X23)+Z23</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG23" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X23)+AA23</f>
@@ -9075,11 +9065,11 @@
       </c>
       <c r="Y24" s="332">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z24" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X24)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA24" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X24)</f>
@@ -9099,11 +9089,11 @@
       </c>
       <c r="AE24" s="332">
         <f t="shared" si="4"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF24" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X24)+Z24</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG24" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X24)+AA24</f>
@@ -9172,11 +9162,11 @@
         <v>76</v>
       </c>
       <c r="X25" s="329" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y25" s="332">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z25" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X25)</f>
@@ -9184,7 +9174,7 @@
       </c>
       <c r="AA25" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X25)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB25" s="333">
         <f t="shared" si="1"/>
@@ -9200,7 +9190,7 @@
       </c>
       <c r="AE25" s="332">
         <f t="shared" si="4"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF25" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X25)+Z25</f>
@@ -9208,7 +9198,7 @@
       </c>
       <c r="AG25" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X25)+AA25</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH25" s="333">
         <f t="shared" si="5"/>
@@ -9559,7 +9549,7 @@
       <c r="T29" s="270"/>
       <c r="U29" s="273"/>
       <c r="V29" s="274" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="X29" s="329" t="s">
         <v>101</v>
@@ -9744,7 +9734,7 @@
         <v>2</v>
       </c>
       <c r="I31" s="380" t="s">
-        <v>33</v>
+        <v>343</v>
       </c>
       <c r="J31" s="374"/>
       <c r="K31" s="266"/>
@@ -9834,13 +9824,21 @@
       <c r="F32" s="268" t="s">
         <v>342</v>
       </c>
-      <c r="G32" s="266"/>
-      <c r="H32" s="266"/>
-      <c r="I32" s="380"/>
+      <c r="G32" s="266">
+        <v>1</v>
+      </c>
+      <c r="H32" s="266">
+        <v>1</v>
+      </c>
+      <c r="I32" s="380" t="s">
+        <v>350</v>
+      </c>
       <c r="J32" s="374"/>
       <c r="K32" s="266"/>
       <c r="L32" s="269"/>
-      <c r="M32" s="246"/>
+      <c r="M32" s="246" t="s">
+        <v>66</v>
+      </c>
       <c r="N32" s="270"/>
       <c r="O32" s="270"/>
       <c r="P32" s="271"/>
@@ -9848,18 +9846,22 @@
       <c r="R32" s="270"/>
       <c r="S32" s="270"/>
       <c r="T32" s="270"/>
-      <c r="U32" s="273"/>
-      <c r="V32" s="274"/>
+      <c r="U32" s="273">
+        <v>9312</v>
+      </c>
+      <c r="V32" s="274" t="s">
+        <v>53</v>
+      </c>
       <c r="X32" s="451" t="s">
         <v>105</v>
       </c>
       <c r="Y32" s="332">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z32" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X32)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA32" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X32)</f>
@@ -9879,11 +9881,11 @@
       </c>
       <c r="AE32" s="332">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF32" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X32)+Z32</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG32" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X32)+AA32</f>
@@ -9942,11 +9944,11 @@
       </c>
       <c r="Y33" s="332">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z33" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X33)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA33" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X33)</f>
@@ -9966,11 +9968,11 @@
       </c>
       <c r="AE33" s="332">
         <f t="shared" si="4"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF33" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X33)+Z33</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG33" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X33)+AA33</f>
@@ -10608,11 +10610,11 @@
       </c>
       <c r="Y41" s="332">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z41" s="474">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X41)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA41" s="474">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X41)</f>
@@ -10632,11 +10634,11 @@
       </c>
       <c r="AE41" s="475">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF41" s="475">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X41)+Z41</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG41" s="475">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X41)+AA41</f>
@@ -10668,7 +10670,7 @@
       </c>
       <c r="Y42" s="332">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z42" s="474">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X42)</f>
@@ -10676,7 +10678,7 @@
       </c>
       <c r="AA42" s="474">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X42)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB42" s="333">
         <f t="shared" si="1"/>
@@ -10692,7 +10694,7 @@
       </c>
       <c r="AE42" s="475">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF42" s="475">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X42)+Z42</f>
@@ -10700,7 +10702,7 @@
       </c>
       <c r="AG42" s="475">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X42)+AA42</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH42" s="475">
         <f t="shared" si="5"/>
@@ -10798,15 +10800,15 @@
       </c>
       <c r="N44" s="2">
         <f>COUNT(U3:U40)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O44" s="96">
         <f>SUMIFS(U3:U41,A3:A41,M44)</f>
-        <v>138674</v>
+        <v>147986</v>
       </c>
       <c r="P44" s="96">
         <f>O44/N44</f>
-        <v>9905.2857142857138</v>
+        <v>9865.7333333333336</v>
       </c>
       <c r="Q44" s="136">
         <v>19</v>
@@ -10819,7 +10821,7 @@
       </c>
       <c r="T44" s="165">
         <f>(P44-S44)/S44</f>
-        <v>-2.6391715701707317E-2</v>
+        <v>-3.0279390108051914E-2</v>
       </c>
     </row>
     <row r="45" spans="1:36">
@@ -11646,7 +11648,7 @@
     </row>
     <row r="22" spans="2:11">
       <c r="B22" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C22" s="2">
         <v>3</v>
@@ -11742,7 +11744,7 @@
     </row>
     <row r="25" spans="2:11">
       <c r="B25" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C25" s="2">
         <v>3</v>
@@ -12163,7 +12165,7 @@
     </row>
     <row r="40" spans="2:11">
       <c r="B40" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C40" s="2">
         <v>4</v>
@@ -12259,7 +12261,7 @@
     </row>
     <row r="43" spans="2:11">
       <c r="B43" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C43" s="2">
         <v>4</v>
@@ -12712,7 +12714,7 @@
     </row>
     <row r="59" spans="2:11">
       <c r="B59" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C59" s="2">
         <v>4</v>
@@ -12776,7 +12778,7 @@
     </row>
     <row r="61" spans="2:11">
       <c r="B61" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C61" s="2">
         <v>3</v>
@@ -13293,7 +13295,7 @@
     </row>
     <row r="79" spans="2:11">
       <c r="B79" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C79" s="2">
         <v>0</v>
@@ -13421,7 +13423,7 @@
     </row>
     <row r="83" spans="2:11">
       <c r="B83" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C83" s="2">
         <v>0</v>
@@ -13992,7 +13994,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E5" s="30" t="s">
         <v>45</v>
@@ -14369,7 +14371,7 @@
         <v>6</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E8" s="30" t="s">
         <v>49</v>
@@ -15146,7 +15148,7 @@
         <v>12</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E14" s="24" t="s">
         <v>49</v>
@@ -15238,7 +15240,7 @@
         <v>13</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E15" s="24" t="s">
         <v>45</v>
@@ -16690,7 +16692,7 @@
         <v>25</v>
       </c>
       <c r="D27" s="30" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E27" s="30" t="s">
         <v>49</v>
@@ -17285,7 +17287,7 @@
         <v>42</v>
       </c>
       <c r="AD31" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="AE31" s="2">
         <f t="shared" si="17"/>
@@ -17335,7 +17337,7 @@
         <v>30</v>
       </c>
       <c r="D32" s="30" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E32" s="30" t="s">
         <v>45</v>
@@ -17505,7 +17507,7 @@
         <v>42</v>
       </c>
       <c r="AD33" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="AE33" s="2">
         <f t="shared" si="17"/>
@@ -17983,7 +17985,7 @@
         <v>36</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E38" s="24" t="s">
         <v>45</v>
@@ -18937,7 +18939,7 @@
         <v>114</v>
       </c>
       <c r="AD47" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="AE47" s="2">
         <f t="shared" si="17"/>
@@ -19095,7 +19097,7 @@
         <v>130</v>
       </c>
       <c r="D50" s="104" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E50" s="104" t="s">
         <v>49</v>
@@ -19712,7 +19714,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D5" s="30" t="s">
         <v>45</v>
@@ -20034,7 +20036,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D8" s="30" t="s">
         <v>49</v>
@@ -20732,7 +20734,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D14" s="24" t="s">
         <v>49</v>
@@ -20843,7 +20845,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D15" s="24" t="s">
         <v>45</v>
@@ -21990,7 +21992,7 @@
         <v>25</v>
       </c>
       <c r="C27" s="30" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D27" s="30" t="s">
         <v>49</v>
@@ -22444,7 +22446,7 @@
         <v>3</v>
       </c>
       <c r="Y31" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="Z31" s="2">
         <f t="shared" si="14"/>
@@ -22491,7 +22493,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="30" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D32" s="30" t="s">
         <v>45</v>
@@ -22640,7 +22642,7 @@
         <v>0</v>
       </c>
       <c r="Y33" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="Z33" s="2">
         <f t="shared" si="14"/>
@@ -23069,7 +23071,7 @@
         <v>36</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D38" s="24" t="s">
         <v>45</v>
@@ -26660,7 +26662,7 @@
         <v>130</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D5" s="30" t="s">
         <v>49</v>
@@ -28490,7 +28492,7 @@
         <v>0</v>
       </c>
       <c r="AC32" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="AD32" s="2">
         <f>SUM(AE32:AG32)</f>
@@ -29959,7 +29961,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="73" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D11" s="73" t="s">
         <v>45</v>
@@ -30195,7 +30197,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="73" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D13" s="73" t="s">
         <v>45</v>
@@ -30702,7 +30704,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="73" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D18" s="73" t="s">
         <v>49</v>
@@ -31225,7 +31227,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D23" s="24" t="s">
         <v>49</v>
@@ -31678,7 +31680,7 @@
         <v>28</v>
       </c>
       <c r="C28" s="30" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D28" s="30" t="s">
         <v>45</v>
@@ -31808,7 +31810,7 @@
         <v>0</v>
       </c>
       <c r="AD29" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="AE29" s="2">
         <f t="shared" ref="AE29:AE39" si="13">SUM(AF29:AH29)</f>
@@ -32033,7 +32035,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="30" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D32" s="30" t="s">
         <v>49</v>
@@ -32078,7 +32080,7 @@
         <v>0</v>
       </c>
       <c r="AD32" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="AE32" s="2">
         <f t="shared" si="13"/>
@@ -32569,7 +32571,7 @@
         <v>36</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D38" s="24" t="s">
         <v>45</v>
@@ -32723,7 +32725,7 @@
         <v>38</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D40" s="37" t="s">
         <v>49</v>
@@ -33280,7 +33282,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D11" s="20" t="s">
         <v>49</v>
@@ -33340,7 +33342,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D12" s="20" t="s">
         <v>45</v>
@@ -33778,7 +33780,7 @@
         <v>18</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D20" s="20" t="s">
         <v>45</v>
@@ -33924,7 +33926,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D23" s="20" t="s">
         <v>49</v>
@@ -34257,7 +34259,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D29" s="20" t="s">
         <v>45</v>
@@ -34275,7 +34277,7 @@
         <v>33</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="L29" s="2">
         <f t="shared" ref="L29:L39" si="0">SUM(M29:O29)</f>
@@ -34452,7 +34454,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D32" s="20" t="s">
         <v>49</v>
@@ -34470,7 +34472,7 @@
         <v>33</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="L32" s="2">
         <f t="shared" si="0"/>
@@ -35317,7 +35319,7 @@
         <v>46</v>
       </c>
       <c r="N2" s="110" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>98</v>
@@ -35396,7 +35398,7 @@
         <v>59</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>85</v>
@@ -35472,7 +35474,7 @@
         <v>59</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
@@ -35544,13 +35546,13 @@
         <v>59</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R5" s="159" t="s">
         <v>66</v>
@@ -35622,10 +35624,10 @@
         <v>71</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q6" s="159" t="s">
         <v>66</v>
@@ -35698,7 +35700,7 @@
         <v>71</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>83</v>
@@ -35779,7 +35781,7 @@
         <v>71</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q8" s="159" t="s">
         <v>66</v>
@@ -35820,7 +35822,7 @@
         <v>71</v>
       </c>
       <c r="K9" s="243" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L9" s="243" t="s">
         <v>66</v>
@@ -35863,7 +35865,7 @@
         <v>89</v>
       </c>
       <c r="F10" s="243" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G10" s="243" t="s">
         <v>98</v>
@@ -35884,7 +35886,7 @@
         <v>66</v>
       </c>
       <c r="M10" s="298" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N10" s="110" t="s">
         <v>64</v>
@@ -35939,7 +35941,7 @@
         <v>71</v>
       </c>
       <c r="L11" s="243" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M11" s="298" t="s">
         <v>46</v>
@@ -35948,7 +35950,7 @@
         <v>97</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>85</v>
@@ -35994,7 +35996,7 @@
         <v>59</v>
       </c>
       <c r="K12" s="243" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L12" s="243" t="s">
         <v>66</v>
@@ -36012,7 +36014,7 @@
         <v>99</v>
       </c>
       <c r="Q12" s="159" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R12" s="159" t="s">
         <v>113</v>
@@ -36067,10 +36069,10 @@
         <v>59</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q13" s="159" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R13" s="159" t="s">
         <v>106</v>
@@ -36110,7 +36112,7 @@
         <v>59</v>
       </c>
       <c r="K14" s="243" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L14" s="243" t="s">
         <v>66</v>
@@ -36153,7 +36155,7 @@
         <v>96</v>
       </c>
       <c r="F15" s="243" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G15" s="243" t="s">
         <v>64</v>
@@ -36189,7 +36191,7 @@
         <v>74</v>
       </c>
       <c r="R15" s="159" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S15" s="51"/>
       <c r="T15" s="1"/>
@@ -36229,13 +36231,13 @@
         <v>71</v>
       </c>
       <c r="L16" s="243" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M16" s="298" t="s">
         <v>66</v>
       </c>
       <c r="N16" s="110" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>92</v>
@@ -36287,13 +36289,13 @@
         <v>71</v>
       </c>
       <c r="L17" s="243" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M17" s="298" t="s">
         <v>66</v>
       </c>
       <c r="N17" s="110" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>46</v>
@@ -36345,13 +36347,13 @@
         <v>71</v>
       </c>
       <c r="L18" s="243" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M18" s="298" t="s">
         <v>66</v>
       </c>
       <c r="N18" s="110" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>46</v>
@@ -36401,13 +36403,13 @@
         <v>71</v>
       </c>
       <c r="L19" s="243" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M19" s="298" t="s">
         <v>66</v>
       </c>
       <c r="N19" s="110" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>46</v>
@@ -36459,13 +36461,13 @@
         <v>71</v>
       </c>
       <c r="L20" s="243" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M20" s="298" t="s">
         <v>66</v>
       </c>
       <c r="N20" s="110" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>46</v>
@@ -36517,13 +36519,13 @@
         <v>71</v>
       </c>
       <c r="L21" s="243" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M21" s="298" t="s">
         <v>66</v>
       </c>
       <c r="N21" s="110" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>46</v>
@@ -36578,7 +36580,7 @@
         <v>46</v>
       </c>
       <c r="M22" s="298" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N22" s="110" t="s">
         <v>66</v>
@@ -36590,7 +36592,7 @@
         <v>94</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R22" s="159" t="s">
         <v>93</v>
@@ -36659,7 +36661,7 @@
         <v>51</v>
       </c>
       <c r="L24" s="243" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M24" s="298" t="s">
         <v>66</v>
@@ -36668,7 +36670,7 @@
         <v>46</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>94</v>
@@ -36717,13 +36719,13 @@
         <v>87</v>
       </c>
       <c r="L25" s="243" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M25" s="298" t="s">
         <v>66</v>
       </c>
       <c r="N25" s="110" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>46</v>
@@ -36757,7 +36759,7 @@
         <v>97</v>
       </c>
       <c r="F26" s="243" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G26" s="243" t="s">
         <v>64</v>
@@ -36781,7 +36783,7 @@
         <v>66</v>
       </c>
       <c r="N26" s="110" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>46</v>
@@ -36836,7 +36838,7 @@
         <v>46</v>
       </c>
       <c r="M27" s="298" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N27" s="110" t="s">
         <v>87</v>
@@ -36892,7 +36894,7 @@
         <v>46</v>
       </c>
       <c r="M28" s="298" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N28" s="110" t="s">
         <v>96</v>
@@ -36956,7 +36958,7 @@
         <v>71</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>121</v>
@@ -36965,7 +36967,7 @@
         <v>87</v>
       </c>
       <c r="R29" s="159" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S29" s="51"/>
       <c r="T29" s="1"/>
@@ -36984,7 +36986,7 @@
         <v>89</v>
       </c>
       <c r="E30" s="243" t="s">
-        <v>394</v>
+        <v>105</v>
       </c>
       <c r="F30" s="243" t="s">
         <v>64</v>
@@ -37002,13 +37004,13 @@
         <v>51</v>
       </c>
       <c r="K30" s="243" t="s">
-        <v>395</v>
+        <v>102</v>
       </c>
       <c r="L30" s="243" t="s">
         <v>46</v>
       </c>
       <c r="M30" s="298" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N30" s="110" t="s">
         <v>59</v>
@@ -37033,21 +37035,51 @@
       <c r="B31" s="264" t="s">
         <v>353</v>
       </c>
-      <c r="C31" s="297"/>
-      <c r="D31" s="243"/>
-      <c r="E31" s="243"/>
-      <c r="F31" s="243"/>
-      <c r="G31" s="243"/>
-      <c r="H31" s="243"/>
-      <c r="I31" s="243"/>
-      <c r="J31" s="243"/>
-      <c r="K31" s="243"/>
-      <c r="L31" s="243"/>
-      <c r="M31" s="298"/>
-      <c r="N31" s="110"/>
-      <c r="O31" s="2"/>
-      <c r="P31" s="2"/>
-      <c r="Q31" s="159"/>
+      <c r="C31" s="297" t="s">
+        <v>106</v>
+      </c>
+      <c r="D31" s="243" t="s">
+        <v>89</v>
+      </c>
+      <c r="E31" s="243" t="s">
+        <v>97</v>
+      </c>
+      <c r="F31" s="243" t="s">
+        <v>64</v>
+      </c>
+      <c r="G31" s="243" t="s">
+        <v>52</v>
+      </c>
+      <c r="H31" s="243" t="s">
+        <v>74</v>
+      </c>
+      <c r="I31" s="243" t="s">
+        <v>51</v>
+      </c>
+      <c r="J31" s="243" t="s">
+        <v>102</v>
+      </c>
+      <c r="K31" s="243" t="s">
+        <v>80</v>
+      </c>
+      <c r="L31" s="243" t="s">
+        <v>46</v>
+      </c>
+      <c r="M31" s="298" t="s">
+        <v>66</v>
+      </c>
+      <c r="N31" s="110" t="s">
+        <v>71</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q31" s="159" t="s">
+        <v>121</v>
+      </c>
       <c r="R31" s="159"/>
       <c r="S31" s="51"/>
       <c r="T31" s="1"/>
@@ -37396,7 +37428,7 @@
         <v>8</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C50" s="2">
         <v>1</v>
@@ -37413,7 +37445,7 @@
         <v>9</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C51" s="2">
         <v>2</v>
@@ -37430,7 +37462,7 @@
         <v>10</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C52" s="2">
         <v>6</v>
@@ -37554,7 +37586,7 @@
         <v>18</v>
       </c>
       <c r="B60" s="352" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="96"/>
@@ -37576,7 +37608,7 @@
         <v>20</v>
       </c>
       <c r="B62" s="352" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="96"/>
@@ -37587,7 +37619,7 @@
         <v>21</v>
       </c>
       <c r="B63" s="352" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="96"/>
@@ -37642,7 +37674,7 @@
         <v>26</v>
       </c>
       <c r="B68" s="352" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="96"/>
@@ -37664,7 +37696,7 @@
         <v>28</v>
       </c>
       <c r="B70" s="352" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" s="96"/>
@@ -37719,7 +37751,7 @@
         <v>33</v>
       </c>
       <c r="B75" s="413" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C75" s="441"/>
       <c r="D75" s="442"/>
@@ -39507,7 +39539,7 @@
         <v>9</v>
       </c>
       <c r="E11" s="267" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F11" s="266" t="s">
         <v>49</v>
@@ -40309,7 +40341,7 @@
         <v>42</v>
       </c>
       <c r="AM15" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AN15" s="89">
         <f t="shared" si="15"/>
@@ -40567,7 +40599,7 @@
         <v>15</v>
       </c>
       <c r="E17" s="243" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F17" s="244" t="s">
         <v>45</v>
@@ -41509,7 +41541,7 @@
       <c r="O23" s="58"/>
       <c r="P23" s="59"/>
       <c r="Q23" s="143" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R23" s="58"/>
       <c r="S23" s="58"/>
@@ -42233,7 +42265,7 @@
         <v>28</v>
       </c>
       <c r="E30" s="267" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F30" s="266" t="s">
         <v>49</v>
@@ -42263,7 +42295,7 @@
         <v>65</v>
       </c>
       <c r="X30" s="329" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y30" s="297">
         <f t="shared" si="0"/>
@@ -44031,7 +44063,7 @@
         <v>64</v>
       </c>
       <c r="G2" s="243" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H2" s="243" t="s">
         <v>74</v>
@@ -44141,7 +44173,7 @@
         <v>64</v>
       </c>
       <c r="G3" s="243" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H3" s="243" t="s">
         <v>74</v>
@@ -44253,7 +44285,7 @@
         <v>64</v>
       </c>
       <c r="G4" s="243" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H4" s="243" t="s">
         <v>74</v>
@@ -44297,7 +44329,7 @@
         <v>108</v>
       </c>
       <c r="X4" s="243" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y4" s="243" t="s">
         <v>178</v>
@@ -44363,7 +44395,7 @@
         <v>64</v>
       </c>
       <c r="G5" s="243" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H5" s="243" t="s">
         <v>74</v>
@@ -44441,7 +44473,7 @@
         <v>64</v>
       </c>
       <c r="G6" s="243" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H6" s="243" t="s">
         <v>74</v>
@@ -44540,7 +44572,7 @@
         <v>46</v>
       </c>
       <c r="N7" s="110" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>71</v>
@@ -44597,7 +44629,7 @@
         <v>64</v>
       </c>
       <c r="G8" s="243" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H8" s="243" t="s">
         <v>93</v>
@@ -44676,7 +44708,7 @@
         <v>46</v>
       </c>
       <c r="N9" s="110" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>59</v>
@@ -44698,7 +44730,7 @@
         <v>197</v>
       </c>
       <c r="B10" s="264" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C10" s="297" t="s">
         <v>179</v>
@@ -44734,7 +44766,7 @@
         <v>46</v>
       </c>
       <c r="N10" s="110" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>59</v>
@@ -45046,7 +45078,7 @@
         <v>203</v>
       </c>
       <c r="B16" s="264" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C16" s="297" t="s">
         <v>179</v>
@@ -45183,7 +45215,7 @@
         <v>93</v>
       </c>
       <c r="I18" s="243" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J18" s="243" t="s">
         <v>71</v>
@@ -45265,7 +45297,7 @@
         <v>156</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R19" s="159" t="s">
         <v>113</v>
@@ -45354,7 +45386,7 @@
         <v>52</v>
       </c>
       <c r="H21" s="243" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I21" s="243" t="s">
         <v>74</v>
@@ -45430,7 +45462,7 @@
         <v>46</v>
       </c>
       <c r="N22" s="110" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>87</v>
@@ -45470,7 +45502,7 @@
         <v>52</v>
       </c>
       <c r="H23" s="243" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I23" s="243" t="s">
         <v>74</v>
@@ -45526,7 +45558,7 @@
         <v>52</v>
       </c>
       <c r="H24" s="243" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I24" s="243" t="s">
         <v>74</v>
@@ -45586,7 +45618,7 @@
         <v>87</v>
       </c>
       <c r="H25" s="243" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I25" s="243" t="s">
         <v>74</v>
@@ -45644,7 +45676,7 @@
         <v>87</v>
       </c>
       <c r="H26" s="243" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I26" s="243" t="s">
         <v>74</v>
@@ -45781,7 +45813,7 @@
         <v>87</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>140</v>
@@ -45800,7 +45832,7 @@
         <v>216</v>
       </c>
       <c r="B29" s="264" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C29" s="297" t="s">
         <v>179</v>
@@ -46219,7 +46251,7 @@
         <v>64</v>
       </c>
       <c r="G36" s="243" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H36" s="243" t="s">
         <v>90</v>
@@ -46273,7 +46305,7 @@
         <v>64</v>
       </c>
       <c r="G37" s="243" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H37" s="243" t="s">
         <v>90</v>
@@ -46331,7 +46363,7 @@
         <v>64</v>
       </c>
       <c r="G38" s="243" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H38" s="243" t="s">
         <v>90</v>
@@ -46539,7 +46571,7 @@
         <v>237</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>165</v>
@@ -46668,7 +46700,7 @@
         <v>44</v>
       </c>
       <c r="C3" s="251" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D3" s="252"/>
     </row>
@@ -46791,7 +46823,7 @@
         <v>147</v>
       </c>
       <c r="D19" s="257" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="2:4">
@@ -47895,7 +47927,7 @@
         <v>6</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E8" s="30" t="s">
         <v>45</v>
@@ -48459,7 +48491,7 @@
         <v>10</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E12" s="30" t="s">
         <v>45</v>
@@ -49467,7 +49499,7 @@
         <v>17</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E19" s="24" t="s">
         <v>49</v>
@@ -49755,7 +49787,7 @@
         <v>19</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E21" s="24" t="s">
         <v>49</v>
@@ -50644,7 +50676,7 @@
         <v>42</v>
       </c>
       <c r="AJ27" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="AK27" s="2">
         <f t="shared" si="18"/>
@@ -50694,7 +50726,7 @@
         <v>26</v>
       </c>
       <c r="D28" s="30" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E28" s="30" t="s">
         <v>49</v>
@@ -50956,7 +50988,7 @@
         <v>28</v>
       </c>
       <c r="D30" s="30" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E30" s="30" t="s">
         <v>45</v>
@@ -51170,7 +51202,7 @@
         <v>42</v>
       </c>
       <c r="AJ31" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="AK31" s="2">
         <f t="shared" si="18"/>
@@ -51694,7 +51726,7 @@
         <v>34</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E36" s="24" t="s">
         <v>45</v>
@@ -51872,7 +51904,7 @@
         <v>36</v>
       </c>
       <c r="D38" s="73" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E38" s="24" t="s">
         <v>49</v>
@@ -51907,7 +51939,7 @@
       <c r="U38" s="61"/>
       <c r="V38" s="193"/>
       <c r="X38" s="150" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y38" s="153">
         <f t="shared" si="0"/>

--- a/인천 2026 기록.xlsx
+++ b/인천 2026 기록.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://familyinter-my.sharepoint.com/personal/hwlee_familyinter_onmicrosoft_com/Documents/바탕 화면/프로젝트300/대시보드/인천 대시보드/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1110" documentId="11_54A2C5EF959CB4B30F95B27560762D485FE60CF6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6BDC7E4-95AC-44AF-A38B-1C2F08F079EC}"/>
+  <xr:revisionPtr revIDLastSave="2220" documentId="11_54A2C5EF959CB4B30F95B27560762D485FE60CF6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99F2A139-9441-4249-BA4E-BFDB0E68EB1A}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1770" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4961,6 +4961,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="기록표" displayName="기록표" ref="A42:E57" totalsRowShown="0" headerRowDxfId="84" headerRowBorderDxfId="83" tableBorderDxfId="82" totalsRowBorderDxfId="81">
   <tableColumns count="5">

--- a/인천 2026 기록.xlsx
+++ b/인천 2026 기록.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://familyinter-my.sharepoint.com/personal/hwlee_familyinter_onmicrosoft_com/Documents/바탕 화면/프로젝트300/대시보드/인천 대시보드/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2220" documentId="11_54A2C5EF959CB4B30F95B27560762D485FE60CF6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99F2A139-9441-4249-BA4E-BFDB0E68EB1A}"/>
+  <xr:revisionPtr revIDLastSave="4440" documentId="11_54A2C5EF959CB4B30F95B27560762D485FE60CF6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{753D7E44-B3FE-4FF3-8805-F66A7258E70A}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1770" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/인천 2026 기록.xlsx
+++ b/인천 2026 기록.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://familyinter-my.sharepoint.com/personal/hwlee_familyinter_onmicrosoft_com/Documents/바탕 화면/프로젝트300/대시보드/인천 대시보드/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4440" documentId="11_54A2C5EF959CB4B30F95B27560762D485FE60CF6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{753D7E44-B3FE-4FF3-8805-F66A7258E70A}"/>
+  <xr:revisionPtr revIDLastSave="1131" documentId="11_BF33D991949CD4390BF5506260E94D8B12D16660" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12AAEC6C-9FB8-4C53-A8DF-0C15E1CB99D4}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1770" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6054" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6070" uniqueCount="395">
   <si>
     <t>리그</t>
   </si>
@@ -294,6 +294,9 @@
     <t>신용준</t>
   </si>
   <si>
+    <t>인천</t>
+  </si>
+  <si>
     <t>최승구</t>
   </si>
   <si>
@@ -301,9 +304,6 @@
   </si>
   <si>
     <t>고형진</t>
-  </si>
-  <si>
-    <t>인천</t>
   </si>
   <si>
     <t>정치인</t>
@@ -4961,10 +4961,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="기록표" displayName="기록표" ref="A42:E57" totalsRowShown="0" headerRowDxfId="84" headerRowBorderDxfId="83" tableBorderDxfId="82" totalsRowBorderDxfId="81">
   <tableColumns count="5">
@@ -5597,11 +5593,11 @@
       </c>
       <c r="Y3" s="332">
         <f t="shared" ref="Y3:Y43" si="0">Z3+AA3</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z3" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X3)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA3" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X3)</f>
@@ -5621,11 +5617,11 @@
       </c>
       <c r="AE3" s="332">
         <f t="shared" ref="AE3:AE43" si="4">AF3+AG3</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF3" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X3)+Z3</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG3" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X3)+AA3</f>
@@ -5809,7 +5805,7 @@
       </c>
       <c r="Y4" s="332">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z4" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X4)</f>
@@ -5817,7 +5813,7 @@
       </c>
       <c r="AA4" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X4)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB4" s="333">
         <f t="shared" si="1"/>
@@ -5833,7 +5829,7 @@
       </c>
       <c r="AE4" s="332">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF4" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X4)+Z4</f>
@@ -5841,7 +5837,7 @@
       </c>
       <c r="AG4" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X4)+AA4</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH4" s="333">
         <f t="shared" si="5"/>
@@ -5860,7 +5856,7 @@
       </c>
       <c r="AN4" s="2">
         <f>SUM(AO4:AQ4)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO4" s="243">
         <f t="shared" si="8"/>
@@ -5868,7 +5864,7 @@
       </c>
       <c r="AP4" s="58">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ4" s="342">
         <f t="shared" si="8"/>
@@ -5876,11 +5872,11 @@
       </c>
       <c r="AR4" s="352">
         <f>AO4*3+AP4</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS4" s="23">
         <f>IFERROR(AO4/AN4,0)</f>
-        <v>0.35714285714285715</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AT4" s="2">
         <f>SUMIFS($G$3:$G$40,$A$3:$A$40,"K리그",$F$3:$F$40,$AM4)</f>
@@ -5896,15 +5892,15 @@
       </c>
       <c r="AW4" s="434">
         <f>IFERROR(AR4/AN4,0)</f>
-        <v>1.3571428571428572</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="AX4" s="434">
         <f>IFERROR(AT4/AN4,0)</f>
-        <v>1.3571428571428572</v>
+        <v>1.2666666666666666</v>
       </c>
       <c r="AY4" s="434">
         <f>IFERROR(AU4/AN4,0)</f>
-        <v>1.2142857142857142</v>
+        <v>1.1333333333333333</v>
       </c>
       <c r="BA4" s="464" t="s">
         <v>53</v>
@@ -6066,7 +6062,7 @@
       </c>
       <c r="AN5" s="337">
         <f>SUM(AN3:AN4)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO5" s="337">
         <f>SUM(AO3:AO4)</f>
@@ -6074,7 +6070,7 @@
       </c>
       <c r="AP5" s="337">
         <f>SUM(AP3:AP4)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ5" s="337">
         <f>SUM(AQ3:AQ4)</f>
@@ -6082,11 +6078,11 @@
       </c>
       <c r="AR5" s="337">
         <f>SUM(AR3:AR4)</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AS5" s="349">
         <f>IFERROR(AO5/AN5,0)</f>
-        <v>0.34482758620689657</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AT5" s="337">
         <f>SUM(AT3:AT4)</f>
@@ -6102,15 +6098,15 @@
       </c>
       <c r="AW5" s="435">
         <f>IFERROR(AR5/AN5,0)</f>
-        <v>1.3103448275862069</v>
+        <v>1.3</v>
       </c>
       <c r="AX5" s="435">
         <f>IFERROR(AT5/AN5,0)</f>
-        <v>1.2413793103448276</v>
+        <v>1.2</v>
       </c>
       <c r="AY5" s="435">
         <f>IFERROR(AU5/AN5,0)</f>
-        <v>1.1379310344827587</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="BA5" s="464" t="s">
         <v>58</v>
@@ -6410,7 +6406,7 @@
       </c>
       <c r="Y7" s="332">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Z7" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X7)</f>
@@ -6418,7 +6414,7 @@
       </c>
       <c r="AA7" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X7)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB7" s="333">
         <f t="shared" si="1"/>
@@ -6434,7 +6430,7 @@
       </c>
       <c r="AE7" s="332">
         <f t="shared" si="4"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF7" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X7)+Z7</f>
@@ -6442,7 +6438,7 @@
       </c>
       <c r="AG7" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X7)+AA7</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH7" s="333">
         <f t="shared" si="5"/>
@@ -6532,13 +6528,13 @@
         <v>369</v>
       </c>
       <c r="BK7" s="479">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BL7" s="479">
         <v>10</v>
       </c>
       <c r="BM7" s="479">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN7" s="479">
         <v>7</v>
@@ -6554,7 +6550,7 @@
         <v>8</v>
       </c>
       <c r="BR7" s="479">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:77">
@@ -6814,11 +6810,11 @@
       </c>
       <c r="Y9" s="332">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z9" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X9)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA9" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X9)</f>
@@ -6838,11 +6834,11 @@
       </c>
       <c r="AE9" s="332">
         <f t="shared" si="4"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF9" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X9)+Z9</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG9" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X9)+AA9</f>
@@ -7015,7 +7011,7 @@
       </c>
       <c r="Y10" s="332">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z10" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X10)</f>
@@ -7023,7 +7019,7 @@
       </c>
       <c r="AA10" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X10)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB10" s="333">
         <f t="shared" si="1"/>
@@ -7039,7 +7035,7 @@
       </c>
       <c r="AE10" s="332">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF10" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X10)+Z10</f>
@@ -7047,7 +7043,7 @@
       </c>
       <c r="AG10" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X10)+AA10</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH10" s="333">
         <f t="shared" si="5"/>
@@ -7130,36 +7126,36 @@
         <f t="shared" si="12"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="BI10" s="479">
+      <c r="BI10" s="471">
         <v>8</v>
       </c>
-      <c r="BJ10" s="479" t="s">
-        <v>355</v>
-      </c>
-      <c r="BK10" s="479">
+      <c r="BJ10" s="471" t="s">
+        <v>394</v>
+      </c>
+      <c r="BK10" s="471">
         <v>30</v>
       </c>
-      <c r="BL10" s="479">
+      <c r="BL10" s="471">
+        <v>10</v>
+      </c>
+      <c r="BM10" s="471">
         <v>9</v>
       </c>
-      <c r="BM10" s="479">
+      <c r="BN10" s="471">
         <v>11</v>
       </c>
-      <c r="BN10" s="479">
-        <v>10</v>
-      </c>
-      <c r="BO10" s="479">
-        <v>38</v>
-      </c>
-      <c r="BP10" s="479">
-        <v>47</v>
-      </c>
-      <c r="BQ10" s="479">
+      <c r="BO10" s="471">
+        <v>36</v>
+      </c>
+      <c r="BP10" s="471">
+        <v>33</v>
+      </c>
+      <c r="BQ10" s="471">
         <f>BO10-BP10</f>
-        <v>-9</v>
-      </c>
-      <c r="BR10" s="479">
-        <v>38</v>
+        <v>3</v>
+      </c>
+      <c r="BR10" s="471">
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:77">
@@ -7202,7 +7198,7 @@
       <c r="O11" s="270"/>
       <c r="P11" s="271"/>
       <c r="Q11" s="272" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R11" s="270"/>
       <c r="S11" s="270"/>
@@ -7212,15 +7208,15 @@
         <v>65</v>
       </c>
       <c r="X11" s="358" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Y11" s="332">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Z11" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X11)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA11" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X11)</f>
@@ -7240,11 +7236,11 @@
       </c>
       <c r="AE11" s="332">
         <f t="shared" si="4"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF11" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X11)+Z11</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG11" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X11)+AA11</f>
@@ -7305,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="BA11" s="464" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BB11" s="464">
         <f t="shared" si="9"/>
@@ -7331,35 +7327,35 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BI11" s="471">
+      <c r="BI11" s="479">
         <v>9</v>
       </c>
-      <c r="BJ11" s="471" t="s">
-        <v>394</v>
-      </c>
-      <c r="BK11" s="471">
-        <v>29</v>
-      </c>
-      <c r="BL11" s="471">
+      <c r="BJ11" s="479" t="s">
+        <v>355</v>
+      </c>
+      <c r="BK11" s="479">
+        <v>30</v>
+      </c>
+      <c r="BL11" s="479">
+        <v>9</v>
+      </c>
+      <c r="BM11" s="479">
+        <v>11</v>
+      </c>
+      <c r="BN11" s="479">
         <v>10</v>
       </c>
-      <c r="BM11" s="471">
-        <v>8</v>
-      </c>
-      <c r="BN11" s="471">
-        <v>11</v>
-      </c>
-      <c r="BO11" s="471">
-        <v>36</v>
-      </c>
-      <c r="BP11" s="471">
-        <v>33</v>
-      </c>
-      <c r="BQ11" s="471">
+      <c r="BO11" s="479">
+        <v>38</v>
+      </c>
+      <c r="BP11" s="479">
+        <v>47</v>
+      </c>
+      <c r="BQ11" s="479">
         <f>BO11-BP11</f>
-        <v>3</v>
-      </c>
-      <c r="BR11" s="471">
+        <v>-9</v>
+      </c>
+      <c r="BR11" s="479">
         <v>38</v>
       </c>
     </row>
@@ -7471,7 +7467,7 @@
       </c>
       <c r="AN12" s="89">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO12" s="243">
         <f t="shared" si="14"/>
@@ -7479,7 +7475,7 @@
       </c>
       <c r="AP12" s="243">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ12" s="351">
         <f t="shared" si="16"/>
@@ -7487,7 +7483,7 @@
       </c>
       <c r="AR12" s="352">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS12" s="23"/>
       <c r="AT12" s="2">
@@ -7604,7 +7600,7 @@
         <v>11404</v>
       </c>
       <c r="V13" s="274" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X13" s="327" t="s">
         <v>85</v>
@@ -7704,7 +7700,7 @@
       </c>
       <c r="BB13" s="464">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC13" s="243">
         <f t="shared" si="10"/>
@@ -7712,7 +7708,7 @@
       </c>
       <c r="BD13" s="465">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE13" s="342">
         <f t="shared" si="10"/>
@@ -7720,11 +7716,11 @@
       </c>
       <c r="BF13" s="89">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BG13" s="11">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BI13" s="479">
         <v>11</v>
@@ -7806,11 +7802,11 @@
       </c>
       <c r="Y14" s="332">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z14" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X14)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA14" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X14)</f>
@@ -7830,11 +7826,11 @@
       </c>
       <c r="AE14" s="332">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF14" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X14)+Z14</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG14" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X14)+AA14</f>
@@ -8102,7 +8098,7 @@
       </c>
       <c r="BB15" s="466">
         <f>SUM(BB3:BB14)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC15" s="243">
         <f>SUM(BC3:BC14)</f>
@@ -8110,7 +8106,7 @@
       </c>
       <c r="BD15" s="467">
         <f>SUM(BD3:BD14)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BE15" s="468">
         <f>SUM(BE3:BE14)</f>
@@ -8118,11 +8114,11 @@
       </c>
       <c r="BF15" s="89">
         <f>SUM(BF3:BF14)</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="BG15" s="11">
         <f t="shared" si="12"/>
-        <v>0.34482758620689657</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="BI15" s="476" t="s">
         <v>91</v>
@@ -8317,13 +8313,13 @@
         <v>71</v>
       </c>
       <c r="P17" s="368" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q17" s="363" t="s">
         <v>64</v>
       </c>
       <c r="R17" s="320" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S17" s="320" t="s">
         <v>59</v>
@@ -8875,11 +8871,11 @@
       </c>
       <c r="Y22" s="332">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z22" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X22)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA22" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X22)</f>
@@ -8899,11 +8895,11 @@
       </c>
       <c r="AE22" s="332">
         <f t="shared" si="4"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF22" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X22)+Z22</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG22" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X22)+AA22</f>
@@ -8970,7 +8966,7 @@
         <v>64</v>
       </c>
       <c r="S23" s="320" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T23" s="320"/>
       <c r="U23" s="400"/>
@@ -8982,11 +8978,11 @@
       </c>
       <c r="Y23" s="332">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z23" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X23)</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA23" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X23)</f>
@@ -9006,11 +9002,11 @@
       </c>
       <c r="AE23" s="332">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF23" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X23)+Z23</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG23" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X23)+AA23</f>
@@ -9048,9 +9044,15 @@
       <c r="F24" s="352" t="s">
         <v>346</v>
       </c>
-      <c r="G24" s="319"/>
-      <c r="H24" s="319"/>
-      <c r="I24" s="398"/>
+      <c r="G24" s="319">
+        <v>0</v>
+      </c>
+      <c r="H24" s="319">
+        <v>0</v>
+      </c>
+      <c r="I24" s="398" t="s">
+        <v>350</v>
+      </c>
       <c r="J24" s="399"/>
       <c r="K24" s="319"/>
       <c r="L24" s="360"/>
@@ -9062,18 +9064,22 @@
       <c r="R24" s="320"/>
       <c r="S24" s="320"/>
       <c r="T24" s="320"/>
-      <c r="U24" s="400"/>
-      <c r="V24" s="312"/>
+      <c r="U24" s="400">
+        <v>5274</v>
+      </c>
+      <c r="V24" s="312" t="s">
+        <v>86</v>
+      </c>
       <c r="X24" s="329" t="s">
         <v>64</v>
       </c>
       <c r="Y24" s="332">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z24" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X24)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA24" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X24)</f>
@@ -9093,11 +9099,11 @@
       </c>
       <c r="AE24" s="332">
         <f t="shared" si="4"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF24" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X24)+Z24</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG24" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X24)+AA24</f>
@@ -9166,7 +9172,7 @@
         <v>76</v>
       </c>
       <c r="X25" s="329" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y25" s="332">
         <f t="shared" si="0"/>
@@ -9553,7 +9559,7 @@
       <c r="T29" s="270"/>
       <c r="U29" s="273"/>
       <c r="V29" s="274" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X29" s="329" t="s">
         <v>101</v>
@@ -9861,11 +9867,11 @@
       </c>
       <c r="Y32" s="332">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z32" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X32)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA32" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X32)</f>
@@ -9885,11 +9891,11 @@
       </c>
       <c r="AE32" s="332">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF32" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X32)+Z32</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG32" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X32)+AA32</f>
@@ -9948,11 +9954,11 @@
       </c>
       <c r="Y33" s="332">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z33" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X33)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA33" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X33)</f>
@@ -9972,11 +9978,11 @@
       </c>
       <c r="AE33" s="332">
         <f t="shared" si="4"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF33" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X33)+Z33</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG33" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X33)+AA33</f>
@@ -10614,11 +10620,11 @@
       </c>
       <c r="Y41" s="332">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z41" s="474">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X41)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA41" s="474">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X41)</f>
@@ -10638,11 +10644,11 @@
       </c>
       <c r="AE41" s="475">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF41" s="475">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X41)+Z41</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG41" s="475">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X41)+AA41</f>
@@ -10674,11 +10680,11 @@
       </c>
       <c r="Y42" s="332">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z42" s="474">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X42)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA42" s="474">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X42)</f>
@@ -10698,11 +10704,11 @@
       </c>
       <c r="AE42" s="475">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF42" s="475">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X42)+Z42</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG42" s="475">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X42)+AA42</f>
@@ -10804,15 +10810,15 @@
       </c>
       <c r="N44" s="2">
         <f>COUNT(U3:U40)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O44" s="96">
         <f>SUMIFS(U3:U41,A3:A41,M44)</f>
-        <v>147986</v>
+        <v>153260</v>
       </c>
       <c r="P44" s="96">
         <f>O44/N44</f>
-        <v>9865.7333333333336</v>
+        <v>9578.75</v>
       </c>
       <c r="Q44" s="136">
         <v>19</v>
@@ -10825,7 +10831,7 @@
       </c>
       <c r="T44" s="165">
         <f>(P44-S44)/S44</f>
-        <v>-3.0279390108051914E-2</v>
+        <v>-5.848749624939209E-2</v>
       </c>
     </row>
     <row r="45" spans="1:36">
@@ -35323,7 +35329,7 @@
         <v>46</v>
       </c>
       <c r="N2" s="110" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>98</v>
@@ -35402,7 +35408,7 @@
         <v>59</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>85</v>
@@ -35478,7 +35484,7 @@
         <v>59</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
@@ -35550,13 +35556,13 @@
         <v>59</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R5" s="159" t="s">
         <v>66</v>
@@ -35628,10 +35634,10 @@
         <v>71</v>
       </c>
       <c r="O6" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="P6" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="Q6" s="159" t="s">
         <v>66</v>
@@ -35704,7 +35710,7 @@
         <v>71</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>83</v>
@@ -35785,7 +35791,7 @@
         <v>71</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q8" s="159" t="s">
         <v>66</v>
@@ -35826,7 +35832,7 @@
         <v>71</v>
       </c>
       <c r="K9" s="243" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L9" s="243" t="s">
         <v>66</v>
@@ -35869,7 +35875,7 @@
         <v>89</v>
       </c>
       <c r="F10" s="243" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G10" s="243" t="s">
         <v>98</v>
@@ -35890,7 +35896,7 @@
         <v>66</v>
       </c>
       <c r="M10" s="298" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N10" s="110" t="s">
         <v>64</v>
@@ -35945,7 +35951,7 @@
         <v>71</v>
       </c>
       <c r="L11" s="243" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M11" s="298" t="s">
         <v>46</v>
@@ -35954,7 +35960,7 @@
         <v>97</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>85</v>
@@ -36000,7 +36006,7 @@
         <v>59</v>
       </c>
       <c r="K12" s="243" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L12" s="243" t="s">
         <v>66</v>
@@ -36018,7 +36024,7 @@
         <v>99</v>
       </c>
       <c r="Q12" s="159" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R12" s="159" t="s">
         <v>113</v>
@@ -36073,10 +36079,10 @@
         <v>59</v>
       </c>
       <c r="P13" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q13" s="159" t="s">
         <v>80</v>
-      </c>
-      <c r="Q13" s="159" t="s">
-        <v>79</v>
       </c>
       <c r="R13" s="159" t="s">
         <v>106</v>
@@ -36116,7 +36122,7 @@
         <v>59</v>
       </c>
       <c r="K14" s="243" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L14" s="243" t="s">
         <v>66</v>
@@ -36159,7 +36165,7 @@
         <v>96</v>
       </c>
       <c r="F15" s="243" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G15" s="243" t="s">
         <v>64</v>
@@ -36195,7 +36201,7 @@
         <v>74</v>
       </c>
       <c r="R15" s="159" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S15" s="51"/>
       <c r="T15" s="1"/>
@@ -36235,13 +36241,13 @@
         <v>71</v>
       </c>
       <c r="L16" s="243" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M16" s="298" t="s">
         <v>66</v>
       </c>
       <c r="N16" s="110" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>92</v>
@@ -36293,13 +36299,13 @@
         <v>71</v>
       </c>
       <c r="L17" s="243" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M17" s="298" t="s">
         <v>66</v>
       </c>
       <c r="N17" s="110" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>46</v>
@@ -36351,13 +36357,13 @@
         <v>71</v>
       </c>
       <c r="L18" s="243" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M18" s="298" t="s">
         <v>66</v>
       </c>
       <c r="N18" s="110" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>46</v>
@@ -36407,13 +36413,13 @@
         <v>71</v>
       </c>
       <c r="L19" s="243" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M19" s="298" t="s">
         <v>66</v>
       </c>
       <c r="N19" s="110" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>46</v>
@@ -36465,13 +36471,13 @@
         <v>71</v>
       </c>
       <c r="L20" s="243" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M20" s="298" t="s">
         <v>66</v>
       </c>
       <c r="N20" s="110" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>46</v>
@@ -36523,13 +36529,13 @@
         <v>71</v>
       </c>
       <c r="L21" s="243" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M21" s="298" t="s">
         <v>66</v>
       </c>
       <c r="N21" s="110" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>46</v>
@@ -36584,7 +36590,7 @@
         <v>46</v>
       </c>
       <c r="M22" s="298" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N22" s="110" t="s">
         <v>66</v>
@@ -36596,7 +36602,7 @@
         <v>94</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R22" s="159" t="s">
         <v>93</v>
@@ -36611,20 +36617,48 @@
       <c r="B23" s="264" t="s">
         <v>369</v>
       </c>
-      <c r="C23" s="297"/>
-      <c r="D23" s="243"/>
-      <c r="E23" s="243"/>
-      <c r="F23" s="243"/>
-      <c r="G23" s="243"/>
-      <c r="H23" s="243"/>
-      <c r="I23" s="243"/>
-      <c r="J23" s="243"/>
-      <c r="K23" s="243"/>
-      <c r="L23" s="243"/>
-      <c r="M23" s="298"/>
-      <c r="N23" s="110"/>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
+      <c r="C23" s="297" t="s">
+        <v>106</v>
+      </c>
+      <c r="D23" s="243" t="s">
+        <v>89</v>
+      </c>
+      <c r="E23" s="243" t="s">
+        <v>105</v>
+      </c>
+      <c r="F23" s="243" t="s">
+        <v>64</v>
+      </c>
+      <c r="G23" s="243" t="s">
+        <v>52</v>
+      </c>
+      <c r="H23" s="243" t="s">
+        <v>74</v>
+      </c>
+      <c r="I23" s="243" t="s">
+        <v>87</v>
+      </c>
+      <c r="J23" s="243" t="s">
+        <v>102</v>
+      </c>
+      <c r="K23" s="243" t="s">
+        <v>81</v>
+      </c>
+      <c r="L23" s="243" t="s">
+        <v>46</v>
+      </c>
+      <c r="M23" s="298" t="s">
+        <v>121</v>
+      </c>
+      <c r="N23" s="110" t="s">
+        <v>50</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="Q23" s="2"/>
       <c r="R23" s="159"/>
       <c r="S23" s="51"/>
@@ -36665,7 +36699,7 @@
         <v>51</v>
       </c>
       <c r="L24" s="243" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M24" s="298" t="s">
         <v>66</v>
@@ -36674,7 +36708,7 @@
         <v>46</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>94</v>
@@ -36723,13 +36757,13 @@
         <v>87</v>
       </c>
       <c r="L25" s="243" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M25" s="298" t="s">
         <v>66</v>
       </c>
       <c r="N25" s="110" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>46</v>
@@ -36763,7 +36797,7 @@
         <v>97</v>
       </c>
       <c r="F26" s="243" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G26" s="243" t="s">
         <v>64</v>
@@ -36787,7 +36821,7 @@
         <v>66</v>
       </c>
       <c r="N26" s="110" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>46</v>
@@ -36842,7 +36876,7 @@
         <v>46</v>
       </c>
       <c r="M27" s="298" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N27" s="110" t="s">
         <v>87</v>
@@ -36898,7 +36932,7 @@
         <v>46</v>
       </c>
       <c r="M28" s="298" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N28" s="110" t="s">
         <v>96</v>
@@ -36962,7 +36996,7 @@
         <v>71</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>121</v>
@@ -36971,7 +37005,7 @@
         <v>87</v>
       </c>
       <c r="R29" s="159" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S29" s="51"/>
       <c r="T29" s="1"/>
@@ -37014,7 +37048,7 @@
         <v>46</v>
       </c>
       <c r="M30" s="298" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N30" s="110" t="s">
         <v>59</v>
@@ -37064,7 +37098,7 @@
         <v>102</v>
       </c>
       <c r="K31" s="243" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L31" s="243" t="s">
         <v>46</v>
@@ -37076,7 +37110,7 @@
         <v>71</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>83</v>
@@ -41545,7 +41579,7 @@
       <c r="O23" s="58"/>
       <c r="P23" s="59"/>
       <c r="Q23" s="143" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R23" s="58"/>
       <c r="S23" s="58"/>
@@ -42299,7 +42333,7 @@
         <v>65</v>
       </c>
       <c r="X30" s="329" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y30" s="297">
         <f t="shared" si="0"/>
@@ -44067,7 +44101,7 @@
         <v>64</v>
       </c>
       <c r="G2" s="243" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H2" s="243" t="s">
         <v>74</v>
@@ -44177,7 +44211,7 @@
         <v>64</v>
       </c>
       <c r="G3" s="243" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H3" s="243" t="s">
         <v>74</v>
@@ -44289,7 +44323,7 @@
         <v>64</v>
       </c>
       <c r="G4" s="243" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H4" s="243" t="s">
         <v>74</v>
@@ -44333,7 +44367,7 @@
         <v>108</v>
       </c>
       <c r="X4" s="243" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y4" s="243" t="s">
         <v>178</v>
@@ -44399,7 +44433,7 @@
         <v>64</v>
       </c>
       <c r="G5" s="243" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H5" s="243" t="s">
         <v>74</v>
@@ -44477,7 +44511,7 @@
         <v>64</v>
       </c>
       <c r="G6" s="243" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H6" s="243" t="s">
         <v>74</v>
@@ -44576,7 +44610,7 @@
         <v>46</v>
       </c>
       <c r="N7" s="110" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>71</v>
@@ -44633,7 +44667,7 @@
         <v>64</v>
       </c>
       <c r="G8" s="243" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H8" s="243" t="s">
         <v>93</v>
@@ -44712,7 +44746,7 @@
         <v>46</v>
       </c>
       <c r="N9" s="110" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>59</v>
@@ -44770,7 +44804,7 @@
         <v>46</v>
       </c>
       <c r="N10" s="110" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>59</v>
@@ -45219,7 +45253,7 @@
         <v>93</v>
       </c>
       <c r="I18" s="243" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J18" s="243" t="s">
         <v>71</v>
@@ -45301,7 +45335,7 @@
         <v>156</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R19" s="159" t="s">
         <v>113</v>
@@ -45390,7 +45424,7 @@
         <v>52</v>
       </c>
       <c r="H21" s="243" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I21" s="243" t="s">
         <v>74</v>
@@ -45466,7 +45500,7 @@
         <v>46</v>
       </c>
       <c r="N22" s="110" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>87</v>
@@ -45506,7 +45540,7 @@
         <v>52</v>
       </c>
       <c r="H23" s="243" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I23" s="243" t="s">
         <v>74</v>
@@ -45562,7 +45596,7 @@
         <v>52</v>
       </c>
       <c r="H24" s="243" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I24" s="243" t="s">
         <v>74</v>
@@ -45622,7 +45656,7 @@
         <v>87</v>
       </c>
       <c r="H25" s="243" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I25" s="243" t="s">
         <v>74</v>
@@ -45680,7 +45714,7 @@
         <v>87</v>
       </c>
       <c r="H26" s="243" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I26" s="243" t="s">
         <v>74</v>
@@ -45817,7 +45851,7 @@
         <v>87</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>140</v>
@@ -46255,7 +46289,7 @@
         <v>64</v>
       </c>
       <c r="G36" s="243" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H36" s="243" t="s">
         <v>90</v>
@@ -46309,7 +46343,7 @@
         <v>64</v>
       </c>
       <c r="G37" s="243" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H37" s="243" t="s">
         <v>90</v>
@@ -46367,7 +46401,7 @@
         <v>64</v>
       </c>
       <c r="G38" s="243" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H38" s="243" t="s">
         <v>90</v>
@@ -46575,7 +46609,7 @@
         <v>237</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>165</v>
@@ -46704,7 +46738,7 @@
         <v>44</v>
       </c>
       <c r="C3" s="251" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D3" s="252"/>
     </row>
@@ -51943,7 +51977,7 @@
       <c r="U38" s="61"/>
       <c r="V38" s="193"/>
       <c r="X38" s="150" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y38" s="153">
         <f t="shared" si="0"/>

--- a/인천 2026 기록.xlsx
+++ b/인천 2026 기록.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://familyinter-my.sharepoint.com/personal/hwlee_familyinter_onmicrosoft_com/Documents/바탕 화면/프로젝트300/대시보드/인천 대시보드/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1131" documentId="11_BF33D991949CD4390BF5506260E94D8B12D16660" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12AAEC6C-9FB8-4C53-A8DF-0C15E1CB99D4}"/>
+  <xr:revisionPtr revIDLastSave="2262" documentId="11_BF33D991949CD4390BF5506260E94D8B12D16660" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E00CB6C5-1B7C-49EA-9DC4-37C1FAE7E9EE}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1770" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4961,6 +4961,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="기록표" displayName="기록표" ref="A42:E57" totalsRowShown="0" headerRowDxfId="84" headerRowBorderDxfId="83" tableBorderDxfId="82" totalsRowBorderDxfId="81">
   <tableColumns count="5">

--- a/인천 2026 기록.xlsx
+++ b/인천 2026 기록.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://familyinter-my.sharepoint.com/personal/hwlee_familyinter_onmicrosoft_com/Documents/바탕 화면/프로젝트300/대시보드/인천 대시보드/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2262" documentId="11_BF33D991949CD4390BF5506260E94D8B12D16660" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E00CB6C5-1B7C-49EA-9DC4-37C1FAE7E9EE}"/>
+  <xr:revisionPtr revIDLastSave="1159" documentId="11_BC30CAD5959CD43F2C1D107F60E94D8BC2537F23" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80DA0A5B-909E-47B6-A93C-EBB181BA06E3}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1770" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6070" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6093" uniqueCount="395">
   <si>
     <t>리그</t>
   </si>
@@ -240,7 +240,7 @@
     <t>총합</t>
   </si>
   <si>
-    <t>제주</t>
+    <t>강원</t>
   </si>
   <si>
     <t>수</t>
@@ -261,7 +261,7 @@
     <t>팀명</t>
   </si>
   <si>
-    <t>전북</t>
+    <t>제주</t>
   </si>
   <si>
     <t>안양</t>
@@ -273,7 +273,7 @@
     <t>제르소</t>
   </si>
   <si>
-    <t>강원</t>
+    <t>전북</t>
   </si>
   <si>
     <t>김천</t>
@@ -288,13 +288,13 @@
     <t>송민석</t>
   </si>
   <si>
+    <t>인천</t>
+  </si>
+  <si>
     <t>부천</t>
   </si>
   <si>
     <t>신용준</t>
-  </si>
-  <si>
-    <t>인천</t>
   </si>
   <si>
     <t>최승구</t>
@@ -375,6 +375,9 @@
     <t>김연수</t>
   </si>
   <si>
+    <t>이민혁</t>
+  </si>
+  <si>
     <t>김동헌</t>
   </si>
   <si>
@@ -418,9 +421,6 @@
   </si>
   <si>
     <t>2025시즌</t>
-  </si>
-  <si>
-    <t>이민혁</t>
   </si>
   <si>
     <t>경기수</t>
@@ -1291,7 +1291,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>K리그1 2026 리그순위   (2026-09-20 - 30R 종료)</t>
+    <t>K리그1 2026 리그순위   (2026-10-11 - 31R 종료)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -4961,10 +4961,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="기록표" displayName="기록표" ref="A42:E57" totalsRowShown="0" headerRowDxfId="84" headerRowBorderDxfId="83" tableBorderDxfId="82" totalsRowBorderDxfId="81">
   <tableColumns count="5">
@@ -5597,11 +5593,11 @@
       </c>
       <c r="Y3" s="332">
         <f t="shared" ref="Y3:Y43" si="0">Z3+AA3</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z3" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X3)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA3" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X3)</f>
@@ -5609,7 +5605,7 @@
       </c>
       <c r="AB3" s="333">
         <f t="shared" ref="AB3:AB43" si="1">COUNTIF($M$3:$P$40,$X3)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC3" s="334">
         <f t="shared" ref="AC3:AC43" si="2">COUNTIF($Q$3:$T$40,$X3)</f>
@@ -5617,15 +5613,15 @@
       </c>
       <c r="AD3" s="335">
         <f t="shared" ref="AD3:AD43" si="3">AB3+AC3</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE3" s="332">
         <f t="shared" ref="AE3:AE43" si="4">AF3+AG3</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF3" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X3)+Z3</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG3" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X3)+AA3</f>
@@ -5633,7 +5629,7 @@
       </c>
       <c r="AH3" s="333">
         <f t="shared" ref="AH3:AH43" si="5">COUNTIF($M$3:$P$41,$X3)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI3" s="334">
         <f t="shared" ref="AI3:AI43" si="6">COUNTIF($Q$3:$T$41,$X3)</f>
@@ -5641,18 +5637,18 @@
       </c>
       <c r="AJ3" s="335">
         <f t="shared" ref="AJ3:AJ43" si="7">AH3+AI3</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM3" s="2" t="s">
         <v>45</v>
       </c>
       <c r="AN3" s="2">
         <f>SUM(AO3:AQ3)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO3" s="243">
         <f t="shared" ref="AO3:AQ4" si="8">COUNTIFS($A$3:$A$40,"K리그",$F$3:$F$40,$AM3,$I$3:$I$40,AO$2)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP3" s="58">
         <f t="shared" si="8"/>
@@ -5664,15 +5660,15 @@
       </c>
       <c r="AR3" s="352">
         <f>AO3*3+AP3</f>
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AS3" s="10">
         <f>IFERROR(AO3/AN3,0)</f>
-        <v>0.33333333333333331</v>
+        <v>0.375</v>
       </c>
       <c r="AT3" s="2">
         <f>SUMIFS($G$3:$G$40,$A$3:$A$40,"K리그",$F$3:$F$40,$AM3)</f>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AU3" s="2">
         <f>SUMIFS($H$3:$H$40,$A$3:$A$40,"K리그",$F$3:$F$40,$AM3)</f>
@@ -5680,19 +5676,19 @@
       </c>
       <c r="AV3" s="2">
         <f>AT3-AU3</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AW3" s="434">
         <f>IFERROR(AR3/AN3,0)</f>
-        <v>1.2666666666666666</v>
+        <v>1.375</v>
       </c>
       <c r="AX3" s="434">
         <f>IFERROR(AT3/AN3,0)</f>
-        <v>1.1333333333333333</v>
+        <v>1.25</v>
       </c>
       <c r="AY3" s="434">
         <f>IFERROR(AU3/AN3,0)</f>
-        <v>1.0666666666666667</v>
+        <v>1</v>
       </c>
       <c r="BA3" s="464" t="s">
         <v>47</v>
@@ -5728,10 +5724,10 @@
         <v>341</v>
       </c>
       <c r="BK3" s="469">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BL3" s="469">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BM3" s="469">
         <v>5</v>
@@ -5740,17 +5736,17 @@
         <v>6</v>
       </c>
       <c r="BO3" s="469">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="BP3" s="469">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BQ3" s="469">
         <f>BO3-BP3</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BR3" s="469">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:77">
@@ -5809,7 +5805,7 @@
       </c>
       <c r="Y4" s="332">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z4" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X4)</f>
@@ -5817,7 +5813,7 @@
       </c>
       <c r="AA4" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X4)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB4" s="333">
         <f t="shared" si="1"/>
@@ -5833,7 +5829,7 @@
       </c>
       <c r="AE4" s="332">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF4" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X4)+Z4</f>
@@ -5841,7 +5837,7 @@
       </c>
       <c r="AG4" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X4)+AA4</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH4" s="333">
         <f t="shared" si="5"/>
@@ -5940,7 +5936,7 @@
         <v>360</v>
       </c>
       <c r="BK4" s="470">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BL4" s="470">
         <v>14</v>
@@ -5949,17 +5945,17 @@
         <v>5</v>
       </c>
       <c r="BN4" s="470">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BO4" s="470">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="BP4" s="470">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BQ4" s="470">
         <f>BO4-BP4</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BR4" s="470">
         <v>47</v>
@@ -6015,7 +6011,7 @@
       </c>
       <c r="Y5" s="332">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z5" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X5)</f>
@@ -6023,7 +6019,7 @@
       </c>
       <c r="AA5" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X5)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AB5" s="333">
         <f t="shared" si="1"/>
@@ -6039,7 +6035,7 @@
       </c>
       <c r="AE5" s="332">
         <f t="shared" si="4"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF5" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X5)+Z5</f>
@@ -6047,7 +6043,7 @@
       </c>
       <c r="AG5" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X5)+AA5</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH5" s="333">
         <f t="shared" si="5"/>
@@ -6066,11 +6062,11 @@
       </c>
       <c r="AN5" s="337">
         <f>SUM(AN3:AN4)</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AO5" s="337">
         <f>SUM(AO3:AO4)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP5" s="337">
         <f>SUM(AP3:AP4)</f>
@@ -6082,15 +6078,15 @@
       </c>
       <c r="AR5" s="337">
         <f>SUM(AR3:AR4)</f>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AS5" s="349">
         <f>IFERROR(AO5/AN5,0)</f>
-        <v>0.33333333333333331</v>
+        <v>0.35483870967741937</v>
       </c>
       <c r="AT5" s="337">
         <f>SUM(AT3:AT4)</f>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="AU5" s="337">
         <f>SUM(AU3:AU4)</f>
@@ -6098,19 +6094,19 @@
       </c>
       <c r="AV5" s="337">
         <f>SUM(AV3:AV4)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AW5" s="435">
         <f>IFERROR(AR5/AN5,0)</f>
-        <v>1.3</v>
+        <v>1.3548387096774193</v>
       </c>
       <c r="AX5" s="435">
         <f>IFERROR(AT5/AN5,0)</f>
-        <v>1.2</v>
+        <v>1.2580645161290323</v>
       </c>
       <c r="AY5" s="435">
         <f>IFERROR(AU5/AN5,0)</f>
-        <v>1.1000000000000001</v>
+        <v>1.064516129032258</v>
       </c>
       <c r="BA5" s="464" t="s">
         <v>58</v>
@@ -6143,29 +6139,29 @@
         <v>3</v>
       </c>
       <c r="BJ5" s="470" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="BK5" s="470">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BL5" s="470">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BM5" s="470">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BN5" s="470">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BO5" s="470">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="BP5" s="470">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BQ5" s="470">
         <f>BO5-BP5</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BR5" s="470">
         <v>46</v>
@@ -6225,7 +6221,7 @@
       </c>
       <c r="Y6" s="332">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z6" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X6)</f>
@@ -6233,7 +6229,7 @@
       </c>
       <c r="AA6" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X6)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AB6" s="333">
         <f t="shared" si="1"/>
@@ -6249,7 +6245,7 @@
       </c>
       <c r="AE6" s="332">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF6" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X6)+Z6</f>
@@ -6257,7 +6253,7 @@
       </c>
       <c r="AG6" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X6)+AA6</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH6" s="333">
         <f t="shared" si="5"/>
@@ -6332,32 +6328,32 @@
         <v>4</v>
       </c>
       <c r="BJ6" s="479" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="BK6" s="479">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BL6" s="479">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BM6" s="479">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BN6" s="479">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BO6" s="479">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BP6" s="479">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="BQ6" s="479">
         <f>BO6-BP6</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="BR6" s="479">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:77">
@@ -6410,7 +6406,7 @@
       </c>
       <c r="Y7" s="332">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Z7" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X7)</f>
@@ -6418,7 +6414,7 @@
       </c>
       <c r="AA7" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X7)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AB7" s="333">
         <f t="shared" si="1"/>
@@ -6434,7 +6430,7 @@
       </c>
       <c r="AE7" s="332">
         <f t="shared" si="4"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AF7" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X7)+Z7</f>
@@ -6442,7 +6438,7 @@
       </c>
       <c r="AG7" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X7)+AA7</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH7" s="333">
         <f t="shared" si="5"/>
@@ -6460,7 +6456,7 @@
         <v>42</v>
       </c>
       <c r="AM7" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="AN7" s="89">
         <f t="shared" ref="AN7:AN17" si="13">SUM(AO7:AQ7)</f>
@@ -6529,32 +6525,32 @@
         <v>5</v>
       </c>
       <c r="BJ7" s="479" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="BK7" s="479">
+        <v>31</v>
+      </c>
+      <c r="BL7" s="479">
+        <v>11</v>
+      </c>
+      <c r="BM7" s="479">
+        <v>11</v>
+      </c>
+      <c r="BN7" s="479">
+        <v>9</v>
+      </c>
+      <c r="BO7" s="479">
+        <v>39</v>
+      </c>
+      <c r="BP7" s="479">
         <v>30</v>
-      </c>
-      <c r="BL7" s="479">
-        <v>10</v>
-      </c>
-      <c r="BM7" s="479">
-        <v>13</v>
-      </c>
-      <c r="BN7" s="479">
-        <v>7</v>
-      </c>
-      <c r="BO7" s="479">
-        <v>36</v>
-      </c>
-      <c r="BP7" s="479">
-        <v>28</v>
       </c>
       <c r="BQ7" s="479">
         <f>BO7-BP7</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BR7" s="479">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:77">
@@ -6613,7 +6609,7 @@
       </c>
       <c r="Y8" s="332">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Z8" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X8)</f>
@@ -6621,7 +6617,7 @@
       </c>
       <c r="AA8" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X8)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB8" s="333">
         <f t="shared" si="1"/>
@@ -6637,7 +6633,7 @@
       </c>
       <c r="AE8" s="332">
         <f t="shared" si="4"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF8" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X8)+Z8</f>
@@ -6645,7 +6641,7 @@
       </c>
       <c r="AG8" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X8)+AA8</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH8" s="333">
         <f t="shared" si="5"/>
@@ -6735,10 +6731,10 @@
         <v>353</v>
       </c>
       <c r="BK8" s="479">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BL8" s="479">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BM8" s="479">
         <v>10</v>
@@ -6747,17 +6743,17 @@
         <v>10</v>
       </c>
       <c r="BO8" s="479">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BP8" s="479">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BQ8" s="479">
         <f>BO8-BP8</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BR8" s="479">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:77">
@@ -6814,11 +6810,11 @@
       </c>
       <c r="Y9" s="332">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z9" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X9)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA9" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X9)</f>
@@ -6838,11 +6834,11 @@
       </c>
       <c r="AE9" s="332">
         <f t="shared" si="4"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF9" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X9)+Z9</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG9" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X9)+AA9</f>
@@ -6929,36 +6925,36 @@
         <f t="shared" si="12"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="BI9" s="479">
+      <c r="BI9" s="471">
         <v>7</v>
       </c>
-      <c r="BJ9" s="479" t="s">
-        <v>349</v>
-      </c>
-      <c r="BK9" s="479">
-        <v>30</v>
-      </c>
-      <c r="BL9" s="479">
+      <c r="BJ9" s="471" t="s">
+        <v>394</v>
+      </c>
+      <c r="BK9" s="471">
+        <v>31</v>
+      </c>
+      <c r="BL9" s="471">
         <v>11</v>
       </c>
-      <c r="BM9" s="479">
-        <v>7</v>
-      </c>
-      <c r="BN9" s="479">
-        <v>12</v>
-      </c>
-      <c r="BO9" s="479">
-        <v>28</v>
-      </c>
-      <c r="BP9" s="479">
-        <v>34</v>
-      </c>
-      <c r="BQ9" s="479">
+      <c r="BM9" s="471">
+        <v>9</v>
+      </c>
+      <c r="BN9" s="471">
+        <v>11</v>
+      </c>
+      <c r="BO9" s="471">
+        <v>39</v>
+      </c>
+      <c r="BP9" s="471">
+        <v>33</v>
+      </c>
+      <c r="BQ9" s="471">
         <f>BO9-BP9</f>
-        <v>-6</v>
-      </c>
-      <c r="BR9" s="479">
-        <v>40</v>
+        <v>6</v>
+      </c>
+      <c r="BR9" s="471">
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:77">
@@ -7008,7 +7004,7 @@
       <c r="T10" s="270"/>
       <c r="U10" s="273"/>
       <c r="V10" s="274" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X10" s="327" t="s">
         <v>50</v>
@@ -7104,7 +7100,7 @@
         <v>-3</v>
       </c>
       <c r="BA10" s="464" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BB10" s="464">
         <f t="shared" si="9"/>
@@ -7130,36 +7126,36 @@
         <f t="shared" si="12"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="BI10" s="471">
+      <c r="BI10" s="479">
         <v>8</v>
       </c>
-      <c r="BJ10" s="471" t="s">
-        <v>394</v>
-      </c>
-      <c r="BK10" s="471">
-        <v>30</v>
-      </c>
-      <c r="BL10" s="471">
+      <c r="BJ10" s="479" t="s">
+        <v>355</v>
+      </c>
+      <c r="BK10" s="479">
+        <v>31</v>
+      </c>
+      <c r="BL10" s="479">
         <v>10</v>
       </c>
-      <c r="BM10" s="471">
-        <v>9</v>
-      </c>
-      <c r="BN10" s="471">
+      <c r="BM10" s="479">
         <v>11</v>
       </c>
-      <c r="BO10" s="471">
-        <v>36</v>
-      </c>
-      <c r="BP10" s="471">
-        <v>33</v>
-      </c>
-      <c r="BQ10" s="471">
+      <c r="BN10" s="479">
+        <v>10</v>
+      </c>
+      <c r="BO10" s="479">
+        <v>39</v>
+      </c>
+      <c r="BP10" s="479">
+        <v>47</v>
+      </c>
+      <c r="BQ10" s="479">
         <f>BO10-BP10</f>
-        <v>3</v>
-      </c>
-      <c r="BR10" s="471">
-        <v>39</v>
+        <v>-8</v>
+      </c>
+      <c r="BR10" s="479">
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:77">
@@ -7216,11 +7212,11 @@
       </c>
       <c r="Y11" s="332">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Z11" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X11)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA11" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X11)</f>
@@ -7228,7 +7224,7 @@
       </c>
       <c r="AB11" s="333">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC11" s="334">
         <f t="shared" si="2"/>
@@ -7236,15 +7232,15 @@
       </c>
       <c r="AD11" s="335">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE11" s="332">
         <f t="shared" si="4"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AF11" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X11)+Z11</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG11" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X11)+AA11</f>
@@ -7252,7 +7248,7 @@
       </c>
       <c r="AH11" s="333">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI11" s="334">
         <f t="shared" si="6"/>
@@ -7260,7 +7256,7 @@
       </c>
       <c r="AJ11" s="335">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL11" s="2" t="s">
         <v>42</v>
@@ -7270,11 +7266,11 @@
       </c>
       <c r="AN11" s="89">
         <f t="shared" si="13"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO11" s="243">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP11" s="243">
         <f t="shared" si="15"/>
@@ -7286,15 +7282,15 @@
       </c>
       <c r="AR11" s="352">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AS11" s="23">
         <f>AO11/AN11</f>
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AT11" s="2">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AU11" s="2">
         <f t="shared" si="19"/>
@@ -7302,18 +7298,18 @@
       </c>
       <c r="AV11" s="2">
         <f t="shared" si="20"/>
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BA11" s="464" t="s">
         <v>82</v>
       </c>
       <c r="BB11" s="464">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC11" s="243">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD11" s="465">
         <f t="shared" si="10"/>
@@ -7325,42 +7321,42 @@
       </c>
       <c r="BF11" s="89">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BG11" s="11">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="BI11" s="479">
         <v>9</v>
       </c>
       <c r="BJ11" s="479" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="BK11" s="479">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BL11" s="479">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BM11" s="479">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BN11" s="479">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BO11" s="479">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BP11" s="479">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="BQ11" s="479">
         <f>BO11-BP11</f>
         <v>-9</v>
       </c>
       <c r="BR11" s="479">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:77">
@@ -7467,7 +7463,7 @@
         <v>42</v>
       </c>
       <c r="AM12" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="AN12" s="89">
         <f t="shared" si="13"/>
@@ -7536,7 +7532,7 @@
         <v>358</v>
       </c>
       <c r="BK12" s="479">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BL12" s="479">
         <v>5</v>
@@ -7545,17 +7541,17 @@
         <v>18</v>
       </c>
       <c r="BN12" s="479">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BO12" s="479">
         <v>30</v>
       </c>
       <c r="BP12" s="479">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="BQ12" s="479">
         <f>BO12-BP12</f>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="BR12" s="479">
         <v>33</v>
@@ -7733,7 +7729,7 @@
         <v>362</v>
       </c>
       <c r="BK13" s="479">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BL13" s="479">
         <v>7</v>
@@ -7742,17 +7738,17 @@
         <v>11</v>
       </c>
       <c r="BN13" s="479">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BO13" s="479">
         <v>31</v>
       </c>
       <c r="BP13" s="479">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BQ13" s="479">
         <f>BO13-BP13</f>
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="BR13" s="479">
         <v>32</v>
@@ -7806,11 +7802,11 @@
       </c>
       <c r="Y14" s="332">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z14" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X14)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA14" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X14)</f>
@@ -7830,11 +7826,11 @@
       </c>
       <c r="AE14" s="332">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF14" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X14)+Z14</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG14" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X14)+AA14</f>
@@ -7928,10 +7924,10 @@
         <v>345</v>
       </c>
       <c r="BK14" s="472">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BL14" s="472">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM14" s="472">
         <v>12</v>
@@ -7940,17 +7936,17 @@
         <v>17</v>
       </c>
       <c r="BO14" s="472">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BP14" s="472">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="BQ14" s="472">
         <f>BO14-BP14</f>
-        <v>-42</v>
+        <v>-41</v>
       </c>
       <c r="BR14" s="472">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:77" ht="17.5" customHeight="1">
@@ -8002,7 +7998,7 @@
       <c r="T15" s="320"/>
       <c r="U15" s="402"/>
       <c r="V15" s="403" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X15" s="358" t="s">
         <v>90</v>
@@ -8102,11 +8098,11 @@
       </c>
       <c r="BB15" s="466">
         <f>SUM(BB3:BB14)</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BC15" s="243">
         <f>SUM(BC3:BC14)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD15" s="467">
         <f>SUM(BD3:BD14)</f>
@@ -8118,11 +8114,11 @@
       </c>
       <c r="BF15" s="89">
         <f>SUM(BF3:BF14)</f>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="BG15" s="11">
         <f t="shared" si="12"/>
-        <v>0.33333333333333331</v>
+        <v>0.35483870967741937</v>
       </c>
       <c r="BI15" s="476" t="s">
         <v>91</v>
@@ -8237,7 +8233,7 @@
         <v>42</v>
       </c>
       <c r="AM16" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="AN16" s="89">
         <f t="shared" si="13"/>
@@ -8390,7 +8386,7 @@
         <v>42</v>
       </c>
       <c r="AM17" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AN17" s="89">
         <f t="shared" si="13"/>
@@ -8470,7 +8466,7 @@
       <c r="T18" s="320"/>
       <c r="U18" s="400"/>
       <c r="V18" s="312" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X18" s="327" t="s">
         <v>94</v>
@@ -8774,11 +8770,11 @@
       </c>
       <c r="Y21" s="332">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z21" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X21)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA21" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X21)</f>
@@ -8798,11 +8794,11 @@
       </c>
       <c r="AE21" s="332">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF21" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X21)+Z21</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG21" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X21)+AA21</f>
@@ -8875,11 +8871,11 @@
       </c>
       <c r="Y22" s="332">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z22" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X22)</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA22" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X22)</f>
@@ -8891,19 +8887,19 @@
       </c>
       <c r="AC22" s="334">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD22" s="335">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE22" s="332">
         <f t="shared" si="4"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF22" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X22)+Z22</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG22" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X22)+AA22</f>
@@ -8915,11 +8911,11 @@
       </c>
       <c r="AI22" s="334">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ22" s="335">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:48">
@@ -8982,11 +8978,11 @@
       </c>
       <c r="Y23" s="332">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z23" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X23)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA23" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X23)</f>
@@ -9006,11 +9002,11 @@
       </c>
       <c r="AE23" s="332">
         <f t="shared" si="4"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF23" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X23)+Z23</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG23" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X23)+AA23</f>
@@ -9079,11 +9075,11 @@
       </c>
       <c r="Y24" s="332">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Z24" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X24)</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA24" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X24)</f>
@@ -9103,11 +9099,11 @@
       </c>
       <c r="AE24" s="332">
         <f t="shared" si="4"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF24" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X24)+Z24</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG24" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X24)+AA24</f>
@@ -9937,32 +9933,52 @@
       <c r="F33" s="268" t="s">
         <v>342</v>
       </c>
-      <c r="G33" s="266"/>
-      <c r="H33" s="266"/>
-      <c r="I33" s="380"/>
+      <c r="G33" s="266">
+        <v>3</v>
+      </c>
+      <c r="H33" s="266">
+        <v>0</v>
+      </c>
+      <c r="I33" s="380" t="s">
+        <v>356</v>
+      </c>
       <c r="J33" s="374"/>
       <c r="K33" s="266"/>
       <c r="L33" s="269"/>
-      <c r="M33" s="246"/>
-      <c r="N33" s="270"/>
-      <c r="O33" s="270"/>
+      <c r="M33" s="246" t="s">
+        <v>106</v>
+      </c>
+      <c r="N33" s="270" t="s">
+        <v>81</v>
+      </c>
+      <c r="O33" s="270" t="s">
+        <v>46</v>
+      </c>
       <c r="P33" s="271"/>
-      <c r="Q33" s="272"/>
-      <c r="R33" s="270"/>
+      <c r="Q33" s="272" t="s">
+        <v>106</v>
+      </c>
+      <c r="R33" s="270" t="s">
+        <v>89</v>
+      </c>
       <c r="S33" s="270"/>
       <c r="T33" s="270"/>
-      <c r="U33" s="273"/>
-      <c r="V33" s="274"/>
+      <c r="U33" s="273">
+        <v>12189</v>
+      </c>
+      <c r="V33" s="274" t="s">
+        <v>82</v>
+      </c>
       <c r="X33" s="330" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Y33" s="332">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z33" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X33)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA33" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X33)</f>
@@ -9982,11 +9998,11 @@
       </c>
       <c r="AE33" s="332">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF33" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X33)+Z33</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG33" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X33)+AA33</f>
@@ -10041,7 +10057,7 @@
       <c r="U34" s="273"/>
       <c r="V34" s="274"/>
       <c r="X34" s="330" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Y34" s="332">
         <f t="shared" si="0"/>
@@ -10128,7 +10144,7 @@
       <c r="U35" s="273"/>
       <c r="V35" s="274"/>
       <c r="X35" s="330" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Y35" s="332">
         <f t="shared" si="0"/>
@@ -10207,7 +10223,7 @@
       <c r="U36" s="400"/>
       <c r="V36" s="312"/>
       <c r="X36" s="330" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y36" s="332">
         <f t="shared" si="0"/>
@@ -10286,7 +10302,7 @@
       <c r="U37" s="400"/>
       <c r="V37" s="312"/>
       <c r="X37" s="356" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y37" s="332">
         <f t="shared" si="0"/>
@@ -10365,7 +10381,7 @@
       <c r="U38" s="400"/>
       <c r="V38" s="312"/>
       <c r="X38" s="356" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y38" s="332">
         <f t="shared" si="0"/>
@@ -10444,7 +10460,7 @@
       <c r="U39" s="409"/>
       <c r="V39" s="410"/>
       <c r="X39" s="356" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Y39" s="332">
         <f t="shared" si="0"/>
@@ -10523,7 +10539,7 @@
       <c r="U40" s="431"/>
       <c r="V40" s="420"/>
       <c r="X40" s="78" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Y40" s="332">
         <f t="shared" si="0"/>
@@ -10576,19 +10592,19 @@
     </row>
     <row r="41" spans="1:36">
       <c r="A41" s="423" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B41" s="432" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C41" s="433" t="s">
         <v>62</v>
       </c>
       <c r="D41" s="421" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E41" s="421" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F41" s="421" t="s">
         <v>45</v>
@@ -10617,18 +10633,18 @@
         <v>3873</v>
       </c>
       <c r="V41" s="428" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="X41" s="473" t="s">
         <v>102</v>
       </c>
       <c r="Y41" s="332">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z41" s="474">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X41)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA41" s="474">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X41)</f>
@@ -10648,11 +10664,11 @@
       </c>
       <c r="AE41" s="475">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF41" s="475">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X41)+Z41</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG41" s="475">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X41)+AA41</f>
@@ -10673,22 +10689,22 @@
     </row>
     <row r="42" spans="1:36">
       <c r="N42" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O42" s="213"/>
       <c r="Q42" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="X42" s="473" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="Y42" s="332">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z42" s="474">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X42)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA42" s="474">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X42)</f>
@@ -10696,23 +10712,23 @@
       </c>
       <c r="AB42" s="333">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC42" s="334">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD42" s="335">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE42" s="475">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF42" s="475">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X42)+Z42</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG42" s="475">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X42)+AA42</f>
@@ -10720,15 +10736,15 @@
       </c>
       <c r="AH42" s="475">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI42" s="475">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ42" s="475">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:36">
@@ -10814,15 +10830,15 @@
       </c>
       <c r="N44" s="2">
         <f>COUNT(U3:U40)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O44" s="96">
         <f>SUMIFS(U3:U41,A3:A41,M44)</f>
-        <v>153260</v>
+        <v>165449</v>
       </c>
       <c r="P44" s="96">
         <f>O44/N44</f>
-        <v>9578.75</v>
+        <v>9732.2941176470595</v>
       </c>
       <c r="Q44" s="136">
         <v>19</v>
@@ -10835,12 +10851,12 @@
       </c>
       <c r="T44" s="165">
         <f>(P44-S44)/S44</f>
-        <v>-5.848749624939209E-2</v>
+        <v>-4.3395369756680527E-2</v>
       </c>
     </row>
     <row r="45" spans="1:36">
       <c r="M45" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N45" s="2">
         <f>COUNT(U41:U41)</f>
@@ -11429,7 +11445,7 @@
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C13" s="2">
         <v>2</v>
@@ -11662,7 +11678,7 @@
     </row>
     <row r="22" spans="2:11">
       <c r="B22" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C22" s="2">
         <v>3</v>
@@ -11758,7 +11774,7 @@
     </row>
     <row r="25" spans="2:11">
       <c r="B25" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C25" s="2">
         <v>3</v>
@@ -11950,7 +11966,7 @@
     </row>
     <row r="31" spans="2:11">
       <c r="B31" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C31" s="2">
         <v>4</v>
@@ -12179,7 +12195,7 @@
     </row>
     <row r="40" spans="2:11">
       <c r="B40" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C40" s="2">
         <v>4</v>
@@ -12275,7 +12291,7 @@
     </row>
     <row r="43" spans="2:11">
       <c r="B43" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C43" s="2">
         <v>4</v>
@@ -12307,7 +12323,7 @@
     </row>
     <row r="44" spans="2:11">
       <c r="B44" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C44" s="2">
         <v>4</v>
@@ -12728,7 +12744,7 @@
     </row>
     <row r="59" spans="2:11">
       <c r="B59" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C59" s="2">
         <v>4</v>
@@ -12792,7 +12808,7 @@
     </row>
     <row r="61" spans="2:11">
       <c r="B61" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C61" s="2">
         <v>3</v>
@@ -12824,7 +12840,7 @@
     </row>
     <row r="62" spans="2:11">
       <c r="B62" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C62" s="2">
         <v>3</v>
@@ -13309,7 +13325,7 @@
     </row>
     <row r="79" spans="2:11">
       <c r="B79" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C79" s="2">
         <v>0</v>
@@ -13437,7 +13453,7 @@
     </row>
     <row r="83" spans="2:11">
       <c r="B83" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C83" s="2">
         <v>0</v>
@@ -13501,7 +13517,7 @@
     </row>
     <row r="85" spans="2:11">
       <c r="B85" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C85" s="2">
         <v>0</v>
@@ -14008,7 +14024,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E5" s="30" t="s">
         <v>45</v>
@@ -14385,7 +14401,7 @@
         <v>6</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E8" s="30" t="s">
         <v>49</v>
@@ -14504,7 +14520,7 @@
         <v>7</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E9" s="30" t="s">
         <v>49</v>
@@ -14545,7 +14561,7 @@
       <c r="U9" s="15"/>
       <c r="V9" s="54"/>
       <c r="X9" s="72" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y9" s="81">
         <f t="shared" si="0"/>
@@ -14672,7 +14688,7 @@
         <v>300</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S10" s="15"/>
       <c r="T10" s="15"/>
@@ -15162,7 +15178,7 @@
         <v>12</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E14" s="24" t="s">
         <v>49</v>
@@ -15254,7 +15270,7 @@
         <v>13</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E15" s="24" t="s">
         <v>45</v>
@@ -15532,7 +15548,7 @@
         <v>171</v>
       </c>
       <c r="M17" s="58" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N17" s="58"/>
       <c r="O17" s="58"/>
@@ -16123,7 +16139,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E22" s="24" t="s">
         <v>45</v>
@@ -16599,7 +16615,7 @@
       <c r="U26" s="15"/>
       <c r="V26" s="54"/>
       <c r="X26" s="70" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y26" s="81">
         <f t="shared" si="0"/>
@@ -16706,7 +16722,7 @@
         <v>25</v>
       </c>
       <c r="D27" s="30" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E27" s="30" t="s">
         <v>49</v>
@@ -17038,7 +17054,7 @@
       <c r="O29" s="15"/>
       <c r="P29" s="15"/>
       <c r="Q29" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="R29" s="15"/>
       <c r="S29" s="15"/>
@@ -17301,7 +17317,7 @@
         <v>42</v>
       </c>
       <c r="AD31" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="AE31" s="2">
         <f t="shared" si="17"/>
@@ -17351,7 +17367,7 @@
         <v>30</v>
       </c>
       <c r="D32" s="30" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E32" s="30" t="s">
         <v>45</v>
@@ -17464,7 +17480,7 @@
         <v>31</v>
       </c>
       <c r="D33" s="30" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E33" s="30" t="s">
         <v>49</v>
@@ -17521,7 +17537,7 @@
         <v>42</v>
       </c>
       <c r="AD33" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="AE33" s="2">
         <f t="shared" si="17"/>
@@ -17632,7 +17648,7 @@
         <v>42</v>
       </c>
       <c r="AD34" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="AE34" s="2">
         <f t="shared" si="17"/>
@@ -17816,7 +17832,7 @@
       <c r="O36" s="58"/>
       <c r="P36" s="58"/>
       <c r="Q36" s="58" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R36" s="58"/>
       <c r="S36" s="58"/>
@@ -17931,7 +17947,7 @@
       <c r="U37" s="58"/>
       <c r="V37" s="59"/>
       <c r="X37" s="68" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Y37" s="81">
         <f t="shared" si="0"/>
@@ -17999,7 +18015,7 @@
         <v>36</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E38" s="24" t="s">
         <v>45</v>
@@ -18038,7 +18054,7 @@
         <v>11912</v>
       </c>
       <c r="X38" s="68" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Y38" s="81">
         <f t="shared" si="0"/>
@@ -18133,7 +18149,7 @@
         <v>54</v>
       </c>
       <c r="M39" s="58" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N39" s="58" t="s">
         <v>278</v>
@@ -18254,7 +18270,7 @@
       <c r="O40" s="64"/>
       <c r="P40" s="64"/>
       <c r="Q40" s="64" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="R40" s="64"/>
       <c r="S40" s="64"/>
@@ -18568,7 +18584,7 @@
       </c>
       <c r="P43" s="76"/>
       <c r="Q43" s="76" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R43" s="76"/>
       <c r="S43" s="76" t="s">
@@ -18762,7 +18778,7 @@
       <c r="U45" s="76"/>
       <c r="V45" s="77"/>
       <c r="AC45" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AD45" s="2" t="s">
         <v>139</v>
@@ -18838,7 +18854,7 @@
         <v>31</v>
       </c>
       <c r="L46" s="76" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M46" s="76" t="s">
         <v>300</v>
@@ -18857,7 +18873,7 @@
         <v>5712</v>
       </c>
       <c r="AC46" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AD46" s="2" t="s">
         <v>142</v>
@@ -18940,7 +18956,7 @@
       <c r="O47" s="126"/>
       <c r="P47" s="126"/>
       <c r="Q47" s="126" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="R47" s="126" t="s">
         <v>272</v>
@@ -18950,10 +18966,10 @@
       <c r="U47" s="126"/>
       <c r="V47" s="127"/>
       <c r="AC47" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AD47" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="AE47" s="2">
         <f t="shared" si="17"/>
@@ -18994,7 +19010,7 @@
     </row>
     <row r="48" spans="1:39">
       <c r="A48" s="98" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B48" s="128">
         <v>45070</v>
@@ -19026,7 +19042,7 @@
         <v>272</v>
       </c>
       <c r="M48" s="129" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N48" s="129" t="s">
         <v>279</v>
@@ -19037,7 +19053,7 @@
         <v>170</v>
       </c>
       <c r="R48" s="129" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S48" s="129" t="s">
         <v>143</v>
@@ -19050,7 +19066,7 @@
     </row>
     <row r="49" spans="1:22">
       <c r="A49" s="110" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B49" s="109">
         <v>45105</v>
@@ -19102,7 +19118,7 @@
     </row>
     <row r="50" spans="1:22" ht="17.5" customHeight="1" thickBot="1">
       <c r="A50" s="100" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B50" s="112">
         <v>45231</v>
@@ -19111,7 +19127,7 @@
         <v>130</v>
       </c>
       <c r="D50" s="104" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E50" s="104" t="s">
         <v>49</v>
@@ -19224,7 +19240,7 @@
     </row>
     <row r="55" spans="1:22">
       <c r="L55" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M55" s="2">
         <v>2</v>
@@ -19728,7 +19744,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D5" s="30" t="s">
         <v>45</v>
@@ -20050,7 +20066,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D8" s="30" t="s">
         <v>49</v>
@@ -20168,7 +20184,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D9" s="30" t="s">
         <v>49</v>
@@ -20204,7 +20220,7 @@
       <c r="O9" s="56"/>
       <c r="P9" s="54"/>
       <c r="S9" s="72" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T9" s="81">
         <f t="shared" si="0"/>
@@ -20326,7 +20342,7 @@
         <v>300</v>
       </c>
       <c r="O10" s="56" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P10" s="54"/>
       <c r="S10" s="72" t="s">
@@ -20748,7 +20764,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D14" s="24" t="s">
         <v>49</v>
@@ -20859,7 +20875,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D15" s="24" t="s">
         <v>45</v>
@@ -21099,7 +21115,7 @@
         <v>171</v>
       </c>
       <c r="L17" s="58" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M17" s="59"/>
       <c r="N17" s="142" t="s">
@@ -21559,7 +21575,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D22" s="24" t="s">
         <v>45</v>
@@ -21932,7 +21948,7 @@
       <c r="O26" s="56"/>
       <c r="P26" s="54"/>
       <c r="S26" s="70" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="T26" s="81">
         <f t="shared" si="0"/>
@@ -22006,7 +22022,7 @@
         <v>25</v>
       </c>
       <c r="C27" s="30" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D27" s="30" t="s">
         <v>49</v>
@@ -22257,7 +22273,7 @@
       </c>
       <c r="M29" s="54"/>
       <c r="N29" s="141" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O29" s="56"/>
       <c r="P29" s="54"/>
@@ -22460,7 +22476,7 @@
         <v>3</v>
       </c>
       <c r="Y31" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="Z31" s="2">
         <f t="shared" si="14"/>
@@ -22507,7 +22523,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="30" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D32" s="30" t="s">
         <v>45</v>
@@ -22607,7 +22623,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="30" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D33" s="30" t="s">
         <v>49</v>
@@ -22656,7 +22672,7 @@
         <v>0</v>
       </c>
       <c r="Y33" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="Z33" s="2">
         <f t="shared" si="14"/>
@@ -22754,7 +22770,7 @@
         <v>1</v>
       </c>
       <c r="Y34" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="Z34" s="2">
         <f t="shared" si="14"/>
@@ -22922,7 +22938,7 @@
       <c r="L36" s="58"/>
       <c r="M36" s="59"/>
       <c r="N36" s="142" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O36" s="61"/>
       <c r="P36" s="59"/>
@@ -23023,7 +23039,7 @@
       <c r="O37" s="61"/>
       <c r="P37" s="59"/>
       <c r="S37" s="68" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T37" s="81">
         <f t="shared" si="0"/>
@@ -23085,7 +23101,7 @@
         <v>36</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D38" s="24" t="s">
         <v>45</v>
@@ -23117,7 +23133,7 @@
       <c r="O38" s="61"/>
       <c r="P38" s="59"/>
       <c r="S38" s="68" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T38" s="81">
         <f t="shared" si="0"/>
@@ -23206,7 +23222,7 @@
         <v>54</v>
       </c>
       <c r="L39" s="58" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M39" s="59" t="s">
         <v>278</v>
@@ -23312,7 +23328,7 @@
       <c r="L40" s="64"/>
       <c r="M40" s="65"/>
       <c r="N40" s="144" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O40" s="67"/>
       <c r="P40" s="65"/>
@@ -23869,7 +23885,7 @@
       </c>
       <c r="O5" s="54"/>
       <c r="P5" s="55" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q5" s="56"/>
       <c r="R5" s="56" t="s">
@@ -24127,7 +24143,7 @@
         <v>31</v>
       </c>
       <c r="K8" s="53" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L8" s="15" t="s">
         <v>300</v>
@@ -24232,7 +24248,7 @@
       <c r="S9" s="56"/>
       <c r="T9" s="54"/>
       <c r="W9" s="72" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X9" s="81">
         <f t="shared" si="0"/>
@@ -25309,7 +25325,7 @@
       <c r="S26" s="56"/>
       <c r="T26" s="54"/>
       <c r="W26" s="70" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="X26" s="81">
         <f t="shared" si="0"/>
@@ -26085,7 +26101,7 @@
       <c r="S37" s="61"/>
       <c r="T37" s="59"/>
       <c r="W37" s="68" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="X37" s="81">
         <f t="shared" si="0"/>
@@ -26132,7 +26148,7 @@
       <c r="S38" s="61"/>
       <c r="T38" s="59"/>
       <c r="W38" s="68" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="X38" s="81">
         <f t="shared" si="0"/>
@@ -26472,7 +26488,7 @@
         <v>272</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M3" s="15" t="s">
         <v>279</v>
@@ -26483,7 +26499,7 @@
         <v>170</v>
       </c>
       <c r="Q3" s="56" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R3" s="56" t="s">
         <v>143</v>
@@ -26676,7 +26692,7 @@
         <v>130</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D5" s="30" t="s">
         <v>49</v>
@@ -26971,7 +26987,7 @@
       <c r="S9" s="56"/>
       <c r="T9" s="54"/>
       <c r="W9" s="72" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X9" s="81">
         <f t="shared" si="0"/>
@@ -28008,7 +28024,7 @@
       <c r="S26" s="56"/>
       <c r="T26" s="54"/>
       <c r="W26" s="70" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="X26" s="81">
         <f t="shared" si="0"/>
@@ -28506,7 +28522,7 @@
         <v>0</v>
       </c>
       <c r="AC32" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="AD32" s="2">
         <f>SUM(AE32:AG32)</f>
@@ -28755,7 +28771,7 @@
       <c r="S37" s="61"/>
       <c r="T37" s="59"/>
       <c r="W37" s="68" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="X37" s="81">
         <f t="shared" si="0"/>
@@ -28802,7 +28818,7 @@
       <c r="S38" s="61"/>
       <c r="T38" s="59"/>
       <c r="W38" s="68" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="X38" s="81">
         <f t="shared" si="0"/>
@@ -29346,7 +29362,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="73" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D5" s="73" t="s">
         <v>49</v>
@@ -29690,7 +29706,7 @@
       <c r="S8" s="79"/>
       <c r="T8" s="77"/>
       <c r="W8" s="72" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X8" s="51">
         <f t="shared" si="0"/>
@@ -29698,7 +29714,7 @@
       </c>
       <c r="Y8" s="1"/>
       <c r="Z8" s="72" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA8" s="51">
         <f t="shared" si="1"/>
@@ -29975,7 +29991,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="73" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D11" s="73" t="s">
         <v>45</v>
@@ -30211,7 +30227,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="73" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D13" s="73" t="s">
         <v>45</v>
@@ -30718,7 +30734,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="73" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D18" s="73" t="s">
         <v>49</v>
@@ -30834,7 +30850,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="73" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D19" s="73" t="s">
         <v>45</v>
@@ -31241,7 +31257,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D23" s="24" t="s">
         <v>49</v>
@@ -31402,7 +31418,7 @@
       <c r="I25" s="30"/>
       <c r="J25" s="30"/>
       <c r="K25" s="53" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L25" s="15"/>
       <c r="M25" s="15"/>
@@ -31414,7 +31430,7 @@
       <c r="S25" s="56"/>
       <c r="T25" s="54"/>
       <c r="W25" s="70" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="X25" s="51">
         <f t="shared" si="0"/>
@@ -31422,7 +31438,7 @@
       </c>
       <c r="Y25" s="1"/>
       <c r="Z25" s="70" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AA25" s="51">
         <f t="shared" si="1"/>
@@ -31694,7 +31710,7 @@
         <v>28</v>
       </c>
       <c r="C28" s="30" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D28" s="30" t="s">
         <v>45</v>
@@ -31824,7 +31840,7 @@
         <v>0</v>
       </c>
       <c r="AD29" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="AE29" s="2">
         <f t="shared" ref="AE29:AE39" si="13">SUM(AF29:AH29)</f>
@@ -31961,7 +31977,7 @@
         <v>29</v>
       </c>
       <c r="C31" s="30" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D31" s="30" t="s">
         <v>45</v>
@@ -32049,7 +32065,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="30" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D32" s="30" t="s">
         <v>49</v>
@@ -32094,7 +32110,7 @@
         <v>0</v>
       </c>
       <c r="AD32" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="AE32" s="2">
         <f t="shared" si="13"/>
@@ -32188,7 +32204,7 @@
         <v>0</v>
       </c>
       <c r="AD33" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="AE33" s="2">
         <f t="shared" si="13"/>
@@ -32261,7 +32277,7 @@
       <c r="S34" s="56"/>
       <c r="T34" s="54"/>
       <c r="W34" s="68" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="X34" s="51">
         <f t="shared" si="0"/>
@@ -32269,7 +32285,7 @@
       </c>
       <c r="Y34" s="1"/>
       <c r="Z34" s="68" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AA34" s="51">
         <f t="shared" si="1"/>
@@ -32349,7 +32365,7 @@
       <c r="S35" s="56"/>
       <c r="T35" s="54"/>
       <c r="W35" s="68" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="X35" s="51">
         <f t="shared" si="0"/>
@@ -32357,7 +32373,7 @@
       </c>
       <c r="Y35" s="1"/>
       <c r="Z35" s="68" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AA35" s="51">
         <f t="shared" si="1"/>
@@ -32497,7 +32513,7 @@
         <v>35</v>
       </c>
       <c r="C37" s="24" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D37" s="24" t="s">
         <v>49</v>
@@ -32585,7 +32601,7 @@
         <v>36</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D38" s="24" t="s">
         <v>45</v>
@@ -32609,7 +32625,7 @@
         <v>156</v>
       </c>
       <c r="M38" s="58" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N38" s="58"/>
       <c r="O38" s="59"/>
@@ -32739,7 +32755,7 @@
         <v>38</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D40" s="37" t="s">
         <v>49</v>
@@ -33150,7 +33166,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D8" s="20" t="s">
         <v>49</v>
@@ -33296,7 +33312,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D11" s="20" t="s">
         <v>49</v>
@@ -33356,7 +33372,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D12" s="20" t="s">
         <v>45</v>
@@ -33534,7 +33550,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D15" s="20" t="s">
         <v>45</v>
@@ -33794,7 +33810,7 @@
         <v>18</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D20" s="20" t="s">
         <v>45</v>
@@ -33940,7 +33956,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D23" s="20" t="s">
         <v>49</v>
@@ -34273,7 +34289,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D29" s="20" t="s">
         <v>45</v>
@@ -34291,7 +34307,7 @@
         <v>33</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="L29" s="2">
         <f t="shared" ref="L29:L39" si="0">SUM(M29:O29)</f>
@@ -34468,7 +34484,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D32" s="20" t="s">
         <v>49</v>
@@ -34486,7 +34502,7 @@
         <v>33</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="L32" s="2">
         <f t="shared" si="0"/>
@@ -34598,7 +34614,7 @@
         <v>32</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D34" s="20" t="s">
         <v>45</v>
@@ -34859,7 +34875,7 @@
         <v>36</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D38" s="20" t="s">
         <v>49</v>
@@ -34877,7 +34893,7 @@
         <v>32</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="L38" s="2">
         <f t="shared" si="0"/>
@@ -35052,7 +35068,7 @@
         <v>261</v>
       </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -35065,7 +35081,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B7" t="s">
         <v>171</v>
@@ -35141,12 +35157,12 @@
     </row>
     <row r="17" spans="3:3">
       <c r="C17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="3:3">
       <c r="C18" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" spans="3:3">
@@ -35238,7 +35254,7 @@
       </c>
       <c r="T1" s="85"/>
       <c r="V1" s="292" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="W1" s="294" t="s">
         <v>26</v>
@@ -35300,7 +35316,7 @@
         <v>341</v>
       </c>
       <c r="C2" s="297" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D2" s="243" t="s">
         <v>97</v>
@@ -35345,7 +35361,7 @@
         <v>74</v>
       </c>
       <c r="R2" s="159" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S2" s="51"/>
       <c r="T2" s="1"/>
@@ -35376,7 +35392,7 @@
         <v>345</v>
       </c>
       <c r="C3" s="297" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D3" s="243" t="s">
         <v>97</v>
@@ -35452,7 +35468,7 @@
         <v>349</v>
       </c>
       <c r="C4" s="297" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D4" s="243" t="s">
         <v>97</v>
@@ -35524,7 +35540,7 @@
         <v>353</v>
       </c>
       <c r="C5" s="297" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D5" s="243" t="s">
         <v>97</v>
@@ -35602,7 +35618,7 @@
         <v>355</v>
       </c>
       <c r="C6" s="297" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D6" s="243" t="s">
         <v>96</v>
@@ -35678,7 +35694,7 @@
         <v>358</v>
       </c>
       <c r="C7" s="297" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D7" s="243" t="s">
         <v>96</v>
@@ -35756,7 +35772,7 @@
         <v>360</v>
       </c>
       <c r="C8" s="297" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D8" s="243" t="s">
         <v>96</v>
@@ -35812,7 +35828,7 @@
         <v>362</v>
       </c>
       <c r="C9" s="297" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D9" s="243" t="s">
         <v>96</v>
@@ -35857,7 +35873,7 @@
         <v>59</v>
       </c>
       <c r="R9" s="159" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S9" s="51"/>
       <c r="T9" s="1"/>
@@ -35870,7 +35886,7 @@
         <v>365</v>
       </c>
       <c r="C10" s="297" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D10" s="243" t="s">
         <v>96</v>
@@ -35915,7 +35931,7 @@
         <v>46</v>
       </c>
       <c r="R10" s="159" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S10" s="51"/>
       <c r="T10" s="1"/>
@@ -35928,7 +35944,7 @@
         <v>367</v>
       </c>
       <c r="C11" s="297" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D11" s="243" t="s">
         <v>96</v>
@@ -35986,7 +36002,7 @@
         <v>369</v>
       </c>
       <c r="C12" s="297" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D12" s="243" t="s">
         <v>96</v>
@@ -36031,7 +36047,7 @@
         <v>80</v>
       </c>
       <c r="R12" s="159" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S12" s="51"/>
       <c r="T12" s="1"/>
@@ -36044,7 +36060,7 @@
         <v>353</v>
       </c>
       <c r="C13" s="297" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D13" s="243" t="s">
         <v>96</v>
@@ -36089,7 +36105,7 @@
         <v>80</v>
       </c>
       <c r="R13" s="159" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="S13" s="51"/>
       <c r="T13" s="1"/>
@@ -36102,7 +36118,7 @@
         <v>358</v>
       </c>
       <c r="C14" s="297" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D14" s="243" t="s">
         <v>97</v>
@@ -36160,7 +36176,7 @@
         <v>349</v>
       </c>
       <c r="C15" s="297" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D15" s="243" t="s">
         <v>97</v>
@@ -36190,7 +36206,7 @@
         <v>54</v>
       </c>
       <c r="M15" s="298" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N15" s="110" t="s">
         <v>71</v>
@@ -36218,7 +36234,7 @@
         <v>345</v>
       </c>
       <c r="C16" s="297" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D16" s="243" t="s">
         <v>97</v>
@@ -36260,7 +36276,7 @@
         <v>87</v>
       </c>
       <c r="Q16" s="159" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="R16" s="159" t="s">
         <v>54</v>
@@ -36276,7 +36292,7 @@
         <v>341</v>
       </c>
       <c r="C17" s="297" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D17" s="243" t="s">
         <v>97</v>
@@ -36334,7 +36350,7 @@
         <v>355</v>
       </c>
       <c r="C18" s="297" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D18" s="243" t="s">
         <v>97</v>
@@ -36390,7 +36406,7 @@
         <v>365</v>
       </c>
       <c r="C19" s="297" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D19" s="243" t="s">
         <v>97</v>
@@ -36448,7 +36464,7 @@
         <v>360</v>
       </c>
       <c r="C20" s="297" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D20" s="243" t="s">
         <v>97</v>
@@ -36506,7 +36522,7 @@
         <v>362</v>
       </c>
       <c r="C21" s="297" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D21" s="243" t="s">
         <v>97</v>
@@ -36564,7 +36580,7 @@
         <v>367</v>
       </c>
       <c r="C22" s="297" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D22" s="243" t="s">
         <v>89</v>
@@ -36622,7 +36638,7 @@
         <v>369</v>
       </c>
       <c r="C23" s="297" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D23" s="243" t="s">
         <v>89</v>
@@ -36652,7 +36668,7 @@
         <v>46</v>
       </c>
       <c r="M23" s="298" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="N23" s="110" t="s">
         <v>50</v>
@@ -36676,7 +36692,7 @@
         <v>358</v>
       </c>
       <c r="C24" s="297" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D24" s="243" t="s">
         <v>89</v>
@@ -36734,7 +36750,7 @@
         <v>345</v>
       </c>
       <c r="C25" s="297" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D25" s="243" t="s">
         <v>89</v>
@@ -36779,7 +36795,7 @@
         <v>59</v>
       </c>
       <c r="R25" s="159" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="S25" s="51"/>
       <c r="T25" s="1"/>
@@ -36792,7 +36808,7 @@
         <v>355</v>
       </c>
       <c r="C26" s="297" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D26" s="243" t="s">
         <v>89</v>
@@ -36816,7 +36832,7 @@
         <v>51</v>
       </c>
       <c r="K26" s="243" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="L26" s="243" t="s">
         <v>94</v>
@@ -36850,7 +36866,7 @@
         <v>365</v>
       </c>
       <c r="C27" s="297" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D27" s="243" t="s">
         <v>97</v>
@@ -36892,7 +36908,7 @@
         <v>66</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="R27" s="159"/>
       <c r="S27" s="51"/>
@@ -36906,7 +36922,7 @@
         <v>341</v>
       </c>
       <c r="C28" s="297" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D28" s="243" t="s">
         <v>89</v>
@@ -36930,7 +36946,7 @@
         <v>83</v>
       </c>
       <c r="K28" s="243" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="L28" s="243" t="s">
         <v>46</v>
@@ -36964,7 +36980,7 @@
         <v>362</v>
       </c>
       <c r="C29" s="297" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D29" s="243" t="s">
         <v>89</v>
@@ -37003,7 +37019,7 @@
         <v>81</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="Q29" s="159" t="s">
         <v>87</v>
@@ -37022,7 +37038,7 @@
         <v>360</v>
       </c>
       <c r="C30" s="297" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D30" s="243" t="s">
         <v>89</v>
@@ -37078,7 +37094,7 @@
         <v>353</v>
       </c>
       <c r="C31" s="297" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D31" s="243" t="s">
         <v>89</v>
@@ -37120,7 +37136,7 @@
         <v>83</v>
       </c>
       <c r="Q31" s="159" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="R31" s="159"/>
       <c r="S31" s="51"/>
@@ -37133,22 +37149,54 @@
       <c r="B32" s="264" t="s">
         <v>349</v>
       </c>
-      <c r="C32" s="297"/>
-      <c r="D32" s="243"/>
-      <c r="E32" s="243"/>
-      <c r="F32" s="243"/>
-      <c r="G32" s="243"/>
-      <c r="H32" s="243"/>
-      <c r="I32" s="243"/>
-      <c r="J32" s="243"/>
-      <c r="K32" s="243"/>
-      <c r="L32" s="243"/>
-      <c r="M32" s="298"/>
-      <c r="N32" s="110"/>
-      <c r="O32" s="2"/>
-      <c r="P32" s="2"/>
-      <c r="Q32" s="159"/>
-      <c r="R32" s="159"/>
+      <c r="C32" s="297" t="s">
+        <v>107</v>
+      </c>
+      <c r="D32" s="243" t="s">
+        <v>89</v>
+      </c>
+      <c r="E32" s="243" t="s">
+        <v>97</v>
+      </c>
+      <c r="F32" s="243" t="s">
+        <v>64</v>
+      </c>
+      <c r="G32" s="243" t="s">
+        <v>52</v>
+      </c>
+      <c r="H32" s="243" t="s">
+        <v>74</v>
+      </c>
+      <c r="I32" s="243" t="s">
+        <v>87</v>
+      </c>
+      <c r="J32" s="243" t="s">
+        <v>106</v>
+      </c>
+      <c r="K32" s="243" t="s">
+        <v>102</v>
+      </c>
+      <c r="L32" s="243" t="s">
+        <v>46</v>
+      </c>
+      <c r="M32" s="298" t="s">
+        <v>81</v>
+      </c>
+      <c r="N32" s="110" t="s">
+        <v>59</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q32" s="159" t="s">
+        <v>54</v>
+      </c>
+      <c r="R32" s="159" t="s">
+        <v>51</v>
+      </c>
       <c r="S32" s="51"/>
       <c r="T32" s="1"/>
     </row>
@@ -37470,7 +37518,7 @@
         <v>8</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C50" s="2">
         <v>1</v>
@@ -37487,7 +37535,7 @@
         <v>9</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C51" s="2">
         <v>2</v>
@@ -37504,7 +37552,7 @@
         <v>10</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C52" s="2">
         <v>6</v>
@@ -37521,7 +37569,7 @@
         <v>11</v>
       </c>
       <c r="B53" s="266" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C53" s="2">
         <v>6</v>
@@ -37628,7 +37676,7 @@
         <v>18</v>
       </c>
       <c r="B60" s="352" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="96"/>
@@ -37650,7 +37698,7 @@
         <v>20</v>
       </c>
       <c r="B62" s="352" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="96"/>
@@ -37661,7 +37709,7 @@
         <v>21</v>
       </c>
       <c r="B63" s="352" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="96"/>
@@ -37672,7 +37720,7 @@
         <v>22</v>
       </c>
       <c r="B64" s="413" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C64" s="441"/>
       <c r="D64" s="442"/>
@@ -37716,7 +37764,7 @@
         <v>26</v>
       </c>
       <c r="B68" s="352" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="96"/>
@@ -37738,7 +37786,7 @@
         <v>28</v>
       </c>
       <c r="B70" s="352" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" s="96"/>
@@ -37782,7 +37830,7 @@
         <v>32</v>
       </c>
       <c r="B74" s="352" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" s="96"/>
@@ -37793,7 +37841,7 @@
         <v>33</v>
       </c>
       <c r="B75" s="413" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C75" s="441"/>
       <c r="D75" s="442"/>
@@ -39581,7 +39629,7 @@
         <v>9</v>
       </c>
       <c r="E11" s="267" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F11" s="266" t="s">
         <v>49</v>
@@ -39761,7 +39809,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="267" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F12" s="268" t="s">
         <v>45</v>
@@ -39801,7 +39849,7 @@
         <v>157</v>
       </c>
       <c r="X12" s="60" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Y12" s="297">
         <f t="shared" si="0"/>
@@ -40383,7 +40431,7 @@
         <v>42</v>
       </c>
       <c r="AM15" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AN15" s="89">
         <f t="shared" si="15"/>
@@ -40422,7 +40470,7 @@
         <v>2</v>
       </c>
       <c r="BA15" s="20" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BB15" s="2">
         <f t="shared" si="8"/>
@@ -40503,7 +40551,7 @@
         <v>75</v>
       </c>
       <c r="X16" s="60" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Y16" s="297">
         <f t="shared" si="0"/>
@@ -40557,7 +40605,7 @@
         <v>42</v>
       </c>
       <c r="AM16" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AN16" s="89">
         <f t="shared" si="15"/>
@@ -40641,7 +40689,7 @@
         <v>15</v>
       </c>
       <c r="E17" s="243" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F17" s="244" t="s">
         <v>45</v>
@@ -41165,7 +41213,7 @@
         <v>18</v>
       </c>
       <c r="E20" s="243" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F20" s="24" t="s">
         <v>49</v>
@@ -41458,7 +41506,7 @@
         <v>9326</v>
       </c>
       <c r="V22" s="93" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="X22" s="327" t="s">
         <v>174</v>
@@ -41575,7 +41623,7 @@
       <c r="K23" s="24"/>
       <c r="L23" s="41"/>
       <c r="M23" s="57" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N23" s="58" t="s">
         <v>171</v>
@@ -42118,7 +42166,7 @@
         <v>71</v>
       </c>
       <c r="N28" s="58" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O28" s="58" t="s">
         <v>71</v>
@@ -42307,7 +42355,7 @@
         <v>28</v>
       </c>
       <c r="E30" s="267" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F30" s="266" t="s">
         <v>49</v>
@@ -42420,10 +42468,10 @@
       <c r="K31" s="266"/>
       <c r="L31" s="269"/>
       <c r="M31" s="246" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N31" s="270" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O31" s="270" t="s">
         <v>171</v>
@@ -42511,7 +42559,7 @@
         <v>30</v>
       </c>
       <c r="E32" s="267" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F32" s="268" t="s">
         <v>45</v>
@@ -42838,7 +42886,7 @@
         <v>76</v>
       </c>
       <c r="X35" s="330" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Y35" s="297">
         <f t="shared" si="0"/>
@@ -43143,7 +43191,7 @@
         <v>173</v>
       </c>
       <c r="X38" s="331" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Y38" s="299">
         <f t="shared" si="0"/>
@@ -43323,7 +43371,7 @@
       <c r="K40" s="278"/>
       <c r="L40" s="280"/>
       <c r="M40" s="246" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N40" s="270"/>
       <c r="O40" s="270"/>
@@ -43436,7 +43484,7 @@
         <v>167</v>
       </c>
       <c r="X41" s="356" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y41" s="297">
         <f t="shared" si="0"/>
@@ -43489,7 +43537,7 @@
     </row>
     <row r="42" spans="1:36">
       <c r="A42" s="377" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B42" s="371">
         <v>45739</v>
@@ -43519,10 +43567,10 @@
       <c r="K42" s="310"/>
       <c r="L42" s="359"/>
       <c r="M42" s="392" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N42" s="311" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O42" s="311" t="s">
         <v>93</v>
@@ -43541,7 +43589,7 @@
         <v>186</v>
       </c>
       <c r="X42" s="356" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y42" s="297">
         <f t="shared" si="0"/>
@@ -43594,7 +43642,7 @@
     </row>
     <row r="43" spans="1:36">
       <c r="A43" s="110" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B43" s="317">
         <v>45763</v>
@@ -43603,7 +43651,7 @@
         <v>62</v>
       </c>
       <c r="D43" s="319" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E43" s="319" t="s">
         <v>187</v>
@@ -43635,7 +43683,7 @@
         <v>143</v>
       </c>
       <c r="R43" s="320" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="S43" s="320"/>
       <c r="T43" s="320"/>
@@ -43699,7 +43747,7 @@
     </row>
     <row r="44" spans="1:36">
       <c r="A44" s="110" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B44" s="317">
         <v>45791</v>
@@ -43738,12 +43786,12 @@
       <c r="T44" s="320"/>
       <c r="U44" s="321"/>
       <c r="V44" s="312" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="45" spans="1:36">
       <c r="A45" s="110" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B45" s="317"/>
       <c r="C45" s="318"/>
@@ -43769,7 +43817,7 @@
     </row>
     <row r="46" spans="1:36" ht="17.5" customHeight="1" thickBot="1">
       <c r="A46" s="100" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B46" s="324"/>
       <c r="C46" s="325"/>
@@ -43795,7 +43843,7 @@
     </row>
     <row r="47" spans="1:36">
       <c r="N47" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O47" s="213"/>
       <c r="Q47" t="s">
@@ -43860,7 +43908,7 @@
     </row>
     <row r="50" spans="13:20">
       <c r="M50" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N50" s="2">
         <f>COUNT(U41:U45)</f>
@@ -44031,7 +44079,7 @@
       </c>
       <c r="T1" s="85"/>
       <c r="V1" s="292" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="W1" s="294" t="s">
         <v>26</v>
@@ -44126,7 +44174,7 @@
         <v>46</v>
       </c>
       <c r="N2" s="110" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>93</v>
@@ -44176,10 +44224,10 @@
         <v>92</v>
       </c>
       <c r="AG2" s="298" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AH2" s="110" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI2" s="2" t="s">
         <v>174</v>
@@ -44239,7 +44287,7 @@
         <v>177</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>170</v>
@@ -44253,7 +44301,7 @@
       <c r="S3" s="51"/>
       <c r="T3" s="1"/>
       <c r="V3" s="159" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="W3" s="297" t="s">
         <v>181</v>
@@ -44271,7 +44319,7 @@
         <v>177</v>
       </c>
       <c r="AB3" s="243" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AC3" s="243" t="s">
         <v>170</v>
@@ -44286,10 +44334,10 @@
         <v>92</v>
       </c>
       <c r="AG3" s="298" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AH3" s="110" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI3" s="2" t="s">
         <v>174</v>
@@ -44309,7 +44357,7 @@
     </row>
     <row r="4" spans="1:39">
       <c r="A4" s="159" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B4" s="264" t="s">
         <v>145</v>
@@ -44348,7 +44396,7 @@
         <v>46</v>
       </c>
       <c r="N4" s="110" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>140</v>
@@ -44368,7 +44416,7 @@
         <v>128</v>
       </c>
       <c r="W4" s="297" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="X4" s="243" t="s">
         <v>80</v>
@@ -44407,10 +44455,10 @@
         <v>189</v>
       </c>
       <c r="AJ4" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AK4" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AL4" s="51" t="s">
         <v>92</v>
@@ -44443,7 +44491,7 @@
         <v>74</v>
       </c>
       <c r="I5" s="243" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J5" s="243" t="s">
         <v>143</v>
@@ -44521,7 +44569,7 @@
         <v>74</v>
       </c>
       <c r="I6" s="243" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J6" s="243" t="s">
         <v>143</v>
@@ -44599,7 +44647,7 @@
         <v>93</v>
       </c>
       <c r="I7" s="243" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J7" s="243" t="s">
         <v>59</v>
@@ -44762,7 +44810,7 @@
         <v>171</v>
       </c>
       <c r="R9" s="159" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S9" s="51"/>
       <c r="T9" s="1"/>
@@ -44772,7 +44820,7 @@
         <v>197</v>
       </c>
       <c r="B10" s="264" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C10" s="297" t="s">
         <v>179</v>
@@ -44790,7 +44838,7 @@
         <v>52</v>
       </c>
       <c r="H10" s="243" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I10" s="243" t="s">
         <v>74</v>
@@ -44817,7 +44865,7 @@
         <v>93</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="R10" s="159" t="s">
         <v>140</v>
@@ -44830,7 +44878,7 @@
         <v>198</v>
       </c>
       <c r="B11" s="264" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C11" s="297" t="s">
         <v>179</v>
@@ -44848,7 +44896,7 @@
         <v>52</v>
       </c>
       <c r="H11" s="243" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I11" s="243" t="s">
         <v>74</v>
@@ -44875,7 +44923,7 @@
         <v>93</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="R11" s="159" t="s">
         <v>171</v>
@@ -44906,7 +44954,7 @@
         <v>52</v>
       </c>
       <c r="H12" s="243" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I12" s="243" t="s">
         <v>74</v>
@@ -44933,7 +44981,7 @@
         <v>93</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="R12" s="159" t="s">
         <v>171</v>
@@ -44964,7 +45012,7 @@
         <v>52</v>
       </c>
       <c r="H13" s="243" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I13" s="243" t="s">
         <v>74</v>
@@ -45022,7 +45070,7 @@
         <v>52</v>
       </c>
       <c r="H14" s="243" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I14" s="243" t="s">
         <v>74</v>
@@ -45049,7 +45097,7 @@
         <v>93</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="R14" s="159" t="s">
         <v>171</v>
@@ -45080,7 +45128,7 @@
         <v>52</v>
       </c>
       <c r="H15" s="243" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I15" s="243" t="s">
         <v>74</v>
@@ -45120,7 +45168,7 @@
         <v>203</v>
       </c>
       <c r="B16" s="264" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C16" s="297" t="s">
         <v>179</v>
@@ -45153,7 +45201,7 @@
         <v>54</v>
       </c>
       <c r="M16" s="298" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N16" s="110" t="s">
         <v>99</v>
@@ -45226,7 +45274,7 @@
         <v>143</v>
       </c>
       <c r="R17" s="159" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S17" s="51"/>
       <c r="T17" s="1"/>
@@ -45284,7 +45332,7 @@
         <v>143</v>
       </c>
       <c r="R18" s="159" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S18" s="51"/>
       <c r="T18" s="1"/>
@@ -45294,10 +45342,10 @@
         <v>206</v>
       </c>
       <c r="B19" s="264" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C19" s="297" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D19" s="243" t="s">
         <v>96</v>
@@ -45342,7 +45390,7 @@
         <v>80</v>
       </c>
       <c r="R19" s="159" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S19" s="51"/>
       <c r="T19" s="1"/>
@@ -45400,7 +45448,7 @@
         <v>143</v>
       </c>
       <c r="R20" s="159" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S20" s="51"/>
       <c r="T20" s="1"/>
@@ -45458,7 +45506,7 @@
         <v>46</v>
       </c>
       <c r="R21" s="159" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S21" s="51"/>
       <c r="T21" s="1"/>
@@ -45516,7 +45564,7 @@
         <v>171</v>
       </c>
       <c r="R22" s="159" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S22" s="51"/>
       <c r="T22" s="1"/>
@@ -45585,7 +45633,7 @@
         <v>147</v>
       </c>
       <c r="C24" s="297" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D24" s="243" t="s">
         <v>177</v>
@@ -45633,7 +45681,7 @@
         <v>176</v>
       </c>
       <c r="S24" s="51" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="T24" s="1"/>
     </row>
@@ -45645,7 +45693,7 @@
         <v>149</v>
       </c>
       <c r="C25" s="297" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D25" s="243" t="s">
         <v>177</v>
@@ -45675,7 +45723,7 @@
         <v>54</v>
       </c>
       <c r="M25" s="298" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N25" s="110" t="s">
         <v>143</v>
@@ -45703,7 +45751,7 @@
         <v>145</v>
       </c>
       <c r="C26" s="297" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D26" s="243" t="s">
         <v>177</v>
@@ -45791,7 +45839,7 @@
         <v>54</v>
       </c>
       <c r="M27" s="298" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N27" s="110" t="s">
         <v>46</v>
@@ -45849,7 +45897,7 @@
         <v>54</v>
       </c>
       <c r="M28" s="298" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N28" s="110" t="s">
         <v>87</v>
@@ -45874,7 +45922,7 @@
         <v>216</v>
       </c>
       <c r="B29" s="264" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C29" s="297" t="s">
         <v>179</v>
@@ -45907,7 +45955,7 @@
         <v>171</v>
       </c>
       <c r="M29" s="298" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N29" s="110" t="s">
         <v>143</v>
@@ -45965,7 +46013,7 @@
         <v>171</v>
       </c>
       <c r="M30" s="298" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N30" s="110" t="s">
         <v>46</v>
@@ -45990,7 +46038,7 @@
         <v>218</v>
       </c>
       <c r="B31" s="264" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C31" s="297" t="s">
         <v>179</v>
@@ -46029,7 +46077,7 @@
         <v>171</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>87</v>
@@ -46093,7 +46141,7 @@
         <v>156</v>
       </c>
       <c r="Q32" s="159" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="R32" s="159"/>
       <c r="S32" s="51"/>
@@ -46137,7 +46185,7 @@
         <v>54</v>
       </c>
       <c r="M33" s="298" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N33" s="110" t="s">
         <v>177</v>
@@ -46253,7 +46301,7 @@
         <v>54</v>
       </c>
       <c r="M35" s="298" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N35" s="110" t="s">
         <v>46</v>
@@ -46281,7 +46329,7 @@
         <v>161</v>
       </c>
       <c r="C36" s="297" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D36" s="243" t="s">
         <v>176</v>
@@ -46335,7 +46383,7 @@
         <v>139</v>
       </c>
       <c r="C37" s="297" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D37" s="243" t="s">
         <v>176</v>
@@ -46380,7 +46428,7 @@
         <v>143</v>
       </c>
       <c r="R37" s="159" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S37" s="51"/>
       <c r="T37" s="1"/>
@@ -46438,7 +46486,7 @@
         <v>140</v>
       </c>
       <c r="R38" s="159" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S38" s="51"/>
       <c r="T38" s="1"/>
@@ -46560,7 +46608,7 @@
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>97</v>
@@ -46598,7 +46646,7 @@
         <v>156</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H5" s="1"/>
     </row>
@@ -46635,7 +46683,7 @@
         <v>170</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>162</v>
@@ -46697,7 +46745,7 @@
     </row>
     <row r="13" spans="2:8">
       <c r="B13" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>220</v>
@@ -46706,13 +46754,13 @@
         <v>105</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>189</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -46742,7 +46790,7 @@
         <v>44</v>
       </c>
       <c r="C3" s="251" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D3" s="252"/>
     </row>
@@ -46865,7 +46913,7 @@
         <v>147</v>
       </c>
       <c r="D19" s="257" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="2:4">
@@ -46926,7 +46974,7 @@
         <v>20</v>
       </c>
       <c r="C27" s="260" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D27" s="252"/>
     </row>
@@ -47854,7 +47902,7 @@
       <c r="P7" s="54"/>
       <c r="Q7" s="171"/>
       <c r="R7" s="15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="S7" s="15"/>
       <c r="T7" s="15"/>
@@ -47969,7 +48017,7 @@
         <v>6</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E8" s="30" t="s">
         <v>45</v>
@@ -48275,7 +48323,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E10" s="30" t="s">
         <v>49</v>
@@ -48533,7 +48581,7 @@
         <v>10</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E12" s="30" t="s">
         <v>45</v>
@@ -49541,7 +49589,7 @@
         <v>17</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E19" s="24" t="s">
         <v>49</v>
@@ -49829,7 +49877,7 @@
         <v>19</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E21" s="24" t="s">
         <v>49</v>
@@ -49973,7 +50021,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E22" s="24" t="s">
         <v>45</v>
@@ -50718,7 +50766,7 @@
         <v>42</v>
       </c>
       <c r="AJ27" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="AK27" s="2">
         <f t="shared" si="18"/>
@@ -50768,7 +50816,7 @@
         <v>26</v>
       </c>
       <c r="D28" s="30" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E28" s="30" t="s">
         <v>49</v>
@@ -51030,7 +51078,7 @@
         <v>28</v>
       </c>
       <c r="D30" s="30" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E30" s="30" t="s">
         <v>45</v>
@@ -51244,7 +51292,7 @@
         <v>42</v>
       </c>
       <c r="AJ31" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="AK31" s="2">
         <f t="shared" si="18"/>
@@ -51500,7 +51548,7 @@
         <v>42</v>
       </c>
       <c r="AJ33" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="AK33" s="2">
         <f t="shared" si="18"/>
@@ -51677,7 +51725,7 @@
         <v>33</v>
       </c>
       <c r="D35" s="73" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E35" s="30" t="s">
         <v>45</v>
@@ -51701,7 +51749,7 @@
         <v>254</v>
       </c>
       <c r="L35" s="53" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M35" s="15"/>
       <c r="N35" s="15"/>
@@ -51768,7 +51816,7 @@
         <v>34</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E36" s="24" t="s">
         <v>45</v>
@@ -51807,7 +51855,7 @@
         <v>7138</v>
       </c>
       <c r="X36" s="150" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y36" s="153">
         <f t="shared" si="0"/>
@@ -51896,7 +51944,7 @@
         <v>8257</v>
       </c>
       <c r="X37" s="150" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y37" s="153">
         <f t="shared" si="0"/>
@@ -51946,7 +51994,7 @@
         <v>36</v>
       </c>
       <c r="D38" s="73" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E38" s="24" t="s">
         <v>49</v>
@@ -52198,13 +52246,13 @@
     </row>
     <row r="41" spans="1:45" ht="17.5" customHeight="1" thickBot="1">
       <c r="A41" s="98" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B41" s="128">
         <v>45399</v>
       </c>
       <c r="C41" s="103" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D41" s="103" t="s">
         <v>282</v>
@@ -52285,7 +52333,7 @@
     </row>
     <row r="42" spans="1:45">
       <c r="A42" s="98" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B42" s="128">
         <v>45462</v>
@@ -52368,7 +52416,7 @@
     </row>
     <row r="43" spans="1:45" ht="17.5" customHeight="1" thickBot="1">
       <c r="A43" s="110" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B43" s="198">
         <v>45490</v>
@@ -52449,7 +52497,7 @@
     </row>
     <row r="44" spans="1:45">
       <c r="A44" s="110" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B44" s="198">
         <v>45525</v>
@@ -52479,7 +52527,7 @@
     </row>
     <row r="45" spans="1:45">
       <c r="A45" s="110" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B45" s="198">
         <v>45532</v>
@@ -52509,7 +52557,7 @@
     </row>
     <row r="46" spans="1:45" ht="17.5" customHeight="1" thickBot="1">
       <c r="A46" s="100" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B46" s="112">
         <v>45626</v>
@@ -52605,7 +52653,7 @@
     </row>
     <row r="50" spans="12:19">
       <c r="L50" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M50" s="2">
         <f>COUNT(V41:V45)</f>
@@ -52766,7 +52814,7 @@
         <v>27</v>
       </c>
       <c r="S1" s="161" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="T1" s="162" t="s">
         <v>26</v>
@@ -52837,7 +52885,7 @@
         <v>268</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>74</v>
@@ -52870,7 +52918,7 @@
         <v>264</v>
       </c>
       <c r="S2" s="159" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="T2" s="153" t="s">
         <v>179</v>
@@ -52888,7 +52936,7 @@
         <v>281</v>
       </c>
       <c r="Y2" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Z2" s="5" t="s">
         <v>170</v>
@@ -52941,7 +52989,7 @@
         <v>279</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>74</v>
@@ -52989,7 +53037,7 @@
     </row>
     <row r="4" spans="1:35">
       <c r="A4" s="159" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B4" s="153" t="s">
         <v>180</v>
@@ -53007,7 +53055,7 @@
         <v>279</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>74</v>
@@ -53089,7 +53137,7 @@
         <v>71</v>
       </c>
       <c r="M5" s="110" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>170</v>
@@ -53143,7 +53191,7 @@
         <v>279</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>74</v>
@@ -53173,7 +53221,7 @@
         <v>271</v>
       </c>
       <c r="Q6" s="51" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S6" s="159" t="s">
         <v>130</v>
@@ -53215,7 +53263,7 @@
         <v>268</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>74</v>
@@ -53338,7 +53386,7 @@
         <v>268</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>74</v>
@@ -53386,7 +53434,7 @@
         <v>105</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>279</v>
@@ -53439,7 +53487,7 @@
         <v>105</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>279</v>
@@ -53492,7 +53540,7 @@
         <v>278</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>279</v>
@@ -53628,7 +53676,7 @@
         <v>143</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q14" s="51" t="s">
         <v>97</v>
@@ -53654,7 +53702,7 @@
         <v>268</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>170</v>
@@ -53707,7 +53755,7 @@
         <v>281</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>170</v>
@@ -53813,7 +53861,7 @@
         <v>281</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>170</v>
@@ -53866,7 +53914,7 @@
         <v>281</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>170</v>
@@ -53928,7 +53976,7 @@
         <v>171</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K20" s="5" t="s">
         <v>54</v>
@@ -53967,7 +54015,7 @@
         <v>177</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>268</v>
@@ -53991,7 +54039,7 @@
         <v>279</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>182</v>
@@ -54018,7 +54066,7 @@
         <v>177</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>279</v>
@@ -54071,7 +54119,7 @@
         <v>105</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>268</v>
@@ -54132,7 +54180,7 @@
         <v>93</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K24" s="5" t="s">
         <v>46</v>
@@ -54195,7 +54243,7 @@
         <v>272</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>87</v>
@@ -54236,7 +54284,7 @@
         <v>272</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K26" s="5" t="s">
         <v>46</v>
@@ -54303,7 +54351,7 @@
         <v>54</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q27" s="51" t="s">
         <v>170</v>
@@ -54412,7 +54460,7 @@
         <v>93</v>
       </c>
       <c r="Q29" s="51" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -54450,7 +54498,7 @@
         <v>46</v>
       </c>
       <c r="L30" s="155" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M30" s="110" t="s">
         <v>143</v>
@@ -54465,7 +54513,7 @@
         <v>279</v>
       </c>
       <c r="Q30" s="51" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -54482,7 +54530,7 @@
         <v>277</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>279</v>
@@ -54512,7 +54560,7 @@
         <v>268</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>54</v>
@@ -54535,7 +54583,7 @@
         <v>277</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>281</v>
@@ -54588,7 +54636,7 @@
         <v>277</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>281</v>
@@ -54642,7 +54690,7 @@
         <v>268</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>279</v>
@@ -54669,7 +54717,7 @@
         <v>71</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P34" s="2" t="s">
         <v>189</v>
@@ -54695,7 +54743,7 @@
         <v>105</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>279</v>
@@ -54725,7 +54773,7 @@
         <v>281</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q35" s="51" t="s">
         <v>261</v>
@@ -54748,7 +54796,7 @@
         <v>105</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>279</v>

--- a/인천 2026 기록.xlsx
+++ b/인천 2026 기록.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://familyinter-my.sharepoint.com/personal/hwlee_familyinter_onmicrosoft_com/Documents/바탕 화면/프로젝트300/대시보드/인천 대시보드/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1159" documentId="11_BC30CAD5959CD43F2C1D107F60E94D8BC2537F23" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80DA0A5B-909E-47B6-A93C-EBB181BA06E3}"/>
+  <xr:revisionPtr revIDLastSave="1182" documentId="11_4EE6FFD7959CA43523F9517F60E94D8B825D3B4E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{029DD364-2BED-4D04-BD15-6CF5AA881FB7}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1770" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 토탈" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6093" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6111" uniqueCount="395">
   <si>
     <t>리그</t>
   </si>
@@ -240,7 +240,7 @@
     <t>총합</t>
   </si>
   <si>
-    <t>강원</t>
+    <t>전북</t>
   </si>
   <si>
     <t>수</t>
@@ -261,7 +261,7 @@
     <t>팀명</t>
   </si>
   <si>
-    <t>제주</t>
+    <t>강원</t>
   </si>
   <si>
     <t>안양</t>
@@ -273,9 +273,6 @@
     <t>제르소</t>
   </si>
   <si>
-    <t>전북</t>
-  </si>
-  <si>
     <t>김천</t>
   </si>
   <si>
@@ -283,6 +280,9 @@
   </si>
   <si>
     <t>최철준</t>
+  </si>
+  <si>
+    <t>제주</t>
   </si>
   <si>
     <t>송민석</t>
@@ -1291,7 +1291,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>K리그1 2026 리그순위   (2026-10-11 - 31R 종료)</t>
+    <t>K리그1 2026 리그순위   (2026-10-17 - 32R 종료)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -5593,11 +5593,11 @@
       </c>
       <c r="Y3" s="332">
         <f t="shared" ref="Y3:Y43" si="0">Z3+AA3</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z3" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X3)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA3" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X3)</f>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="AB3" s="333">
         <f t="shared" ref="AB3:AB43" si="1">COUNTIF($M$3:$P$40,$X3)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC3" s="334">
         <f t="shared" ref="AC3:AC43" si="2">COUNTIF($Q$3:$T$40,$X3)</f>
@@ -5613,15 +5613,15 @@
       </c>
       <c r="AD3" s="335">
         <f t="shared" ref="AD3:AD43" si="3">AB3+AC3</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE3" s="332">
         <f t="shared" ref="AE3:AE43" si="4">AF3+AG3</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF3" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X3)+Z3</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG3" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X3)+AA3</f>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AH3" s="333">
         <f t="shared" ref="AH3:AH43" si="5">COUNTIF($M$3:$P$41,$X3)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI3" s="334">
         <f t="shared" ref="AI3:AI43" si="6">COUNTIF($Q$3:$T$41,$X3)</f>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="AJ3" s="335">
         <f t="shared" ref="AJ3:AJ43" si="7">AH3+AI3</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM3" s="2" t="s">
         <v>45</v>
@@ -5724,29 +5724,29 @@
         <v>341</v>
       </c>
       <c r="BK3" s="469">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BL3" s="469">
         <v>20</v>
       </c>
       <c r="BM3" s="469">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BN3" s="469">
         <v>6</v>
       </c>
       <c r="BO3" s="469">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="BP3" s="469">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BQ3" s="469">
         <f>BO3-BP3</f>
         <v>32</v>
       </c>
       <c r="BR3" s="469">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:77">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="Y4" s="332">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z4" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X4)</f>
@@ -5813,7 +5813,7 @@
       </c>
       <c r="AA4" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X4)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB4" s="333">
         <f t="shared" si="1"/>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="AE4" s="332">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF4" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X4)+Z4</f>
@@ -5837,7 +5837,7 @@
       </c>
       <c r="AG4" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X4)+AA4</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH4" s="333">
         <f t="shared" si="5"/>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="AN4" s="2">
         <f>SUM(AO4:AQ4)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO4" s="243">
         <f t="shared" si="8"/>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="AP4" s="58">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ4" s="342">
         <f t="shared" si="8"/>
@@ -5872,19 +5872,19 @@
       </c>
       <c r="AR4" s="352">
         <f>AO4*3+AP4</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS4" s="23">
         <f>IFERROR(AO4/AN4,0)</f>
-        <v>0.33333333333333331</v>
+        <v>0.3125</v>
       </c>
       <c r="AT4" s="2">
         <f>SUMIFS($G$3:$G$40,$A$3:$A$40,"K리그",$F$3:$F$40,$AM4)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU4" s="2">
         <f>SUMIFS($H$3:$H$40,$A$3:$A$40,"K리그",$F$3:$F$40,$AM4)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV4" s="2">
         <f>AT4-AU4</f>
@@ -5892,15 +5892,15 @@
       </c>
       <c r="AW4" s="434">
         <f>IFERROR(AR4/AN4,0)</f>
-        <v>1.3333333333333333</v>
+        <v>1.3125</v>
       </c>
       <c r="AX4" s="434">
         <f>IFERROR(AT4/AN4,0)</f>
-        <v>1.2666666666666666</v>
+        <v>1.25</v>
       </c>
       <c r="AY4" s="434">
         <f>IFERROR(AU4/AN4,0)</f>
-        <v>1.1333333333333333</v>
+        <v>1.125</v>
       </c>
       <c r="BA4" s="464" t="s">
         <v>53</v>
@@ -5936,10 +5936,10 @@
         <v>360</v>
       </c>
       <c r="BK4" s="470">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BL4" s="470">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BM4" s="470">
         <v>5</v>
@@ -5948,17 +5948,17 @@
         <v>12</v>
       </c>
       <c r="BO4" s="470">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BP4" s="470">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BQ4" s="470">
         <f>BO4-BP4</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BR4" s="470">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:77">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="AN5" s="337">
         <f>SUM(AN3:AN4)</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AO5" s="337">
         <f>SUM(AO3:AO4)</f>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AP5" s="337">
         <f>SUM(AP3:AP4)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ5" s="337">
         <f>SUM(AQ3:AQ4)</f>
@@ -6078,19 +6078,19 @@
       </c>
       <c r="AR5" s="337">
         <f>SUM(AR3:AR4)</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AS5" s="349">
         <f>IFERROR(AO5/AN5,0)</f>
-        <v>0.35483870967741937</v>
+        <v>0.34375</v>
       </c>
       <c r="AT5" s="337">
         <f>SUM(AT3:AT4)</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AU5" s="337">
         <f>SUM(AU3:AU4)</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AV5" s="337">
         <f>SUM(AV3:AV4)</f>
@@ -6098,22 +6098,22 @@
       </c>
       <c r="AW5" s="435">
         <f>IFERROR(AR5/AN5,0)</f>
-        <v>1.3548387096774193</v>
+        <v>1.34375</v>
       </c>
       <c r="AX5" s="435">
         <f>IFERROR(AT5/AN5,0)</f>
-        <v>1.2580645161290323</v>
+        <v>1.25</v>
       </c>
       <c r="AY5" s="435">
         <f>IFERROR(AU5/AN5,0)</f>
-        <v>1.064516129032258</v>
+        <v>1.0625</v>
       </c>
       <c r="BA5" s="464" t="s">
         <v>58</v>
       </c>
       <c r="BB5" s="464">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC5" s="243">
         <f t="shared" si="10"/>
@@ -6121,7 +6121,7 @@
       </c>
       <c r="BD5" s="465">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE5" s="342">
         <f t="shared" si="10"/>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="BF5" s="89">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BG5" s="11">
         <f t="shared" si="12"/>
@@ -6139,32 +6139,32 @@
         <v>3</v>
       </c>
       <c r="BJ5" s="470" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="BK5" s="470">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BL5" s="470">
+        <v>12</v>
+      </c>
+      <c r="BM5" s="470">
         <v>11</v>
       </c>
-      <c r="BM5" s="470">
-        <v>13</v>
-      </c>
       <c r="BN5" s="470">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BO5" s="470">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BP5" s="470">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BQ5" s="470">
         <f>BO5-BP5</f>
         <v>10</v>
       </c>
       <c r="BR5" s="470">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:77">
@@ -6221,11 +6221,11 @@
       </c>
       <c r="Y6" s="332">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z6" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X6)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA6" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X6)</f>
@@ -6245,11 +6245,11 @@
       </c>
       <c r="AE6" s="332">
         <f t="shared" si="4"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF6" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X6)+Z6</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG6" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X6)+AA6</f>
@@ -6328,32 +6328,32 @@
         <v>4</v>
       </c>
       <c r="BJ6" s="479" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="BK6" s="479">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BL6" s="479">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BM6" s="479">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BN6" s="479">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BO6" s="479">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="BP6" s="479">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="BQ6" s="479">
         <f>BO6-BP6</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BR6" s="479">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:77">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="Y7" s="332">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Z7" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X7)</f>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="AA7" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X7)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB7" s="333">
         <f t="shared" si="1"/>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AE7" s="332">
         <f t="shared" si="4"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AF7" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X7)+Z7</f>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="AG7" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X7)+AA7</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH7" s="333">
         <f t="shared" si="5"/>
@@ -6456,7 +6456,7 @@
         <v>42</v>
       </c>
       <c r="AM7" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="AN7" s="89">
         <f t="shared" ref="AN7:AN17" si="13">SUM(AO7:AQ7)</f>
@@ -6525,32 +6525,32 @@
         <v>5</v>
       </c>
       <c r="BJ7" s="479" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="BK7" s="479">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BL7" s="479">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BM7" s="479">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BN7" s="479">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BO7" s="479">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="BP7" s="479">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="BQ7" s="479">
         <f>BO7-BP7</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BR7" s="479">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:77">
@@ -6593,7 +6593,7 @@
       <c r="O8" s="270"/>
       <c r="P8" s="271"/>
       <c r="Q8" s="272" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="R8" s="270"/>
       <c r="S8" s="270"/>
@@ -6602,14 +6602,14 @@
         <v>8239</v>
       </c>
       <c r="V8" s="274" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="X8" s="327" t="s">
         <v>51</v>
       </c>
       <c r="Y8" s="332">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Z8" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X8)</f>
@@ -6617,7 +6617,7 @@
       </c>
       <c r="AA8" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X8)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB8" s="333">
         <f t="shared" si="1"/>
@@ -6633,7 +6633,7 @@
       </c>
       <c r="AE8" s="332">
         <f t="shared" si="4"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AF8" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X8)+Z8</f>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="AG8" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X8)+AA8</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH8" s="333">
         <f t="shared" si="5"/>
@@ -6698,7 +6698,7 @@
         <v>-2</v>
       </c>
       <c r="BA8" s="464" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BB8" s="464">
         <f t="shared" si="9"/>
@@ -6728,13 +6728,13 @@
         <v>6</v>
       </c>
       <c r="BJ8" s="479" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="BK8" s="479">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BL8" s="479">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BM8" s="479">
         <v>10</v>
@@ -6743,17 +6743,17 @@
         <v>10</v>
       </c>
       <c r="BO8" s="479">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="BP8" s="479">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BQ8" s="479">
         <f>BO8-BP8</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="BR8" s="479">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:77">
@@ -6806,15 +6806,15 @@
         <v>76</v>
       </c>
       <c r="X9" s="327" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y9" s="332">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Z9" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X9)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA9" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X9)</f>
@@ -6834,11 +6834,11 @@
       </c>
       <c r="AE9" s="332">
         <f t="shared" si="4"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF9" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X9)+Z9</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG9" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X9)+AA9</f>
@@ -6860,7 +6860,7 @@
         <v>42</v>
       </c>
       <c r="AM9" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AN9" s="89">
         <f t="shared" si="13"/>
@@ -6932,29 +6932,29 @@
         <v>394</v>
       </c>
       <c r="BK9" s="471">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BL9" s="471">
         <v>11</v>
       </c>
       <c r="BM9" s="471">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BN9" s="471">
         <v>11</v>
       </c>
       <c r="BO9" s="471">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BP9" s="471">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BQ9" s="471">
         <f>BO9-BP9</f>
         <v>6</v>
       </c>
       <c r="BR9" s="471">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:77">
@@ -7133,13 +7133,13 @@
         <v>355</v>
       </c>
       <c r="BK10" s="479">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BL10" s="479">
         <v>10</v>
       </c>
       <c r="BM10" s="479">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN10" s="479">
         <v>10</v>
@@ -7155,7 +7155,7 @@
         <v>-8</v>
       </c>
       <c r="BR10" s="479">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:77">
@@ -7190,7 +7190,7 @@
       <c r="K11" s="266"/>
       <c r="L11" s="269"/>
       <c r="M11" s="246" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N11" s="270" t="s">
         <v>59</v>
@@ -7212,11 +7212,11 @@
       </c>
       <c r="Y11" s="332">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Z11" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X11)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA11" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X11)</f>
@@ -7236,11 +7236,11 @@
       </c>
       <c r="AE11" s="332">
         <f t="shared" si="4"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AF11" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X11)+Z11</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG11" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X11)+AA11</f>
@@ -7334,13 +7334,13 @@
         <v>349</v>
       </c>
       <c r="BK11" s="479">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BL11" s="479">
         <v>11</v>
       </c>
       <c r="BM11" s="479">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BN11" s="479">
         <v>13</v>
@@ -7356,7 +7356,7 @@
         <v>-9</v>
       </c>
       <c r="BR11" s="479">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:77">
@@ -7463,11 +7463,11 @@
         <v>42</v>
       </c>
       <c r="AM12" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="AN12" s="89">
         <f t="shared" si="13"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO12" s="243">
         <f t="shared" si="14"/>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="AP12" s="243">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ12" s="351">
         <f t="shared" si="16"/>
@@ -7483,16 +7483,16 @@
       </c>
       <c r="AR12" s="352">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS12" s="23"/>
       <c r="AT12" s="2">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU12" s="2">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV12" s="2">
         <f t="shared" si="20"/>
@@ -7532,29 +7532,29 @@
         <v>358</v>
       </c>
       <c r="BK12" s="479">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BL12" s="479">
         <v>5</v>
       </c>
       <c r="BM12" s="479">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BN12" s="479">
         <v>8</v>
       </c>
       <c r="BO12" s="479">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BP12" s="479">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="BQ12" s="479">
         <f>BO12-BP12</f>
         <v>-7</v>
       </c>
       <c r="BR12" s="479">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:77">
@@ -7729,7 +7729,7 @@
         <v>362</v>
       </c>
       <c r="BK13" s="479">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BL13" s="479">
         <v>7</v>
@@ -7738,17 +7738,17 @@
         <v>11</v>
       </c>
       <c r="BN13" s="479">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BO13" s="479">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BP13" s="479">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BQ13" s="479">
         <f>BO13-BP13</f>
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="BR13" s="479">
         <v>32</v>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="Y14" s="332">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z14" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X14)</f>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="AA14" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X14)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB14" s="333">
         <f t="shared" si="1"/>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="AE14" s="332">
         <f t="shared" si="4"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF14" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X14)+Z14</f>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="AG14" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X14)+AA14</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH14" s="333">
         <f t="shared" si="5"/>
@@ -7924,7 +7924,7 @@
         <v>345</v>
       </c>
       <c r="BK14" s="472">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BL14" s="472">
         <v>2</v>
@@ -7933,17 +7933,17 @@
         <v>12</v>
       </c>
       <c r="BN14" s="472">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BO14" s="472">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BP14" s="472">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="BQ14" s="472">
         <f>BO14-BP14</f>
-        <v>-41</v>
+        <v>-42</v>
       </c>
       <c r="BR14" s="472">
         <v>18</v>
@@ -7991,7 +7991,7 @@
       </c>
       <c r="P15" s="368"/>
       <c r="Q15" s="363" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="R15" s="320"/>
       <c r="S15" s="320"/>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BB15" s="466">
         <f>SUM(BB3:BB14)</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BC15" s="243">
         <f>SUM(BC3:BC14)</f>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BD15" s="467">
         <f>SUM(BD3:BD14)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BE15" s="468">
         <f>SUM(BE3:BE14)</f>
@@ -8114,11 +8114,11 @@
       </c>
       <c r="BF15" s="89">
         <f>SUM(BF3:BF14)</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="BG15" s="11">
         <f t="shared" si="12"/>
-        <v>0.35483870967741937</v>
+        <v>0.34375</v>
       </c>
       <c r="BI15" s="476" t="s">
         <v>91</v>
@@ -8233,7 +8233,7 @@
         <v>42</v>
       </c>
       <c r="AM16" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="AN16" s="89">
         <f t="shared" si="13"/>
@@ -8563,7 +8563,7 @@
         <v>10616</v>
       </c>
       <c r="V19" s="312" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="X19" s="327" t="s">
         <v>95</v>
@@ -8770,11 +8770,11 @@
       </c>
       <c r="Y21" s="332">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z21" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X21)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA21" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X21)</f>
@@ -8794,11 +8794,11 @@
       </c>
       <c r="AE21" s="332">
         <f t="shared" si="4"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF21" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X21)+Z21</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG21" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X21)+AA21</f>
@@ -8864,18 +8864,18 @@
         <v>8623</v>
       </c>
       <c r="V22" s="312" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="X22" s="329" t="s">
         <v>89</v>
       </c>
       <c r="Y22" s="332">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Z22" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X22)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA22" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X22)</f>
@@ -8895,11 +8895,11 @@
       </c>
       <c r="AE22" s="332">
         <f t="shared" si="4"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF22" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X22)+Z22</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG22" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X22)+AA22</f>
@@ -8978,11 +8978,11 @@
       </c>
       <c r="Y23" s="332">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z23" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X23)</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA23" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X23)</f>
@@ -9002,11 +9002,11 @@
       </c>
       <c r="AE23" s="332">
         <f t="shared" si="4"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF23" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X23)+Z23</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG23" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X23)+AA23</f>
@@ -9075,11 +9075,11 @@
       </c>
       <c r="Y24" s="332">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Z24" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X24)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA24" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X24)</f>
@@ -9099,11 +9099,11 @@
       </c>
       <c r="AE24" s="332">
         <f t="shared" si="4"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AF24" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X24)+Z24</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG24" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X24)+AA24</f>
@@ -9656,7 +9656,7 @@
         <v>102</v>
       </c>
       <c r="R30" s="270" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="S30" s="270"/>
       <c r="T30" s="270"/>
@@ -9974,11 +9974,11 @@
       </c>
       <c r="Y33" s="332">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z33" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X33)</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA33" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X33)</f>
@@ -9998,11 +9998,11 @@
       </c>
       <c r="AE33" s="332">
         <f t="shared" si="4"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF33" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X33)+Z33</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG33" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X33)+AA33</f>
@@ -10040,13 +10040,21 @@
       <c r="F34" s="267" t="s">
         <v>346</v>
       </c>
-      <c r="G34" s="266"/>
-      <c r="H34" s="266"/>
-      <c r="I34" s="380"/>
+      <c r="G34" s="266">
+        <v>1</v>
+      </c>
+      <c r="H34" s="266">
+        <v>1</v>
+      </c>
+      <c r="I34" s="380" t="s">
+        <v>350</v>
+      </c>
       <c r="J34" s="374"/>
       <c r="K34" s="266"/>
       <c r="L34" s="269"/>
-      <c r="M34" s="246"/>
+      <c r="M34" s="246" t="s">
+        <v>46</v>
+      </c>
       <c r="N34" s="270"/>
       <c r="O34" s="270"/>
       <c r="P34" s="271"/>
@@ -10054,8 +10062,12 @@
       <c r="R34" s="270"/>
       <c r="S34" s="270"/>
       <c r="T34" s="270"/>
-      <c r="U34" s="273"/>
-      <c r="V34" s="274"/>
+      <c r="U34" s="273">
+        <v>5558</v>
+      </c>
+      <c r="V34" s="274" t="s">
+        <v>58</v>
+      </c>
       <c r="X34" s="330" t="s">
         <v>108</v>
       </c>
@@ -10640,11 +10652,11 @@
       </c>
       <c r="Y41" s="332">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z41" s="474">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X41)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA41" s="474">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X41)</f>
@@ -10664,11 +10676,11 @@
       </c>
       <c r="AE41" s="475">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF41" s="475">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X41)+Z41</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG41" s="475">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X41)+AA41</f>
@@ -10700,11 +10712,11 @@
       </c>
       <c r="Y42" s="332">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z42" s="474">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X42)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA42" s="474">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X42)</f>
@@ -10724,11 +10736,11 @@
       </c>
       <c r="AE42" s="475">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF42" s="475">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X42)+Z42</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG42" s="475">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X42)+AA42</f>
@@ -10830,15 +10842,15 @@
       </c>
       <c r="N44" s="2">
         <f>COUNT(U3:U40)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O44" s="96">
         <f>SUMIFS(U3:U41,A3:A41,M44)</f>
-        <v>165449</v>
+        <v>171007</v>
       </c>
       <c r="P44" s="96">
         <f>O44/N44</f>
-        <v>9732.2941176470595</v>
+        <v>9500.3888888888887</v>
       </c>
       <c r="Q44" s="136">
         <v>19</v>
@@ -10851,7 +10863,7 @@
       </c>
       <c r="T44" s="165">
         <f>(P44-S44)/S44</f>
-        <v>-4.3395369756680527E-2</v>
+        <v>-6.6189750292863517E-2</v>
       </c>
     </row>
     <row r="45" spans="1:36">
@@ -11445,7 +11457,7 @@
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C13" s="2">
         <v>2</v>
@@ -11678,7 +11690,7 @@
     </row>
     <row r="22" spans="2:11">
       <c r="B22" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C22" s="2">
         <v>3</v>
@@ -11774,7 +11786,7 @@
     </row>
     <row r="25" spans="2:11">
       <c r="B25" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C25" s="2">
         <v>3</v>
@@ -11966,7 +11978,7 @@
     </row>
     <row r="31" spans="2:11">
       <c r="B31" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C31" s="2">
         <v>4</v>
@@ -12195,7 +12207,7 @@
     </row>
     <row r="40" spans="2:11">
       <c r="B40" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C40" s="2">
         <v>4</v>
@@ -12291,7 +12303,7 @@
     </row>
     <row r="43" spans="2:11">
       <c r="B43" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C43" s="2">
         <v>4</v>
@@ -12323,7 +12335,7 @@
     </row>
     <row r="44" spans="2:11">
       <c r="B44" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C44" s="2">
         <v>4</v>
@@ -12483,7 +12495,7 @@
     </row>
     <row r="49" spans="2:11">
       <c r="B49" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C49" s="2">
         <v>3</v>
@@ -12744,7 +12756,7 @@
     </row>
     <row r="59" spans="2:11">
       <c r="B59" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C59" s="2">
         <v>4</v>
@@ -12808,7 +12820,7 @@
     </row>
     <row r="61" spans="2:11">
       <c r="B61" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C61" s="2">
         <v>3</v>
@@ -12840,7 +12852,7 @@
     </row>
     <row r="62" spans="2:11">
       <c r="B62" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C62" s="2">
         <v>3</v>
@@ -13325,7 +13337,7 @@
     </row>
     <row r="79" spans="2:11">
       <c r="B79" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C79" s="2">
         <v>0</v>
@@ -13453,7 +13465,7 @@
     </row>
     <row r="83" spans="2:11">
       <c r="B83" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C83" s="2">
         <v>0</v>
@@ -13517,7 +13529,7 @@
     </row>
     <row r="85" spans="2:11">
       <c r="B85" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C85" s="2">
         <v>0</v>
@@ -13549,7 +13561,7 @@
     </row>
     <row r="86" spans="2:11">
       <c r="B86" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C86" s="2">
         <v>0</v>
@@ -13915,7 +13927,7 @@
         <v>32</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M4" s="15" t="s">
         <v>300</v>
@@ -14024,7 +14036,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E5" s="30" t="s">
         <v>45</v>
@@ -14401,7 +14413,7 @@
         <v>6</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E8" s="30" t="s">
         <v>49</v>
@@ -14520,7 +14532,7 @@
         <v>7</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E9" s="30" t="s">
         <v>49</v>
@@ -15178,7 +15190,7 @@
         <v>12</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E14" s="24" t="s">
         <v>49</v>
@@ -15270,7 +15282,7 @@
         <v>13</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E15" s="24" t="s">
         <v>45</v>
@@ -15430,7 +15442,7 @@
         <v>6663</v>
       </c>
       <c r="X16" s="70" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y16" s="81">
         <f t="shared" si="0"/>
@@ -16139,7 +16151,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E22" s="24" t="s">
         <v>45</v>
@@ -16722,7 +16734,7 @@
         <v>25</v>
       </c>
       <c r="D27" s="30" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E27" s="30" t="s">
         <v>49</v>
@@ -16902,7 +16914,7 @@
         <v>71</v>
       </c>
       <c r="R28" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="S28" s="15" t="s">
         <v>46</v>
@@ -17317,7 +17329,7 @@
         <v>42</v>
       </c>
       <c r="AD31" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="AE31" s="2">
         <f t="shared" si="17"/>
@@ -17367,7 +17379,7 @@
         <v>30</v>
       </c>
       <c r="D32" s="30" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E32" s="30" t="s">
         <v>45</v>
@@ -17391,7 +17403,7 @@
         <v>31</v>
       </c>
       <c r="L32" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M32" s="15" t="s">
         <v>300</v>
@@ -17480,7 +17492,7 @@
         <v>31</v>
       </c>
       <c r="D33" s="30" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E33" s="30" t="s">
         <v>49</v>
@@ -17537,7 +17549,7 @@
         <v>42</v>
       </c>
       <c r="AD33" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="AE33" s="2">
         <f t="shared" si="17"/>
@@ -17648,7 +17660,7 @@
         <v>42</v>
       </c>
       <c r="AD34" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="AE34" s="2">
         <f t="shared" si="17"/>
@@ -18015,7 +18027,7 @@
         <v>36</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E38" s="24" t="s">
         <v>45</v>
@@ -18969,7 +18981,7 @@
         <v>115</v>
       </c>
       <c r="AD47" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="AE47" s="2">
         <f t="shared" si="17"/>
@@ -19127,7 +19139,7 @@
         <v>130</v>
       </c>
       <c r="D50" s="104" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E50" s="104" t="s">
         <v>49</v>
@@ -19645,7 +19657,7 @@
         <v>32</v>
       </c>
       <c r="K4" s="53" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L4" s="15" t="s">
         <v>300</v>
@@ -19744,7 +19756,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D5" s="30" t="s">
         <v>45</v>
@@ -20066,7 +20078,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D8" s="30" t="s">
         <v>49</v>
@@ -20184,7 +20196,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D9" s="30" t="s">
         <v>49</v>
@@ -20764,7 +20776,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D14" s="24" t="s">
         <v>49</v>
@@ -20875,7 +20887,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D15" s="24" t="s">
         <v>45</v>
@@ -21025,7 +21037,7 @@
       <c r="O16" s="61"/>
       <c r="P16" s="59"/>
       <c r="S16" s="70" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="T16" s="81">
         <f t="shared" si="0"/>
@@ -21575,7 +21587,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D22" s="24" t="s">
         <v>45</v>
@@ -22022,7 +22034,7 @@
         <v>25</v>
       </c>
       <c r="C27" s="30" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D27" s="30" t="s">
         <v>49</v>
@@ -22162,7 +22174,7 @@
         <v>71</v>
       </c>
       <c r="O28" s="56" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P28" s="54" t="s">
         <v>46</v>
@@ -22476,7 +22488,7 @@
         <v>3</v>
       </c>
       <c r="Y31" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="Z31" s="2">
         <f t="shared" si="14"/>
@@ -22523,7 +22535,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="30" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D32" s="30" t="s">
         <v>45</v>
@@ -22547,7 +22559,7 @@
         <v>31</v>
       </c>
       <c r="K32" s="53" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L32" s="15" t="s">
         <v>300</v>
@@ -22623,7 +22635,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="30" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D33" s="30" t="s">
         <v>49</v>
@@ -22672,7 +22684,7 @@
         <v>0</v>
       </c>
       <c r="Y33" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="Z33" s="2">
         <f t="shared" si="14"/>
@@ -22770,7 +22782,7 @@
         <v>1</v>
       </c>
       <c r="Y34" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="Z34" s="2">
         <f t="shared" si="14"/>
@@ -23101,7 +23113,7 @@
         <v>36</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D38" s="24" t="s">
         <v>45</v>
@@ -24752,7 +24764,7 @@
       <c r="S16" s="61"/>
       <c r="T16" s="59"/>
       <c r="W16" s="70" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X16" s="81">
         <f t="shared" si="0"/>
@@ -26692,7 +26704,7 @@
         <v>130</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D5" s="30" t="s">
         <v>49</v>
@@ -27497,7 +27509,7 @@
       <c r="S16" s="61"/>
       <c r="T16" s="59"/>
       <c r="W16" s="70" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X16" s="81">
         <f t="shared" si="0"/>
@@ -28522,7 +28534,7 @@
         <v>0</v>
       </c>
       <c r="AC32" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="AD32" s="2">
         <f>SUM(AE32:AG32)</f>
@@ -29362,7 +29374,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="73" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D5" s="73" t="s">
         <v>49</v>
@@ -29586,7 +29598,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="73" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D7" s="73" t="s">
         <v>45</v>
@@ -29991,7 +30003,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="73" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D11" s="73" t="s">
         <v>45</v>
@@ -30012,7 +30024,7 @@
         <v>46</v>
       </c>
       <c r="L11" s="76" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M11" s="76"/>
       <c r="N11" s="76"/>
@@ -30127,7 +30139,7 @@
       <c r="I12" s="73"/>
       <c r="J12" s="73"/>
       <c r="K12" s="75" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L12" s="76" t="s">
         <v>46</v>
@@ -30227,7 +30239,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="73" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D13" s="73" t="s">
         <v>45</v>
@@ -30255,7 +30267,7 @@
       <c r="S13" s="79"/>
       <c r="T13" s="77"/>
       <c r="W13" s="70" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X13" s="51">
         <f t="shared" si="0"/>
@@ -30263,7 +30275,7 @@
       </c>
       <c r="Y13" s="1"/>
       <c r="Z13" s="70" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AA13" s="51">
         <f t="shared" si="1"/>
@@ -30734,7 +30746,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="73" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D18" s="73" t="s">
         <v>49</v>
@@ -30850,7 +30862,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="73" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D19" s="73" t="s">
         <v>45</v>
@@ -30990,7 +31002,7 @@
       <c r="I20" s="73"/>
       <c r="J20" s="73"/>
       <c r="K20" s="75" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L20" s="76"/>
       <c r="M20" s="76"/>
@@ -31257,7 +31269,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D23" s="24" t="s">
         <v>49</v>
@@ -31310,7 +31322,7 @@
         <v>22</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D24" s="24" t="s">
         <v>49</v>
@@ -31622,7 +31634,7 @@
       <c r="I27" s="30"/>
       <c r="J27" s="30"/>
       <c r="K27" s="53" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L27" s="15" t="s">
         <v>300</v>
@@ -31710,7 +31722,7 @@
         <v>28</v>
       </c>
       <c r="C28" s="30" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D28" s="30" t="s">
         <v>45</v>
@@ -31840,7 +31852,7 @@
         <v>0</v>
       </c>
       <c r="AD29" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="AE29" s="2">
         <f t="shared" ref="AE29:AE39" si="13">SUM(AF29:AH29)</f>
@@ -31977,7 +31989,7 @@
         <v>29</v>
       </c>
       <c r="C31" s="30" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D31" s="30" t="s">
         <v>45</v>
@@ -32065,7 +32077,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="30" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D32" s="30" t="s">
         <v>49</v>
@@ -32110,7 +32122,7 @@
         <v>0</v>
       </c>
       <c r="AD32" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="AE32" s="2">
         <f t="shared" si="13"/>
@@ -32204,7 +32216,7 @@
         <v>0</v>
       </c>
       <c r="AD33" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="AE33" s="2">
         <f t="shared" si="13"/>
@@ -32337,7 +32349,7 @@
         <v>33</v>
       </c>
       <c r="C35" s="30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D35" s="30" t="s">
         <v>49</v>
@@ -32513,7 +32525,7 @@
         <v>35</v>
       </c>
       <c r="C37" s="24" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D37" s="24" t="s">
         <v>49</v>
@@ -32601,7 +32613,7 @@
         <v>36</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D38" s="24" t="s">
         <v>45</v>
@@ -32635,7 +32647,7 @@
       <c r="S38" s="61"/>
       <c r="T38" s="59"/>
       <c r="AD38" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AE38" s="2">
         <f t="shared" si="13"/>
@@ -32755,7 +32767,7 @@
         <v>38</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D40" s="37" t="s">
         <v>49</v>
@@ -33166,7 +33178,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D8" s="20" t="s">
         <v>49</v>
@@ -33312,7 +33324,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D11" s="20" t="s">
         <v>49</v>
@@ -33372,7 +33384,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D12" s="20" t="s">
         <v>45</v>
@@ -33550,7 +33562,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D15" s="20" t="s">
         <v>45</v>
@@ -33810,7 +33822,7 @@
         <v>18</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D20" s="20" t="s">
         <v>45</v>
@@ -33956,7 +33968,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D23" s="20" t="s">
         <v>49</v>
@@ -34289,7 +34301,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D29" s="20" t="s">
         <v>45</v>
@@ -34307,7 +34319,7 @@
         <v>33</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="L29" s="2">
         <f t="shared" ref="L29:L39" si="0">SUM(M29:O29)</f>
@@ -34484,7 +34496,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D32" s="20" t="s">
         <v>49</v>
@@ -34502,7 +34514,7 @@
         <v>33</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="L32" s="2">
         <f t="shared" si="0"/>
@@ -34614,7 +34626,7 @@
         <v>32</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D34" s="20" t="s">
         <v>45</v>
@@ -34875,7 +34887,7 @@
         <v>36</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D38" s="20" t="s">
         <v>49</v>
@@ -34893,7 +34905,7 @@
         <v>32</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="L38" s="2">
         <f t="shared" si="0"/>
@@ -35087,7 +35099,7 @@
         <v>171</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
         <v>281</v>
@@ -35358,7 +35370,7 @@
         <v>83</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="R2" s="159" t="s">
         <v>114</v>
@@ -35410,7 +35422,7 @@
         <v>51</v>
       </c>
       <c r="I3" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J3" s="243" t="s">
         <v>71</v>
@@ -35486,7 +35498,7 @@
         <v>51</v>
       </c>
       <c r="I4" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J4" s="243" t="s">
         <v>71</v>
@@ -35579,7 +35591,7 @@
         <v>81</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>80</v>
@@ -35636,7 +35648,7 @@
         <v>51</v>
       </c>
       <c r="I6" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J6" s="243" t="s">
         <v>59</v>
@@ -35712,7 +35724,7 @@
         <v>51</v>
       </c>
       <c r="I7" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J7" s="243" t="s">
         <v>59</v>
@@ -35790,7 +35802,7 @@
         <v>51</v>
       </c>
       <c r="I8" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J8" s="243" t="s">
         <v>59</v>
@@ -35846,7 +35858,7 @@
         <v>51</v>
       </c>
       <c r="I9" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J9" s="243" t="s">
         <v>71</v>
@@ -35904,7 +35916,7 @@
         <v>51</v>
       </c>
       <c r="I10" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J10" s="243" t="s">
         <v>59</v>
@@ -35962,7 +35974,7 @@
         <v>51</v>
       </c>
       <c r="I11" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J11" s="243" t="s">
         <v>59</v>
@@ -36020,7 +36032,7 @@
         <v>51</v>
       </c>
       <c r="I12" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J12" s="243" t="s">
         <v>59</v>
@@ -36078,7 +36090,7 @@
         <v>51</v>
       </c>
       <c r="I13" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J13" s="243" t="s">
         <v>83</v>
@@ -36136,7 +36148,7 @@
         <v>51</v>
       </c>
       <c r="I14" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J14" s="243" t="s">
         <v>59</v>
@@ -36218,7 +36230,7 @@
         <v>59</v>
       </c>
       <c r="Q15" s="159" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="R15" s="159" t="s">
         <v>81</v>
@@ -36252,7 +36264,7 @@
         <v>51</v>
       </c>
       <c r="I16" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J16" s="243" t="s">
         <v>59</v>
@@ -36310,7 +36322,7 @@
         <v>51</v>
       </c>
       <c r="I17" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J17" s="243" t="s">
         <v>59</v>
@@ -36424,7 +36436,7 @@
         <v>51</v>
       </c>
       <c r="I19" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J19" s="243" t="s">
         <v>59</v>
@@ -36482,7 +36494,7 @@
         <v>51</v>
       </c>
       <c r="I20" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J20" s="243" t="s">
         <v>87</v>
@@ -36540,7 +36552,7 @@
         <v>51</v>
       </c>
       <c r="I21" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J21" s="243" t="s">
         <v>87</v>
@@ -36595,7 +36607,7 @@
         <v>52</v>
       </c>
       <c r="H22" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I22" s="243" t="s">
         <v>71</v>
@@ -36653,7 +36665,7 @@
         <v>52</v>
       </c>
       <c r="H23" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I23" s="243" t="s">
         <v>87</v>
@@ -36707,7 +36719,7 @@
         <v>52</v>
       </c>
       <c r="H24" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I24" s="243" t="s">
         <v>59</v>
@@ -36765,7 +36777,7 @@
         <v>52</v>
       </c>
       <c r="H25" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I25" s="243" t="s">
         <v>71</v>
@@ -36850,7 +36862,7 @@
         <v>102</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="R26" s="159" t="s">
         <v>87</v>
@@ -36881,7 +36893,7 @@
         <v>52</v>
       </c>
       <c r="H27" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I27" s="243" t="s">
         <v>59</v>
@@ -36995,7 +37007,7 @@
         <v>52</v>
       </c>
       <c r="H29" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I29" s="243" t="s">
         <v>59</v>
@@ -37053,7 +37065,7 @@
         <v>52</v>
       </c>
       <c r="H30" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I30" s="243" t="s">
         <v>71</v>
@@ -37109,7 +37121,7 @@
         <v>52</v>
       </c>
       <c r="H31" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I31" s="243" t="s">
         <v>51</v>
@@ -37165,7 +37177,7 @@
         <v>52</v>
       </c>
       <c r="H32" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I32" s="243" t="s">
         <v>87</v>
@@ -37207,21 +37219,51 @@
       <c r="B33" s="264" t="s">
         <v>369</v>
       </c>
-      <c r="C33" s="297"/>
-      <c r="D33" s="243"/>
-      <c r="E33" s="243"/>
-      <c r="F33" s="243"/>
-      <c r="G33" s="243"/>
-      <c r="H33" s="243"/>
-      <c r="I33" s="243"/>
-      <c r="J33" s="243"/>
-      <c r="K33" s="243"/>
-      <c r="L33" s="243"/>
-      <c r="M33" s="298"/>
-      <c r="N33" s="110"/>
-      <c r="O33" s="2"/>
-      <c r="P33" s="2"/>
-      <c r="Q33" s="159"/>
+      <c r="C33" s="297" t="s">
+        <v>107</v>
+      </c>
+      <c r="D33" s="243" t="s">
+        <v>64</v>
+      </c>
+      <c r="E33" s="243" t="s">
+        <v>89</v>
+      </c>
+      <c r="F33" s="243" t="s">
+        <v>97</v>
+      </c>
+      <c r="G33" s="243" t="s">
+        <v>52</v>
+      </c>
+      <c r="H33" s="243" t="s">
+        <v>102</v>
+      </c>
+      <c r="I33" s="243" t="s">
+        <v>106</v>
+      </c>
+      <c r="J33" s="243" t="s">
+        <v>73</v>
+      </c>
+      <c r="K33" s="243" t="s">
+        <v>81</v>
+      </c>
+      <c r="L33" s="243" t="s">
+        <v>46</v>
+      </c>
+      <c r="M33" s="298" t="s">
+        <v>66</v>
+      </c>
+      <c r="N33" s="110" t="s">
+        <v>71</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q33" s="159" t="s">
+        <v>54</v>
+      </c>
       <c r="R33" s="159"/>
       <c r="S33" s="51"/>
       <c r="T33" s="1"/>
@@ -37484,7 +37526,7 @@
         <v>6</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C48" s="2">
         <v>4</v>
@@ -37535,7 +37577,7 @@
         <v>9</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C51" s="2">
         <v>2</v>
@@ -37552,7 +37594,7 @@
         <v>10</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C52" s="2">
         <v>6</v>
@@ -37569,7 +37611,7 @@
         <v>11</v>
       </c>
       <c r="B53" s="266" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C53" s="2">
         <v>6</v>
@@ -37603,7 +37645,7 @@
         <v>13</v>
       </c>
       <c r="B55" s="319" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C55" s="2">
         <v>3</v>
@@ -37676,7 +37718,7 @@
         <v>18</v>
       </c>
       <c r="B60" s="352" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="96"/>
@@ -37709,7 +37751,7 @@
         <v>21</v>
       </c>
       <c r="B63" s="352" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="96"/>
@@ -37720,7 +37762,7 @@
         <v>22</v>
       </c>
       <c r="B64" s="413" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C64" s="441"/>
       <c r="D64" s="442"/>
@@ -37731,7 +37773,7 @@
         <v>23</v>
       </c>
       <c r="B65" s="352" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="96"/>
@@ -37764,7 +37806,7 @@
         <v>26</v>
       </c>
       <c r="B68" s="352" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="96"/>
@@ -37830,7 +37872,7 @@
         <v>32</v>
       </c>
       <c r="B74" s="352" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" s="96"/>
@@ -37841,7 +37883,7 @@
         <v>33</v>
       </c>
       <c r="B75" s="413" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C75" s="441"/>
       <c r="D75" s="442"/>
@@ -39650,7 +39692,7 @@
         <v>54</v>
       </c>
       <c r="N11" s="270" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O11" s="270" t="s">
         <v>46</v>
@@ -39942,7 +39984,7 @@
         <v>4</v>
       </c>
       <c r="BA12" s="20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BB12" s="2">
         <f t="shared" si="8"/>
@@ -40015,7 +40057,7 @@
       </c>
       <c r="P13" s="271"/>
       <c r="Q13" s="272" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="R13" s="270" t="s">
         <v>46</v>
@@ -40548,7 +40590,7 @@
       <c r="T16" s="58"/>
       <c r="U16" s="248"/>
       <c r="V16" s="93" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="X16" s="60" t="s">
         <v>113</v>
@@ -40723,7 +40765,7 @@
         <v>152</v>
       </c>
       <c r="X17" s="327" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y17" s="297">
         <f t="shared" si="0"/>
@@ -41778,7 +41820,7 @@
         <v>7392</v>
       </c>
       <c r="V24" s="93" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="X24" s="358" t="s">
         <v>176</v>
@@ -42272,7 +42314,7 @@
       <c r="K29" s="266"/>
       <c r="L29" s="269"/>
       <c r="M29" s="246" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N29" s="270"/>
       <c r="O29" s="270"/>
@@ -42874,7 +42916,7 @@
       <c r="O35" s="270"/>
       <c r="P35" s="271"/>
       <c r="Q35" s="272" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="R35" s="270"/>
       <c r="S35" s="270"/>
@@ -43180,7 +43222,7 @@
       <c r="P38" s="271"/>
       <c r="Q38" s="272"/>
       <c r="R38" s="270" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="S38" s="270"/>
       <c r="T38" s="270"/>
@@ -43285,7 +43327,7 @@
         <v>7058</v>
       </c>
       <c r="V39" s="277" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="X39" s="356" t="s">
         <v>182</v>
@@ -44156,7 +44198,7 @@
         <v>80</v>
       </c>
       <c r="H2" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I2" s="243" t="s">
         <v>170</v>
@@ -44266,7 +44308,7 @@
         <v>80</v>
       </c>
       <c r="H3" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I3" s="243" t="s">
         <v>93</v>
@@ -44378,7 +44420,7 @@
         <v>80</v>
       </c>
       <c r="H4" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I4" s="243" t="s">
         <v>170</v>
@@ -44488,7 +44530,7 @@
         <v>80</v>
       </c>
       <c r="H5" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I5" s="243" t="s">
         <v>112</v>
@@ -44566,7 +44608,7 @@
         <v>80</v>
       </c>
       <c r="H6" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I6" s="243" t="s">
         <v>112</v>
@@ -44725,7 +44767,7 @@
         <v>93</v>
       </c>
       <c r="I8" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J8" s="243" t="s">
         <v>71</v>
@@ -44783,7 +44825,7 @@
         <v>93</v>
       </c>
       <c r="I9" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J9" s="243" t="s">
         <v>71</v>
@@ -44841,7 +44883,7 @@
         <v>112</v>
       </c>
       <c r="I10" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J10" s="243" t="s">
         <v>71</v>
@@ -44899,7 +44941,7 @@
         <v>112</v>
       </c>
       <c r="I11" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J11" s="243" t="s">
         <v>71</v>
@@ -44957,7 +44999,7 @@
         <v>112</v>
       </c>
       <c r="I12" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J12" s="243" t="s">
         <v>71</v>
@@ -45015,7 +45057,7 @@
         <v>112</v>
       </c>
       <c r="I13" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J13" s="243" t="s">
         <v>71</v>
@@ -45073,7 +45115,7 @@
         <v>112</v>
       </c>
       <c r="I14" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J14" s="243" t="s">
         <v>71</v>
@@ -45131,7 +45173,7 @@
         <v>112</v>
       </c>
       <c r="I15" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J15" s="243" t="s">
         <v>71</v>
@@ -45189,7 +45231,7 @@
         <v>93</v>
       </c>
       <c r="I16" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J16" s="243" t="s">
         <v>71</v>
@@ -45247,7 +45289,7 @@
         <v>93</v>
       </c>
       <c r="I17" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J17" s="243" t="s">
         <v>71</v>
@@ -45363,7 +45405,7 @@
         <v>93</v>
       </c>
       <c r="I19" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J19" s="243" t="s">
         <v>71</v>
@@ -45421,7 +45463,7 @@
         <v>176</v>
       </c>
       <c r="I20" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J20" s="243" t="s">
         <v>71</v>
@@ -45479,7 +45521,7 @@
         <v>80</v>
       </c>
       <c r="I21" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J21" s="243" t="s">
         <v>71</v>
@@ -45537,7 +45579,7 @@
         <v>90</v>
       </c>
       <c r="I22" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J22" s="243" t="s">
         <v>71</v>
@@ -45595,7 +45637,7 @@
         <v>80</v>
       </c>
       <c r="I23" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J23" s="243" t="s">
         <v>71</v>
@@ -45651,7 +45693,7 @@
         <v>80</v>
       </c>
       <c r="I24" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J24" s="243" t="s">
         <v>71</v>
@@ -45711,7 +45753,7 @@
         <v>80</v>
       </c>
       <c r="I25" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J25" s="243" t="s">
         <v>71</v>
@@ -45769,7 +45811,7 @@
         <v>80</v>
       </c>
       <c r="I26" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J26" s="243" t="s">
         <v>71</v>
@@ -45827,7 +45869,7 @@
         <v>90</v>
       </c>
       <c r="I27" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J27" s="243" t="s">
         <v>71</v>
@@ -45885,7 +45927,7 @@
         <v>90</v>
       </c>
       <c r="I28" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J28" s="243" t="s">
         <v>71</v>
@@ -45943,7 +45985,7 @@
         <v>90</v>
       </c>
       <c r="I29" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J29" s="243" t="s">
         <v>71</v>
@@ -46001,7 +46043,7 @@
         <v>90</v>
       </c>
       <c r="I30" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J30" s="243" t="s">
         <v>71</v>
@@ -46117,7 +46159,7 @@
         <v>90</v>
       </c>
       <c r="I32" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J32" s="243" t="s">
         <v>143</v>
@@ -46173,7 +46215,7 @@
         <v>90</v>
       </c>
       <c r="I33" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J33" s="243" t="s">
         <v>71</v>
@@ -46231,7 +46273,7 @@
         <v>90</v>
       </c>
       <c r="I34" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J34" s="243" t="s">
         <v>71</v>
@@ -46289,7 +46331,7 @@
         <v>90</v>
       </c>
       <c r="I35" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J35" s="243" t="s">
         <v>71</v>
@@ -46347,7 +46389,7 @@
         <v>90</v>
       </c>
       <c r="I36" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J36" s="243" t="s">
         <v>71</v>
@@ -46401,7 +46443,7 @@
         <v>90</v>
       </c>
       <c r="I37" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J37" s="243" t="s">
         <v>71</v>
@@ -46459,7 +46501,7 @@
         <v>90</v>
       </c>
       <c r="I38" s="243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J38" s="243" t="s">
         <v>92</v>
@@ -46594,7 +46636,7 @@
         <v>99</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>71</v>
@@ -48017,7 +48059,7 @@
         <v>6</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E8" s="30" t="s">
         <v>45</v>
@@ -48323,7 +48365,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E10" s="30" t="s">
         <v>49</v>
@@ -48581,7 +48623,7 @@
         <v>10</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E12" s="30" t="s">
         <v>45</v>
@@ -48731,7 +48773,7 @@
         <v>11</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E13" s="30" t="s">
         <v>49</v>
@@ -49236,7 +49278,7 @@
         <v>9107</v>
       </c>
       <c r="X16" s="149" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y16" s="153">
         <f t="shared" si="0"/>
@@ -49589,7 +49631,7 @@
         <v>17</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E19" s="24" t="s">
         <v>49</v>
@@ -49877,7 +49919,7 @@
         <v>19</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E21" s="24" t="s">
         <v>49</v>
@@ -50021,7 +50063,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E22" s="24" t="s">
         <v>45</v>
@@ -50167,7 +50209,7 @@
         <v>21</v>
       </c>
       <c r="D23" s="73" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E23" s="24" t="s">
         <v>45</v>
@@ -50766,7 +50808,7 @@
         <v>42</v>
       </c>
       <c r="AJ27" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="AK27" s="2">
         <f t="shared" si="18"/>
@@ -50816,7 +50858,7 @@
         <v>26</v>
       </c>
       <c r="D28" s="30" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E28" s="30" t="s">
         <v>49</v>
@@ -51078,7 +51120,7 @@
         <v>28</v>
       </c>
       <c r="D30" s="30" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E30" s="30" t="s">
         <v>45</v>
@@ -51292,7 +51334,7 @@
         <v>42</v>
       </c>
       <c r="AJ31" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="AK31" s="2">
         <f t="shared" si="18"/>
@@ -51342,7 +51384,7 @@
         <v>30</v>
       </c>
       <c r="D32" s="30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E32" s="30" t="s">
         <v>49</v>
@@ -51548,7 +51590,7 @@
         <v>42</v>
       </c>
       <c r="AJ33" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="AK33" s="2">
         <f t="shared" si="18"/>
@@ -51675,7 +51717,7 @@
         <v>42</v>
       </c>
       <c r="AJ34" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AK34" s="2">
         <f t="shared" si="18"/>
@@ -51725,7 +51767,7 @@
         <v>33</v>
       </c>
       <c r="D35" s="73" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E35" s="30" t="s">
         <v>45</v>
@@ -51816,7 +51858,7 @@
         <v>34</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E36" s="24" t="s">
         <v>45</v>
@@ -51994,7 +52036,7 @@
         <v>36</v>
       </c>
       <c r="D38" s="73" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E38" s="24" t="s">
         <v>49</v>
@@ -52104,7 +52146,7 @@
       <c r="O39" s="58"/>
       <c r="P39" s="59"/>
       <c r="Q39" s="143" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="R39" s="58"/>
       <c r="S39" s="58"/>
@@ -52342,7 +52384,7 @@
         <v>128</v>
       </c>
       <c r="D42" s="103" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E42" s="103" t="s">
         <v>45</v>
@@ -52888,7 +52930,7 @@
         <v>111</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>272</v>
@@ -52992,7 +53034,7 @@
         <v>111</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>272</v>
@@ -53058,7 +53100,7 @@
         <v>111</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>172</v>
@@ -53122,7 +53164,7 @@
         <v>268</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>272</v>
@@ -53194,7 +53236,7 @@
         <v>111</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>272</v>
@@ -53266,7 +53308,7 @@
         <v>112</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>170</v>
@@ -53338,7 +53380,7 @@
         <v>279</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>272</v>
@@ -53389,7 +53431,7 @@
         <v>112</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>93</v>
@@ -53440,7 +53482,7 @@
         <v>279</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>272</v>
@@ -53493,7 +53535,7 @@
         <v>279</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>93</v>
@@ -54146,7 +54188,7 @@
         <v>87</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P23" s="2"/>
       <c r="Q23" s="51"/>
@@ -54189,7 +54231,7 @@
         <v>143</v>
       </c>
       <c r="M24" s="110" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>87</v>
@@ -54231,7 +54273,7 @@
         <v>93</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K25" s="5" t="s">
         <v>46</v>
@@ -54278,7 +54320,7 @@
         <v>281</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I26" s="5" t="s">
         <v>272</v>
@@ -54327,7 +54369,7 @@
         <v>171</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>272</v>
@@ -54380,7 +54422,7 @@
         <v>171</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I28" s="5" t="s">
         <v>272</v>
@@ -54433,7 +54475,7 @@
         <v>171</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I29" s="5" t="s">
         <v>170</v>
@@ -54486,7 +54528,7 @@
         <v>171</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I30" s="5" t="s">
         <v>170</v>
@@ -54539,7 +54581,7 @@
         <v>171</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>170</v>
@@ -54592,7 +54634,7 @@
         <v>279</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I32" s="5" t="s">
         <v>170</v>
@@ -54645,7 +54687,7 @@
         <v>171</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I33" s="5" t="s">
         <v>170</v>
@@ -54696,7 +54738,7 @@
         <v>279</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I34" s="5" t="s">
         <v>170</v>
@@ -54749,7 +54791,7 @@
         <v>279</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I35" s="5" t="s">
         <v>170</v>
@@ -54802,7 +54844,7 @@
         <v>279</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I36" s="5" t="s">
         <v>170</v>

--- a/인천 2026 기록.xlsx
+++ b/인천 2026 기록.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://familyinter-my.sharepoint.com/personal/hwlee_familyinter_onmicrosoft_com/Documents/바탕 화면/프로젝트300/대시보드/인천 대시보드/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1182" documentId="11_4EE6FFD7959CA43523F9517F60E94D8B825D3B4E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{029DD364-2BED-4D04-BD15-6CF5AA881FB7}"/>
+  <xr:revisionPtr revIDLastSave="1210" documentId="11_0F6BF197949C94B063893377604B65CBEB673EAF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DDB606E-B619-4BAE-903E-6C3CD5BA9300}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 토탈" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6111" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6134" uniqueCount="395">
   <si>
     <t>리그</t>
   </si>
@@ -240,13 +240,10 @@
     <t>총합</t>
   </si>
   <si>
-    <t>전북</t>
+    <t>대전</t>
   </si>
   <si>
     <t>수</t>
-  </si>
-  <si>
-    <t>대전</t>
   </si>
   <si>
     <t>이주용</t>
@@ -261,7 +258,7 @@
     <t>팀명</t>
   </si>
   <si>
-    <t>강원</t>
+    <t>전북</t>
   </si>
   <si>
     <t>안양</t>
@@ -273,6 +270,9 @@
     <t>제르소</t>
   </si>
   <si>
+    <t>강원</t>
+  </si>
+  <si>
     <t>김천</t>
   </si>
   <si>
@@ -282,13 +282,13 @@
     <t>최철준</t>
   </si>
   <si>
-    <t>제주</t>
+    <t>인천</t>
   </si>
   <si>
     <t>송민석</t>
   </si>
   <si>
-    <t>인천</t>
+    <t>제주</t>
   </si>
   <si>
     <t>부천</t>
@@ -1291,7 +1291,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>K리그1 2026 리그순위   (2026-10-17 - 32R 종료)</t>
+    <t>K리그1 2026 리그순위   (2026-10-24 - 33R 종료)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -5593,11 +5593,11 @@
       </c>
       <c r="Y3" s="332">
         <f t="shared" ref="Y3:Y43" si="0">Z3+AA3</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Z3" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X3)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA3" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X3)</f>
@@ -5609,19 +5609,19 @@
       </c>
       <c r="AC3" s="334">
         <f t="shared" ref="AC3:AC43" si="2">COUNTIF($Q$3:$T$40,$X3)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD3" s="335">
         <f t="shared" ref="AD3:AD43" si="3">AB3+AC3</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE3" s="332">
         <f t="shared" ref="AE3:AE43" si="4">AF3+AG3</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF3" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X3)+Z3</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG3" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X3)+AA3</f>
@@ -5633,22 +5633,22 @@
       </c>
       <c r="AI3" s="334">
         <f t="shared" ref="AI3:AI43" si="6">COUNTIF($Q$3:$T$41,$X3)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ3" s="335">
         <f t="shared" ref="AJ3:AJ43" si="7">AH3+AI3</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM3" s="2" t="s">
         <v>45</v>
       </c>
       <c r="AN3" s="2">
         <f>SUM(AO3:AQ3)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO3" s="243">
         <f t="shared" ref="AO3:AQ4" si="8">COUNTIFS($A$3:$A$40,"K리그",$F$3:$F$40,$AM3,$I$3:$I$40,AO$2)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP3" s="58">
         <f t="shared" si="8"/>
@@ -5660,31 +5660,31 @@
       </c>
       <c r="AR3" s="352">
         <f>AO3*3+AP3</f>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AS3" s="10">
         <f>IFERROR(AO3/AN3,0)</f>
-        <v>0.375</v>
+        <v>0.41176470588235292</v>
       </c>
       <c r="AT3" s="2">
         <f>SUMIFS($G$3:$G$40,$A$3:$A$40,"K리그",$F$3:$F$40,$AM3)</f>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AU3" s="2">
         <f>SUMIFS($H$3:$H$40,$A$3:$A$40,"K리그",$F$3:$F$40,$AM3)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV3" s="2">
         <f>AT3-AU3</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW3" s="434">
         <f>IFERROR(AR3/AN3,0)</f>
-        <v>1.375</v>
+        <v>1.4705882352941178</v>
       </c>
       <c r="AX3" s="434">
         <f>IFERROR(AT3/AN3,0)</f>
-        <v>1.25</v>
+        <v>1.3529411764705883</v>
       </c>
       <c r="AY3" s="434">
         <f>IFERROR(AU3/AN3,0)</f>
@@ -5724,29 +5724,29 @@
         <v>341</v>
       </c>
       <c r="BK3" s="469">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BL3" s="469">
         <v>20</v>
       </c>
       <c r="BM3" s="469">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BN3" s="469">
         <v>6</v>
       </c>
       <c r="BO3" s="469">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="BP3" s="469">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BQ3" s="469">
         <f>BO3-BP3</f>
         <v>32</v>
       </c>
       <c r="BR3" s="469">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:77">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="Y4" s="332">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z4" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X4)</f>
@@ -5813,7 +5813,7 @@
       </c>
       <c r="AA4" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X4)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB4" s="333">
         <f t="shared" si="1"/>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="AE4" s="332">
         <f t="shared" si="4"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF4" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X4)+Z4</f>
@@ -5837,7 +5837,7 @@
       </c>
       <c r="AG4" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X4)+AA4</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH4" s="333">
         <f t="shared" si="5"/>
@@ -5936,29 +5936,29 @@
         <v>360</v>
       </c>
       <c r="BK4" s="470">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BL4" s="470">
         <v>15</v>
       </c>
       <c r="BM4" s="470">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BN4" s="470">
         <v>12</v>
       </c>
       <c r="BO4" s="470">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BP4" s="470">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="BQ4" s="470">
         <f>BO4-BP4</f>
         <v>5</v>
       </c>
       <c r="BR4" s="470">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:77">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="Y5" s="332">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z5" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X5)</f>
@@ -6019,11 +6019,11 @@
       </c>
       <c r="AA5" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X5)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB5" s="333">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC5" s="334">
         <f t="shared" si="2"/>
@@ -6031,11 +6031,11 @@
       </c>
       <c r="AD5" s="335">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE5" s="332">
         <f t="shared" si="4"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF5" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X5)+Z5</f>
@@ -6043,11 +6043,11 @@
       </c>
       <c r="AG5" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X5)+AA5</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH5" s="333">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI5" s="334">
         <f t="shared" si="6"/>
@@ -6055,18 +6055,18 @@
       </c>
       <c r="AJ5" s="335">
         <f t="shared" si="7"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM5" s="337" t="s">
         <v>60</v>
       </c>
       <c r="AN5" s="337">
         <f>SUM(AN3:AN4)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AO5" s="337">
         <f>SUM(AO3:AO4)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP5" s="337">
         <f>SUM(AP3:AP4)</f>
@@ -6078,35 +6078,35 @@
       </c>
       <c r="AR5" s="337">
         <f>SUM(AR3:AR4)</f>
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AS5" s="349">
         <f>IFERROR(AO5/AN5,0)</f>
-        <v>0.34375</v>
+        <v>0.36363636363636365</v>
       </c>
       <c r="AT5" s="337">
         <f>SUM(AT3:AT4)</f>
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AU5" s="337">
         <f>SUM(AU3:AU4)</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AV5" s="337">
         <f>SUM(AV3:AV4)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AW5" s="435">
         <f>IFERROR(AR5/AN5,0)</f>
-        <v>1.34375</v>
+        <v>1.393939393939394</v>
       </c>
       <c r="AX5" s="435">
         <f>IFERROR(AT5/AN5,0)</f>
-        <v>1.25</v>
+        <v>1.303030303030303</v>
       </c>
       <c r="AY5" s="435">
         <f>IFERROR(AU5/AN5,0)</f>
-        <v>1.0625</v>
+        <v>1.0606060606060606</v>
       </c>
       <c r="BA5" s="464" t="s">
         <v>58</v>
@@ -6139,32 +6139,32 @@
         <v>3</v>
       </c>
       <c r="BJ5" s="470" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="BK5" s="470">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BL5" s="470">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BM5" s="470">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BN5" s="470">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BO5" s="470">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="BP5" s="470">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="BQ5" s="470">
         <f>BO5-BP5</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BR5" s="470">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:77">
@@ -6205,7 +6205,7 @@
       <c r="O6" s="270"/>
       <c r="P6" s="271"/>
       <c r="Q6" s="272" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R6" s="270"/>
       <c r="S6" s="270"/>
@@ -6214,14 +6214,14 @@
         <v>6360</v>
       </c>
       <c r="V6" s="274" t="s">
+        <v>64</v>
+      </c>
+      <c r="X6" s="60" t="s">
         <v>65</v>
-      </c>
-      <c r="X6" s="60" t="s">
-        <v>66</v>
       </c>
       <c r="Y6" s="332">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z6" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X6)</f>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="AA6" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X6)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB6" s="333">
         <f t="shared" si="1"/>
@@ -6237,15 +6237,15 @@
       </c>
       <c r="AC6" s="334">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD6" s="335">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE6" s="332">
         <f t="shared" si="4"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF6" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X6)+Z6</f>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="AG6" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X6)+AA6</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH6" s="333">
         <f t="shared" si="5"/>
@@ -6261,14 +6261,14 @@
       </c>
       <c r="AI6" s="334">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ6" s="335">
         <f t="shared" si="7"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM6" s="337" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AN6" s="337" t="s">
         <v>30</v>
@@ -6298,7 +6298,7 @@
         <v>36</v>
       </c>
       <c r="BA6" s="464" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="BB6" s="464">
         <f t="shared" si="9"/>
@@ -6328,32 +6328,32 @@
         <v>4</v>
       </c>
       <c r="BJ6" s="479" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="BK6" s="479">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BL6" s="479">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BM6" s="479">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BN6" s="479">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BO6" s="479">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="BP6" s="479">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="BQ6" s="479">
         <f>BO6-BP6</f>
         <v>10</v>
       </c>
       <c r="BR6" s="479">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:77">
@@ -6399,14 +6399,14 @@
       <c r="T7" s="270"/>
       <c r="U7" s="273"/>
       <c r="V7" s="274" t="s">
+        <v>69</v>
+      </c>
+      <c r="X7" s="327" t="s">
         <v>70</v>
-      </c>
-      <c r="X7" s="327" t="s">
-        <v>71</v>
       </c>
       <c r="Y7" s="332">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Z7" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X7)</f>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="AA7" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X7)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB7" s="333">
         <f t="shared" si="1"/>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AE7" s="332">
         <f t="shared" si="4"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AF7" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X7)+Z7</f>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="AG7" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X7)+AA7</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH7" s="333">
         <f t="shared" si="5"/>
@@ -6456,7 +6456,7 @@
         <v>42</v>
       </c>
       <c r="AM7" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="AN7" s="89">
         <f t="shared" ref="AN7:AN17" si="13">SUM(AO7:AQ7)</f>
@@ -6495,7 +6495,7 @@
         <v>2</v>
       </c>
       <c r="BA7" s="464" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BB7" s="464">
         <f t="shared" si="9"/>
@@ -6525,32 +6525,32 @@
         <v>5</v>
       </c>
       <c r="BJ7" s="479" t="s">
-        <v>353</v>
+        <v>369</v>
       </c>
       <c r="BK7" s="479">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BL7" s="479">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BM7" s="479">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BN7" s="479">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BO7" s="479">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="BP7" s="479">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="BQ7" s="479">
         <f>BO7-BP7</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BR7" s="479">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:77">
@@ -6609,11 +6609,11 @@
       </c>
       <c r="Y8" s="332">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Z8" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X8)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA8" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X8)</f>
@@ -6633,11 +6633,11 @@
       </c>
       <c r="AE8" s="332">
         <f t="shared" si="4"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AF8" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X8)+Z8</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG8" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X8)+AA8</f>
@@ -6659,7 +6659,7 @@
         <v>42</v>
       </c>
       <c r="AM8" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AN8" s="89">
         <f t="shared" si="13"/>
@@ -6724,35 +6724,35 @@
         <f t="shared" si="12"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="BI8" s="479">
+      <c r="BI8" s="471">
         <v>6</v>
       </c>
-      <c r="BJ8" s="479" t="s">
-        <v>367</v>
-      </c>
-      <c r="BK8" s="479">
-        <v>32</v>
-      </c>
-      <c r="BL8" s="479">
+      <c r="BJ8" s="471" t="s">
+        <v>394</v>
+      </c>
+      <c r="BK8" s="471">
+        <v>33</v>
+      </c>
+      <c r="BL8" s="471">
         <v>12</v>
       </c>
-      <c r="BM8" s="479">
+      <c r="BM8" s="471">
         <v>10</v>
       </c>
-      <c r="BN8" s="479">
-        <v>10</v>
-      </c>
-      <c r="BO8" s="479">
-        <v>38</v>
-      </c>
-      <c r="BP8" s="479">
-        <v>34</v>
-      </c>
-      <c r="BQ8" s="479">
+      <c r="BN8" s="471">
+        <v>11</v>
+      </c>
+      <c r="BO8" s="471">
+        <v>43</v>
+      </c>
+      <c r="BP8" s="471">
+        <v>35</v>
+      </c>
+      <c r="BQ8" s="471">
         <f>BO8-BP8</f>
-        <v>4</v>
-      </c>
-      <c r="BR8" s="479">
+        <v>8</v>
+      </c>
+      <c r="BR8" s="471">
         <v>46</v>
       </c>
     </row>
@@ -6810,11 +6810,11 @@
       </c>
       <c r="Y9" s="332">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Z9" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X9)</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA9" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X9)</f>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="AB9" s="333">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC9" s="334">
         <f t="shared" si="2"/>
@@ -6830,15 +6830,15 @@
       </c>
       <c r="AD9" s="335">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE9" s="332">
         <f t="shared" si="4"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AF9" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X9)+Z9</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG9" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X9)+AA9</f>
@@ -6846,7 +6846,7 @@
       </c>
       <c r="AH9" s="333">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI9" s="334">
         <f t="shared" si="6"/>
@@ -6854,7 +6854,7 @@
       </c>
       <c r="AJ9" s="335">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL9" s="2" t="s">
         <v>42</v>
@@ -6925,36 +6925,36 @@
         <f t="shared" si="12"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="BI9" s="471">
+      <c r="BI9" s="479">
         <v>7</v>
       </c>
-      <c r="BJ9" s="471" t="s">
-        <v>394</v>
-      </c>
-      <c r="BK9" s="471">
-        <v>32</v>
-      </c>
-      <c r="BL9" s="471">
+      <c r="BJ9" s="479" t="s">
+        <v>367</v>
+      </c>
+      <c r="BK9" s="479">
+        <v>33</v>
+      </c>
+      <c r="BL9" s="479">
+        <v>12</v>
+      </c>
+      <c r="BM9" s="479">
+        <v>10</v>
+      </c>
+      <c r="BN9" s="479">
         <v>11</v>
       </c>
-      <c r="BM9" s="471">
-        <v>10</v>
-      </c>
-      <c r="BN9" s="471">
-        <v>11</v>
-      </c>
-      <c r="BO9" s="471">
-        <v>40</v>
-      </c>
-      <c r="BP9" s="471">
-        <v>34</v>
-      </c>
-      <c r="BQ9" s="471">
+      <c r="BO9" s="479">
+        <v>39</v>
+      </c>
+      <c r="BP9" s="479">
+        <v>37</v>
+      </c>
+      <c r="BQ9" s="479">
         <f>BO9-BP9</f>
-        <v>6</v>
-      </c>
-      <c r="BR9" s="471">
-        <v>43</v>
+        <v>2</v>
+      </c>
+      <c r="BR9" s="479">
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:77">
@@ -6989,10 +6989,10 @@
       <c r="K10" s="266"/>
       <c r="L10" s="269"/>
       <c r="M10" s="246" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N10" s="270" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O10" s="270"/>
       <c r="P10" s="271"/>
@@ -7104,11 +7104,11 @@
       </c>
       <c r="BB10" s="464">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC10" s="243">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD10" s="465">
         <f t="shared" si="10"/>
@@ -7120,11 +7120,11 @@
       </c>
       <c r="BF10" s="89">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BG10" s="11">
         <f t="shared" si="12"/>
-        <v>0.33333333333333331</v>
+        <v>0.5</v>
       </c>
       <c r="BI10" s="479">
         <v>8</v>
@@ -7133,29 +7133,29 @@
         <v>355</v>
       </c>
       <c r="BK10" s="479">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BL10" s="479">
         <v>10</v>
       </c>
       <c r="BM10" s="479">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN10" s="479">
         <v>10</v>
       </c>
       <c r="BO10" s="479">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BP10" s="479">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="BQ10" s="479">
         <f>BO10-BP10</f>
         <v>-8</v>
       </c>
       <c r="BR10" s="479">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:77">
@@ -7205,18 +7205,18 @@
       <c r="T11" s="270"/>
       <c r="U11" s="273"/>
       <c r="V11" s="274" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="X11" s="358" t="s">
         <v>81</v>
       </c>
       <c r="Y11" s="332">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Z11" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X11)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA11" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X11)</f>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="AB11" s="333">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC11" s="334">
         <f t="shared" si="2"/>
@@ -7232,15 +7232,15 @@
       </c>
       <c r="AD11" s="335">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE11" s="332">
         <f t="shared" si="4"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AF11" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X11)+Z11</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG11" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X11)+AA11</f>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="AH11" s="333">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI11" s="334">
         <f t="shared" si="6"/>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="AJ11" s="335">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL11" s="2" t="s">
         <v>42</v>
@@ -7334,29 +7334,29 @@
         <v>349</v>
       </c>
       <c r="BK11" s="479">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BL11" s="479">
         <v>11</v>
       </c>
       <c r="BM11" s="479">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BN11" s="479">
         <v>13</v>
       </c>
       <c r="BO11" s="479">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BP11" s="479">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="BQ11" s="479">
         <f>BO11-BP11</f>
         <v>-9</v>
       </c>
       <c r="BR11" s="479">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:77">
@@ -7391,7 +7391,7 @@
       <c r="K12" s="266"/>
       <c r="L12" s="269"/>
       <c r="M12" s="246" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N12" s="270"/>
       <c r="O12" s="270"/>
@@ -7463,7 +7463,7 @@
         <v>42</v>
       </c>
       <c r="AM12" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AN12" s="89">
         <f t="shared" si="13"/>
@@ -7532,7 +7532,7 @@
         <v>358</v>
       </c>
       <c r="BK12" s="479">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BL12" s="479">
         <v>5</v>
@@ -7541,17 +7541,17 @@
         <v>19</v>
       </c>
       <c r="BN12" s="479">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BO12" s="479">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BP12" s="479">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="BQ12" s="479">
         <f>BO12-BP12</f>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="BR12" s="479">
         <v>34</v>
@@ -7729,7 +7729,7 @@
         <v>362</v>
       </c>
       <c r="BK13" s="479">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BL13" s="479">
         <v>7</v>
@@ -7738,17 +7738,17 @@
         <v>11</v>
       </c>
       <c r="BN13" s="479">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BO13" s="479">
         <v>32</v>
       </c>
       <c r="BP13" s="479">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="BQ13" s="479">
         <f>BO13-BP13</f>
-        <v>-12</v>
+        <v>-15</v>
       </c>
       <c r="BR13" s="479">
         <v>32</v>
@@ -7795,18 +7795,18 @@
       <c r="T14" s="320"/>
       <c r="U14" s="400"/>
       <c r="V14" s="312" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="X14" s="327" t="s">
         <v>87</v>
       </c>
       <c r="Y14" s="332">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z14" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X14)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA14" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X14)</f>
@@ -7826,11 +7826,11 @@
       </c>
       <c r="AE14" s="332">
         <f t="shared" si="4"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF14" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X14)+Z14</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG14" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X14)+AA14</f>
@@ -7852,7 +7852,7 @@
         <v>42</v>
       </c>
       <c r="AM14" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AN14" s="89">
         <f t="shared" si="13"/>
@@ -7924,10 +7924,10 @@
         <v>345</v>
       </c>
       <c r="BK14" s="472">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BL14" s="472">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM14" s="472">
         <v>12</v>
@@ -7936,17 +7936,17 @@
         <v>18</v>
       </c>
       <c r="BO14" s="472">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BP14" s="472">
         <v>69</v>
       </c>
       <c r="BQ14" s="472">
         <f>BO14-BP14</f>
-        <v>-42</v>
+        <v>-39</v>
       </c>
       <c r="BR14" s="472">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:77" ht="17.5" customHeight="1">
@@ -7987,7 +7987,7 @@
         <v>59</v>
       </c>
       <c r="O15" s="320" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P15" s="368"/>
       <c r="Q15" s="363" t="s">
@@ -8098,11 +8098,11 @@
       </c>
       <c r="BB15" s="466">
         <f>SUM(BB3:BB14)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BC15" s="243">
         <f>SUM(BC3:BC14)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD15" s="467">
         <f>SUM(BD3:BD14)</f>
@@ -8114,11 +8114,11 @@
       </c>
       <c r="BF15" s="89">
         <f>SUM(BF3:BF14)</f>
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="BG15" s="11">
         <f t="shared" si="12"/>
-        <v>0.34375</v>
+        <v>0.36363636363636365</v>
       </c>
       <c r="BI15" s="476" t="s">
         <v>91</v>
@@ -8233,15 +8233,15 @@
         <v>42</v>
       </c>
       <c r="AM16" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AN16" s="89">
         <f t="shared" si="13"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO16" s="243">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP16" s="243">
         <f t="shared" si="15"/>
@@ -8253,23 +8253,23 @@
       </c>
       <c r="AR16" s="352">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AS16" s="23">
         <f>AO16/AN16</f>
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AT16" s="2">
         <f t="shared" si="18"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AU16" s="2">
         <f t="shared" si="19"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV16" s="2">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:48">
@@ -8307,16 +8307,16 @@
         <v>89</v>
       </c>
       <c r="N17" s="320" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O17" s="320" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P17" s="368" t="s">
         <v>81</v>
       </c>
       <c r="Q17" s="363" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R17" s="320" t="s">
         <v>81</v>
@@ -8649,7 +8649,7 @@
       <c r="K20" s="319"/>
       <c r="L20" s="360"/>
       <c r="M20" s="367" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N20" s="320"/>
       <c r="O20" s="320"/>
@@ -8748,7 +8748,7 @@
       <c r="K21" s="319"/>
       <c r="L21" s="360"/>
       <c r="M21" s="367" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N21" s="320" t="s">
         <v>46</v>
@@ -8770,11 +8770,11 @@
       </c>
       <c r="Y21" s="332">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z21" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X21)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA21" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X21)</f>
@@ -8794,11 +8794,11 @@
       </c>
       <c r="AE21" s="332">
         <f t="shared" si="4"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF21" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X21)+Z21</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG21" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X21)+AA21</f>
@@ -8849,7 +8849,7 @@
       <c r="K22" s="319"/>
       <c r="L22" s="360"/>
       <c r="M22" s="367" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N22" s="320"/>
       <c r="O22" s="320"/>
@@ -8871,11 +8871,11 @@
       </c>
       <c r="Y22" s="332">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Z22" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X22)</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AA22" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X22)</f>
@@ -8895,11 +8895,11 @@
       </c>
       <c r="AE22" s="332">
         <f t="shared" si="4"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AF22" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X22)+Z22</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG22" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X22)+AA22</f>
@@ -8956,14 +8956,14 @@
         <v>97</v>
       </c>
       <c r="O23" s="320" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P23" s="368"/>
       <c r="Q23" s="363" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R23" s="320" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S23" s="320" t="s">
         <v>81</v>
@@ -8978,11 +8978,11 @@
       </c>
       <c r="Y23" s="332">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Z23" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X23)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA23" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X23)</f>
@@ -9002,11 +9002,11 @@
       </c>
       <c r="AE23" s="332">
         <f t="shared" si="4"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF23" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X23)+Z23</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG23" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X23)+AA23</f>
@@ -9071,15 +9071,15 @@
         <v>86</v>
       </c>
       <c r="X24" s="329" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Y24" s="332">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Z24" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X24)</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA24" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X24)</f>
@@ -9099,11 +9099,11 @@
       </c>
       <c r="AE24" s="332">
         <f t="shared" si="4"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AF24" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X24)+Z24</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG24" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X24)+AA24</f>
@@ -9160,7 +9160,7 @@
       <c r="O25" s="270"/>
       <c r="P25" s="271"/>
       <c r="Q25" s="272" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R25" s="270"/>
       <c r="S25" s="270"/>
@@ -9266,7 +9266,7 @@
       <c r="T26" s="270"/>
       <c r="U26" s="273"/>
       <c r="V26" s="274" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="X26" s="329" t="s">
         <v>98</v>
@@ -9451,7 +9451,7 @@
       <c r="K28" s="266"/>
       <c r="L28" s="269"/>
       <c r="M28" s="246" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N28" s="270"/>
       <c r="O28" s="270"/>
@@ -9761,7 +9761,7 @@
       <c r="T31" s="270"/>
       <c r="U31" s="273"/>
       <c r="V31" s="274" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="X31" s="329" t="s">
         <v>104</v>
@@ -9847,7 +9847,7 @@
       <c r="K32" s="266"/>
       <c r="L32" s="269"/>
       <c r="M32" s="246" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N32" s="270"/>
       <c r="O32" s="270"/>
@@ -9974,11 +9974,11 @@
       </c>
       <c r="Y33" s="332">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z33" s="132">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X33)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA33" s="132">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X33)</f>
@@ -9998,11 +9998,11 @@
       </c>
       <c r="AE33" s="332">
         <f t="shared" si="4"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF33" s="132">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X33)+Z33</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG33" s="132">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X33)+AA33</f>
@@ -10139,22 +10139,42 @@
       <c r="F35" s="268" t="s">
         <v>342</v>
       </c>
-      <c r="G35" s="266"/>
-      <c r="H35" s="266"/>
-      <c r="I35" s="380"/>
+      <c r="G35" s="266">
+        <v>3</v>
+      </c>
+      <c r="H35" s="266">
+        <v>1</v>
+      </c>
+      <c r="I35" s="380" t="s">
+        <v>356</v>
+      </c>
       <c r="J35" s="374"/>
       <c r="K35" s="266"/>
       <c r="L35" s="269"/>
-      <c r="M35" s="246"/>
-      <c r="N35" s="270"/>
-      <c r="O35" s="270"/>
+      <c r="M35" s="246" t="s">
+        <v>73</v>
+      </c>
+      <c r="N35" s="270" t="s">
+        <v>59</v>
+      </c>
+      <c r="O35" s="270" t="s">
+        <v>81</v>
+      </c>
       <c r="P35" s="271"/>
-      <c r="Q35" s="272"/>
-      <c r="R35" s="270"/>
+      <c r="Q35" s="272" t="s">
+        <v>46</v>
+      </c>
+      <c r="R35" s="270" t="s">
+        <v>65</v>
+      </c>
       <c r="S35" s="270"/>
       <c r="T35" s="270"/>
-      <c r="U35" s="273"/>
-      <c r="V35" s="274"/>
+      <c r="U35" s="273">
+        <v>11541</v>
+      </c>
+      <c r="V35" s="274" t="s">
+        <v>79</v>
+      </c>
       <c r="X35" s="330" t="s">
         <v>109</v>
       </c>
@@ -10652,11 +10672,11 @@
       </c>
       <c r="Y41" s="332">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z41" s="474">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X41)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA41" s="474">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X41)</f>
@@ -10676,11 +10696,11 @@
       </c>
       <c r="AE41" s="475">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF41" s="475">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X41)+Z41</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG41" s="475">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X41)+AA41</f>
@@ -10712,7 +10732,7 @@
       </c>
       <c r="Y42" s="332">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z42" s="474">
         <f>COUNTIF('출전기록 (26)'!C$2:M$39,'2026 토탈'!X42)</f>
@@ -10720,7 +10740,7 @@
       </c>
       <c r="AA42" s="474">
         <f>COUNTIF('출전기록 (26)'!N$2:S$39,'2026 토탈'!X42)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB42" s="333">
         <f t="shared" si="1"/>
@@ -10736,7 +10756,7 @@
       </c>
       <c r="AE42" s="475">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF42" s="475">
         <f>COUNTIF('출전기록 (26)'!W$2:AG$7,'2026 토탈'!X42)+Z42</f>
@@ -10744,7 +10764,7 @@
       </c>
       <c r="AG42" s="475">
         <f>COUNTIF('출전기록 (26)'!AH$2:AM$7,'2026 토탈'!X42)+AA42</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH42" s="475">
         <f t="shared" si="5"/>
@@ -10842,15 +10862,15 @@
       </c>
       <c r="N44" s="2">
         <f>COUNT(U3:U40)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O44" s="96">
         <f>SUMIFS(U3:U41,A3:A41,M44)</f>
-        <v>171007</v>
+        <v>182548</v>
       </c>
       <c r="P44" s="96">
         <f>O44/N44</f>
-        <v>9500.3888888888887</v>
+        <v>9607.78947368421</v>
       </c>
       <c r="Q44" s="136">
         <v>19</v>
@@ -10863,7 +10883,7 @@
       </c>
       <c r="T44" s="165">
         <f>(P44-S44)/S44</f>
-        <v>-6.6189750292863517E-2</v>
+        <v>-5.563315433880664E-2</v>
       </c>
     </row>
     <row r="45" spans="1:36">
@@ -11221,7 +11241,7 @@
     </row>
     <row r="6" spans="2:22">
       <c r="B6" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>30</v>
@@ -11457,7 +11477,7 @@
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C13" s="2">
         <v>2</v>
@@ -11658,7 +11678,7 @@
     </row>
     <row r="21" spans="2:11">
       <c r="B21" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>30</v>
@@ -11690,7 +11710,7 @@
     </row>
     <row r="22" spans="2:11">
       <c r="B22" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C22" s="2">
         <v>3</v>
@@ -11786,7 +11806,7 @@
     </row>
     <row r="25" spans="2:11">
       <c r="B25" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C25" s="2">
         <v>3</v>
@@ -11978,7 +11998,7 @@
     </row>
     <row r="31" spans="2:11">
       <c r="B31" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C31" s="2">
         <v>4</v>
@@ -12175,7 +12195,7 @@
     </row>
     <row r="39" spans="2:11">
       <c r="B39" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>30</v>
@@ -12207,7 +12227,7 @@
     </row>
     <row r="40" spans="2:11">
       <c r="B40" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C40" s="2">
         <v>4</v>
@@ -12303,7 +12323,7 @@
     </row>
     <row r="43" spans="2:11">
       <c r="B43" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C43" s="2">
         <v>4</v>
@@ -12335,7 +12355,7 @@
     </row>
     <row r="44" spans="2:11">
       <c r="B44" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C44" s="2">
         <v>4</v>
@@ -12692,7 +12712,7 @@
     </row>
     <row r="57" spans="2:11">
       <c r="B57" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>30</v>
@@ -12756,7 +12776,7 @@
     </row>
     <row r="59" spans="2:11">
       <c r="B59" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C59" s="2">
         <v>4</v>
@@ -12820,7 +12840,7 @@
     </row>
     <row r="61" spans="2:11">
       <c r="B61" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C61" s="2">
         <v>3</v>
@@ -12852,7 +12872,7 @@
     </row>
     <row r="62" spans="2:11">
       <c r="B62" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C62" s="2">
         <v>3</v>
@@ -13044,7 +13064,7 @@
     </row>
     <row r="68" spans="2:11">
       <c r="B68" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C68" s="2">
         <v>3</v>
@@ -13209,7 +13229,7 @@
     </row>
     <row r="75" spans="2:11">
       <c r="B75" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>30</v>
@@ -13337,7 +13357,7 @@
     </row>
     <row r="79" spans="2:11">
       <c r="B79" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C79" s="2">
         <v>0</v>
@@ -13433,7 +13453,7 @@
     </row>
     <row r="82" spans="2:11">
       <c r="B82" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C82" s="2">
         <v>1</v>
@@ -13465,7 +13485,7 @@
     </row>
     <row r="83" spans="2:11">
       <c r="B83" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C83" s="2">
         <v>0</v>
@@ -13529,7 +13549,7 @@
     </row>
     <row r="85" spans="2:11">
       <c r="B85" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C85" s="2">
         <v>0</v>
@@ -13903,7 +13923,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E4" s="30" t="s">
         <v>45</v>
@@ -13948,7 +13968,7 @@
         <v>10011</v>
       </c>
       <c r="X4" s="72" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Y4" s="81">
         <f t="shared" si="0"/>
@@ -14036,7 +14056,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E5" s="30" t="s">
         <v>45</v>
@@ -14060,7 +14080,7 @@
         <v>31</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M5" s="15"/>
       <c r="N5" s="15"/>
@@ -14413,7 +14433,7 @@
         <v>6</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E8" s="30" t="s">
         <v>49</v>
@@ -14532,7 +14552,7 @@
         <v>7</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E9" s="30" t="s">
         <v>49</v>
@@ -14565,7 +14585,7 @@
       <c r="O9" s="15"/>
       <c r="P9" s="15"/>
       <c r="Q9" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R9" s="15"/>
       <c r="S9" s="15"/>
@@ -14964,7 +14984,7 @@
         <v>143</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S12" s="15"/>
       <c r="T12" s="15"/>
@@ -15190,7 +15210,7 @@
         <v>12</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E14" s="24" t="s">
         <v>49</v>
@@ -15282,7 +15302,7 @@
         <v>13</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E15" s="24" t="s">
         <v>45</v>
@@ -15667,7 +15687,7 @@
         <v>16</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E18" s="24" t="s">
         <v>49</v>
@@ -15820,7 +15840,7 @@
         <v>32</v>
       </c>
       <c r="L19" s="58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M19" s="58"/>
       <c r="N19" s="58"/>
@@ -16151,7 +16171,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E22" s="24" t="s">
         <v>45</v>
@@ -16383,7 +16403,7 @@
         <v>300</v>
       </c>
       <c r="R24" s="58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S24" s="58"/>
       <c r="T24" s="58"/>
@@ -16447,7 +16467,7 @@
         <v>23</v>
       </c>
       <c r="D25" s="30" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E25" s="30" t="s">
         <v>45</v>
@@ -16471,7 +16491,7 @@
         <v>31</v>
       </c>
       <c r="L25" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M25" s="15" t="s">
         <v>300</v>
@@ -16483,7 +16503,7 @@
         <v>300</v>
       </c>
       <c r="R25" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S25" s="15"/>
       <c r="T25" s="15"/>
@@ -16619,7 +16639,7 @@
       <c r="O26" s="15"/>
       <c r="P26" s="15"/>
       <c r="Q26" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R26" s="15"/>
       <c r="S26" s="15"/>
@@ -16734,7 +16754,7 @@
         <v>25</v>
       </c>
       <c r="D27" s="30" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E27" s="30" t="s">
         <v>49</v>
@@ -16906,12 +16926,12 @@
         <v>93</v>
       </c>
       <c r="N28" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O28" s="15"/>
       <c r="P28" s="15"/>
       <c r="Q28" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R28" s="15" t="s">
         <v>73</v>
@@ -17057,10 +17077,10 @@
         <v>32</v>
       </c>
       <c r="L29" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M29" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N29" s="15"/>
       <c r="O29" s="15"/>
@@ -17091,7 +17111,7 @@
         <v>0</v>
       </c>
       <c r="AD29" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AE29" s="4" t="s">
         <v>30</v>
@@ -17329,7 +17349,7 @@
         <v>42</v>
       </c>
       <c r="AD31" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="AE31" s="2">
         <f t="shared" si="17"/>
@@ -17379,7 +17399,7 @@
         <v>30</v>
       </c>
       <c r="D32" s="30" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E32" s="30" t="s">
         <v>45</v>
@@ -17492,7 +17512,7 @@
         <v>31</v>
       </c>
       <c r="D33" s="30" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E33" s="30" t="s">
         <v>49</v>
@@ -17549,7 +17569,7 @@
         <v>42</v>
       </c>
       <c r="AD33" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AE33" s="2">
         <f t="shared" si="17"/>
@@ -17660,7 +17680,7 @@
         <v>42</v>
       </c>
       <c r="AD34" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AE34" s="2">
         <f t="shared" si="17"/>
@@ -17837,7 +17857,7 @@
         <v>32</v>
       </c>
       <c r="L36" s="58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M36" s="58"/>
       <c r="N36" s="58"/>
@@ -18027,7 +18047,7 @@
         <v>36</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E38" s="24" t="s">
         <v>45</v>
@@ -18308,7 +18328,7 @@
         <v>42</v>
       </c>
       <c r="AD40" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AE40" s="2">
         <f t="shared" si="17"/>
@@ -18388,7 +18408,7 @@
         <v>300</v>
       </c>
       <c r="N41" s="123" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O41" s="123"/>
       <c r="P41" s="123"/>
@@ -18396,7 +18416,7 @@
         <v>46</v>
       </c>
       <c r="R41" s="123" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S41" s="123"/>
       <c r="T41" s="123"/>
@@ -18484,7 +18504,7 @@
         <v>314</v>
       </c>
       <c r="M42" s="76" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N42" s="76" t="s">
         <v>300</v>
@@ -18600,7 +18620,7 @@
       </c>
       <c r="R43" s="76"/>
       <c r="S43" s="76" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T43" s="76"/>
       <c r="U43" s="76"/>
@@ -18981,7 +19001,7 @@
         <v>115</v>
       </c>
       <c r="AD47" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="AE47" s="2">
         <f t="shared" si="17"/>
@@ -19120,7 +19140,7 @@
       <c r="Q49" s="91"/>
       <c r="R49" s="91"/>
       <c r="S49" s="91" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T49" s="91"/>
       <c r="U49" s="91"/>
@@ -19139,7 +19159,7 @@
         <v>130</v>
       </c>
       <c r="D50" s="104" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E50" s="104" t="s">
         <v>49</v>
@@ -19163,7 +19183,7 @@
         <v>33</v>
       </c>
       <c r="L50" s="113" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M50" s="113"/>
       <c r="N50" s="113"/>
@@ -19633,7 +19653,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D4" s="30" t="s">
         <v>45</v>
@@ -19671,7 +19691,7 @@
       </c>
       <c r="P4" s="54"/>
       <c r="S4" s="72" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T4" s="81">
         <f t="shared" si="0"/>
@@ -19756,7 +19776,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D5" s="30" t="s">
         <v>45</v>
@@ -19780,7 +19800,7 @@
         <v>31</v>
       </c>
       <c r="K5" s="53" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L5" s="15"/>
       <c r="M5" s="54"/>
@@ -20078,7 +20098,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D8" s="30" t="s">
         <v>49</v>
@@ -20196,7 +20216,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D9" s="30" t="s">
         <v>49</v>
@@ -20227,7 +20247,7 @@
       </c>
       <c r="M9" s="54"/>
       <c r="N9" s="141" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O9" s="56"/>
       <c r="P9" s="54"/>
@@ -20573,7 +20593,7 @@
         <v>143</v>
       </c>
       <c r="O12" s="56" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P12" s="54"/>
       <c r="S12" s="72" t="s">
@@ -20776,7 +20796,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D14" s="24" t="s">
         <v>49</v>
@@ -20887,7 +20907,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D15" s="24" t="s">
         <v>45</v>
@@ -21201,7 +21221,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D18" s="24" t="s">
         <v>49</v>
@@ -21328,7 +21348,7 @@
         <v>32</v>
       </c>
       <c r="K19" s="57" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L19" s="58"/>
       <c r="M19" s="59"/>
@@ -21587,7 +21607,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D22" s="24" t="s">
         <v>45</v>
@@ -21799,7 +21819,7 @@
         <v>300</v>
       </c>
       <c r="O24" s="61" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P24" s="59"/>
       <c r="S24" s="70" t="s">
@@ -21826,7 +21846,7 @@
         <v>23</v>
       </c>
       <c r="C25" s="30" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D25" s="30" t="s">
         <v>45</v>
@@ -21850,7 +21870,7 @@
         <v>31</v>
       </c>
       <c r="K25" s="53" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L25" s="15" t="s">
         <v>300</v>
@@ -21860,7 +21880,7 @@
         <v>300</v>
       </c>
       <c r="O25" s="56" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P25" s="54"/>
       <c r="S25" s="70" t="s">
@@ -21955,7 +21975,7 @@
       <c r="L26" s="15"/>
       <c r="M26" s="54"/>
       <c r="N26" s="141" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O26" s="56"/>
       <c r="P26" s="54"/>
@@ -22034,7 +22054,7 @@
         <v>25</v>
       </c>
       <c r="C27" s="30" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D27" s="30" t="s">
         <v>49</v>
@@ -22168,10 +22188,10 @@
         <v>93</v>
       </c>
       <c r="M28" s="54" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N28" s="141" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O28" s="56" t="s">
         <v>73</v>
@@ -22278,10 +22298,10 @@
         <v>32</v>
       </c>
       <c r="K29" s="53" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L29" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M29" s="54"/>
       <c r="N29" s="141" t="s">
@@ -22305,7 +22325,7 @@
         <v>0</v>
       </c>
       <c r="Y29" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Z29" s="4" t="s">
         <v>30</v>
@@ -22488,7 +22508,7 @@
         <v>3</v>
       </c>
       <c r="Y31" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="Z31" s="2">
         <f t="shared" si="14"/>
@@ -22535,7 +22555,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="30" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D32" s="30" t="s">
         <v>45</v>
@@ -22635,7 +22655,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="30" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D33" s="30" t="s">
         <v>49</v>
@@ -22684,7 +22704,7 @@
         <v>0</v>
       </c>
       <c r="Y33" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Z33" s="2">
         <f t="shared" si="14"/>
@@ -22782,7 +22802,7 @@
         <v>1</v>
       </c>
       <c r="Y34" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="Z34" s="2">
         <f t="shared" si="14"/>
@@ -22945,7 +22965,7 @@
         <v>32</v>
       </c>
       <c r="K36" s="57" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L36" s="58"/>
       <c r="M36" s="59"/>
@@ -23113,7 +23133,7 @@
         <v>36</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D38" s="24" t="s">
         <v>45</v>
@@ -23360,7 +23380,7 @@
         <v>0</v>
       </c>
       <c r="Y40" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="Z40" s="2">
         <f t="shared" si="14"/>
@@ -23628,7 +23648,7 @@
         <v>300</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N3" s="15"/>
       <c r="O3" s="54"/>
@@ -23636,7 +23656,7 @@
         <v>46</v>
       </c>
       <c r="Q3" s="56" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R3" s="56"/>
       <c r="S3" s="56"/>
@@ -23754,7 +23774,7 @@
         <v>314</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M4" s="15" t="s">
         <v>300</v>
@@ -23775,7 +23795,7 @@
       </c>
       <c r="T4" s="54"/>
       <c r="W4" s="72" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="X4" s="81">
         <f t="shared" si="0"/>
@@ -23901,7 +23921,7 @@
       </c>
       <c r="Q5" s="56"/>
       <c r="R5" s="56" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S5" s="56"/>
       <c r="T5" s="54"/>
@@ -25616,7 +25636,7 @@
         <v>0</v>
       </c>
       <c r="AC29" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AD29" s="4" t="s">
         <v>30</v>
@@ -26637,12 +26657,12 @@
       <c r="P4" s="56"/>
       <c r="Q4" s="56"/>
       <c r="R4" s="56" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S4" s="56"/>
       <c r="T4" s="54"/>
       <c r="W4" s="72" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="X4" s="81">
         <f t="shared" si="0"/>
@@ -26704,7 +26724,7 @@
         <v>130</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D5" s="30" t="s">
         <v>49</v>
@@ -26728,7 +26748,7 @@
         <v>33</v>
       </c>
       <c r="K5" s="53" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L5" s="15"/>
       <c r="M5" s="15"/>
@@ -28315,7 +28335,7 @@
         <v>0</v>
       </c>
       <c r="AC29" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AD29" s="4" t="s">
         <v>30</v>
@@ -28534,7 +28554,7 @@
         <v>0</v>
       </c>
       <c r="AC32" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="AD32" s="2">
         <f>SUM(AE32:AG32)</f>
@@ -29299,7 +29319,7 @@
       </c>
       <c r="Y4" s="1"/>
       <c r="Z4" s="72" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AA4" s="51">
         <f t="shared" si="1"/>
@@ -29374,7 +29394,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="73" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D5" s="73" t="s">
         <v>49</v>
@@ -30003,7 +30023,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="73" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D11" s="73" t="s">
         <v>45</v>
@@ -30239,7 +30259,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="73" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D13" s="73" t="s">
         <v>45</v>
@@ -30746,7 +30766,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="73" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D18" s="73" t="s">
         <v>49</v>
@@ -30862,7 +30882,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="73" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D19" s="73" t="s">
         <v>45</v>
@@ -31269,7 +31289,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D23" s="24" t="s">
         <v>49</v>
@@ -31722,7 +31742,7 @@
         <v>28</v>
       </c>
       <c r="C28" s="30" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D28" s="30" t="s">
         <v>45</v>
@@ -31771,7 +31791,7 @@
         <v>0</v>
       </c>
       <c r="AD28" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AE28" s="4" t="s">
         <v>30</v>
@@ -31852,7 +31872,7 @@
         <v>0</v>
       </c>
       <c r="AD29" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="AE29" s="2">
         <f t="shared" ref="AE29:AE39" si="13">SUM(AF29:AH29)</f>
@@ -31989,7 +32009,7 @@
         <v>29</v>
       </c>
       <c r="C31" s="30" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D31" s="30" t="s">
         <v>45</v>
@@ -32077,7 +32097,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="30" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D32" s="30" t="s">
         <v>49</v>
@@ -32122,7 +32142,7 @@
         <v>0</v>
       </c>
       <c r="AD32" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AE32" s="2">
         <f t="shared" si="13"/>
@@ -32216,7 +32236,7 @@
         <v>0</v>
       </c>
       <c r="AD33" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AE33" s="2">
         <f t="shared" si="13"/>
@@ -32525,7 +32545,7 @@
         <v>35</v>
       </c>
       <c r="C37" s="24" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D37" s="24" t="s">
         <v>49</v>
@@ -32613,7 +32633,7 @@
         <v>36</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D38" s="24" t="s">
         <v>45</v>
@@ -32767,7 +32787,7 @@
         <v>38</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D40" s="37" t="s">
         <v>49</v>
@@ -33178,7 +33198,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D8" s="20" t="s">
         <v>49</v>
@@ -33324,7 +33344,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D11" s="20" t="s">
         <v>49</v>
@@ -33384,7 +33404,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D12" s="20" t="s">
         <v>45</v>
@@ -33562,7 +33582,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D15" s="20" t="s">
         <v>45</v>
@@ -33822,7 +33842,7 @@
         <v>18</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D20" s="20" t="s">
         <v>45</v>
@@ -33968,7 +33988,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D23" s="20" t="s">
         <v>49</v>
@@ -34263,7 +34283,7 @@
         <v>33</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L28" s="4" t="s">
         <v>30</v>
@@ -34301,7 +34321,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D29" s="20" t="s">
         <v>45</v>
@@ -34319,7 +34339,7 @@
         <v>33</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="L29" s="2">
         <f t="shared" ref="L29:L39" si="0">SUM(M29:O29)</f>
@@ -34496,7 +34516,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D32" s="20" t="s">
         <v>49</v>
@@ -34514,7 +34534,7 @@
         <v>33</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L32" s="2">
         <f t="shared" si="0"/>
@@ -34626,7 +34646,7 @@
         <v>32</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D34" s="20" t="s">
         <v>45</v>
@@ -34887,7 +34907,7 @@
         <v>36</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D38" s="20" t="s">
         <v>49</v>
@@ -34905,7 +34925,7 @@
         <v>32</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L38" s="2">
         <f t="shared" si="0"/>
@@ -35052,7 +35072,7 @@
   <sheetData>
     <row r="2" spans="1:4">
       <c r="B2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
         <v>300</v>
@@ -35340,7 +35360,7 @@
         <v>52</v>
       </c>
       <c r="G2" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H2" s="243" t="s">
         <v>51</v>
@@ -35349,7 +35369,7 @@
         <v>85</v>
       </c>
       <c r="J2" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K2" s="243" t="s">
         <v>50</v>
@@ -35416,7 +35436,7 @@
         <v>52</v>
       </c>
       <c r="G3" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H3" s="243" t="s">
         <v>51</v>
@@ -35425,7 +35445,7 @@
         <v>73</v>
       </c>
       <c r="J3" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K3" s="243" t="s">
         <v>83</v>
@@ -35492,7 +35512,7 @@
         <v>52</v>
       </c>
       <c r="G4" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H4" s="243" t="s">
         <v>51</v>
@@ -35501,7 +35521,7 @@
         <v>73</v>
       </c>
       <c r="J4" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K4" s="243" t="s">
         <v>83</v>
@@ -35564,7 +35584,7 @@
         <v>52</v>
       </c>
       <c r="G5" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H5" s="243" t="s">
         <v>51</v>
@@ -35573,7 +35593,7 @@
         <v>85</v>
       </c>
       <c r="J5" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K5" s="243" t="s">
         <v>83</v>
@@ -35597,7 +35617,7 @@
         <v>80</v>
       </c>
       <c r="R5" s="159" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="S5" s="51"/>
       <c r="T5" s="1"/>
@@ -35642,7 +35662,7 @@
         <v>52</v>
       </c>
       <c r="G6" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H6" s="243" t="s">
         <v>51</v>
@@ -35663,7 +35683,7 @@
         <v>46</v>
       </c>
       <c r="N6" s="110" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>81</v>
@@ -35672,7 +35692,7 @@
         <v>80</v>
       </c>
       <c r="Q6" s="159" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R6" s="159"/>
       <c r="S6" s="51"/>
@@ -35718,7 +35738,7 @@
         <v>52</v>
       </c>
       <c r="G7" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H7" s="243" t="s">
         <v>51</v>
@@ -35739,7 +35759,7 @@
         <v>46</v>
       </c>
       <c r="N7" s="110" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>81</v>
@@ -35748,7 +35768,7 @@
         <v>83</v>
       </c>
       <c r="Q7" s="159" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R7" s="159" t="s">
         <v>85</v>
@@ -35796,7 +35816,7 @@
         <v>52</v>
       </c>
       <c r="G8" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H8" s="243" t="s">
         <v>51</v>
@@ -35820,13 +35840,13 @@
         <v>98</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>81</v>
       </c>
       <c r="Q8" s="159" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R8" s="159"/>
       <c r="S8" s="51"/>
@@ -35861,19 +35881,19 @@
         <v>73</v>
       </c>
       <c r="J9" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K9" s="243" t="s">
         <v>81</v>
       </c>
       <c r="L9" s="243" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M9" s="298" t="s">
         <v>46</v>
       </c>
       <c r="N9" s="110" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>50</v>
@@ -35925,19 +35945,19 @@
         <v>83</v>
       </c>
       <c r="L10" s="243" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M10" s="298" t="s">
         <v>81</v>
       </c>
       <c r="N10" s="110" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>85</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q10" s="159" t="s">
         <v>46</v>
@@ -35968,7 +35988,7 @@
         <v>52</v>
       </c>
       <c r="G11" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H11" s="243" t="s">
         <v>51</v>
@@ -35980,7 +36000,7 @@
         <v>59</v>
       </c>
       <c r="K11" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L11" s="243" t="s">
         <v>81</v>
@@ -36001,7 +36021,7 @@
         <v>87</v>
       </c>
       <c r="R11" s="159" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="S11" s="51"/>
       <c r="T11" s="1"/>
@@ -36026,7 +36046,7 @@
         <v>52</v>
       </c>
       <c r="G12" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H12" s="243" t="s">
         <v>51</v>
@@ -36041,13 +36061,13 @@
         <v>81</v>
       </c>
       <c r="L12" s="243" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M12" s="298" t="s">
         <v>46</v>
       </c>
       <c r="N12" s="110" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>83</v>
@@ -36096,7 +36116,7 @@
         <v>83</v>
       </c>
       <c r="K13" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L13" s="243" t="s">
         <v>54</v>
@@ -36105,7 +36125,7 @@
         <v>46</v>
       </c>
       <c r="N13" s="110" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>59</v>
@@ -36157,13 +36177,13 @@
         <v>81</v>
       </c>
       <c r="L14" s="243" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M14" s="298" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N14" s="110" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>96</v>
@@ -36200,7 +36220,7 @@
         <v>80</v>
       </c>
       <c r="G15" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H15" s="243" t="s">
         <v>51</v>
@@ -36221,10 +36241,10 @@
         <v>114</v>
       </c>
       <c r="N15" s="110" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>59</v>
@@ -36258,7 +36278,7 @@
         <v>52</v>
       </c>
       <c r="G16" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H16" s="243" t="s">
         <v>51</v>
@@ -36270,13 +36290,13 @@
         <v>59</v>
       </c>
       <c r="K16" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L16" s="243" t="s">
         <v>81</v>
       </c>
       <c r="M16" s="298" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N16" s="110" t="s">
         <v>80</v>
@@ -36316,7 +36336,7 @@
         <v>52</v>
       </c>
       <c r="G17" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H17" s="243" t="s">
         <v>51</v>
@@ -36328,13 +36348,13 @@
         <v>59</v>
       </c>
       <c r="K17" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L17" s="243" t="s">
         <v>81</v>
       </c>
       <c r="M17" s="298" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N17" s="110" t="s">
         <v>80</v>
@@ -36374,7 +36394,7 @@
         <v>52</v>
       </c>
       <c r="G18" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H18" s="243" t="s">
         <v>51</v>
@@ -36386,13 +36406,13 @@
         <v>59</v>
       </c>
       <c r="K18" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L18" s="243" t="s">
         <v>81</v>
       </c>
       <c r="M18" s="298" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N18" s="110" t="s">
         <v>80</v>
@@ -36430,7 +36450,7 @@
         <v>52</v>
       </c>
       <c r="G19" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H19" s="243" t="s">
         <v>51</v>
@@ -36442,13 +36462,13 @@
         <v>59</v>
       </c>
       <c r="K19" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L19" s="243" t="s">
         <v>81</v>
       </c>
       <c r="M19" s="298" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N19" s="110" t="s">
         <v>80</v>
@@ -36488,7 +36508,7 @@
         <v>52</v>
       </c>
       <c r="G20" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H20" s="243" t="s">
         <v>51</v>
@@ -36500,13 +36520,13 @@
         <v>87</v>
       </c>
       <c r="K20" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L20" s="243" t="s">
         <v>81</v>
       </c>
       <c r="M20" s="298" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N20" s="110" t="s">
         <v>80</v>
@@ -36546,7 +36566,7 @@
         <v>52</v>
       </c>
       <c r="G21" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H21" s="243" t="s">
         <v>51</v>
@@ -36558,13 +36578,13 @@
         <v>87</v>
       </c>
       <c r="K21" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L21" s="243" t="s">
         <v>81</v>
       </c>
       <c r="M21" s="298" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N21" s="110" t="s">
         <v>80</v>
@@ -36601,7 +36621,7 @@
         <v>97</v>
       </c>
       <c r="F22" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G22" s="243" t="s">
         <v>52</v>
@@ -36610,7 +36630,7 @@
         <v>73</v>
       </c>
       <c r="I22" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J22" s="243" t="s">
         <v>51</v>
@@ -36625,7 +36645,7 @@
         <v>81</v>
       </c>
       <c r="N22" s="110" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>59</v>
@@ -36659,7 +36679,7 @@
         <v>105</v>
       </c>
       <c r="F23" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G23" s="243" t="s">
         <v>52</v>
@@ -36686,7 +36706,7 @@
         <v>50</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>54</v>
@@ -36713,7 +36733,7 @@
         <v>97</v>
       </c>
       <c r="F24" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G24" s="243" t="s">
         <v>52</v>
@@ -36725,7 +36745,7 @@
         <v>59</v>
       </c>
       <c r="J24" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K24" s="243" t="s">
         <v>51</v>
@@ -36734,7 +36754,7 @@
         <v>81</v>
       </c>
       <c r="M24" s="298" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N24" s="110" t="s">
         <v>46</v>
@@ -36771,7 +36791,7 @@
         <v>97</v>
       </c>
       <c r="F25" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G25" s="243" t="s">
         <v>52</v>
@@ -36780,7 +36800,7 @@
         <v>73</v>
       </c>
       <c r="I25" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J25" s="243" t="s">
         <v>51</v>
@@ -36792,7 +36812,7 @@
         <v>81</v>
       </c>
       <c r="M25" s="298" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N25" s="110" t="s">
         <v>80</v>
@@ -36832,13 +36852,13 @@
         <v>80</v>
       </c>
       <c r="G26" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H26" s="243" t="s">
         <v>59</v>
       </c>
       <c r="I26" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J26" s="243" t="s">
         <v>51</v>
@@ -36850,7 +36870,7 @@
         <v>94</v>
       </c>
       <c r="M26" s="298" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N26" s="110" t="s">
         <v>81</v>
@@ -36887,7 +36907,7 @@
         <v>96</v>
       </c>
       <c r="F27" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G27" s="243" t="s">
         <v>52</v>
@@ -36914,10 +36934,10 @@
         <v>87</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Q27" s="2" t="s">
         <v>106</v>
@@ -36943,7 +36963,7 @@
         <v>97</v>
       </c>
       <c r="F28" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G28" s="243" t="s">
         <v>52</v>
@@ -36970,13 +36990,13 @@
         <v>96</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R28" s="159" t="s">
         <v>94</v>
@@ -37001,7 +37021,7 @@
         <v>105</v>
       </c>
       <c r="F29" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G29" s="243" t="s">
         <v>52</v>
@@ -37022,10 +37042,10 @@
         <v>46</v>
       </c>
       <c r="M29" s="298" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N29" s="110" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>81</v>
@@ -37059,7 +37079,7 @@
         <v>105</v>
       </c>
       <c r="F30" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G30" s="243" t="s">
         <v>52</v>
@@ -37068,7 +37088,7 @@
         <v>73</v>
       </c>
       <c r="I30" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J30" s="243" t="s">
         <v>51</v>
@@ -37092,7 +37112,7 @@
         <v>83</v>
       </c>
       <c r="Q30" s="159" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R30" s="159"/>
       <c r="S30" s="51"/>
@@ -37115,7 +37135,7 @@
         <v>97</v>
       </c>
       <c r="F31" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G31" s="243" t="s">
         <v>52</v>
@@ -37136,10 +37156,10 @@
         <v>46</v>
       </c>
       <c r="M31" s="298" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N31" s="110" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>80</v>
@@ -37171,7 +37191,7 @@
         <v>97</v>
       </c>
       <c r="F32" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G32" s="243" t="s">
         <v>52</v>
@@ -37198,10 +37218,10 @@
         <v>59</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Q32" s="159" t="s">
         <v>54</v>
@@ -37223,7 +37243,7 @@
         <v>107</v>
       </c>
       <c r="D33" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E33" s="243" t="s">
         <v>89</v>
@@ -37250,10 +37270,10 @@
         <v>46</v>
       </c>
       <c r="M33" s="298" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N33" s="110" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>87</v>
@@ -37275,22 +37295,54 @@
       <c r="B34" s="264" t="s">
         <v>367</v>
       </c>
-      <c r="C34" s="297"/>
-      <c r="D34" s="243"/>
-      <c r="E34" s="243"/>
-      <c r="F34" s="243"/>
-      <c r="G34" s="243"/>
-      <c r="H34" s="243"/>
-      <c r="I34" s="243"/>
-      <c r="J34" s="243"/>
-      <c r="K34" s="243"/>
-      <c r="L34" s="243"/>
-      <c r="M34" s="298"/>
-      <c r="N34" s="110"/>
-      <c r="O34" s="2"/>
-      <c r="P34" s="2"/>
-      <c r="Q34" s="159"/>
-      <c r="R34" s="159"/>
+      <c r="C34" s="297" t="s">
+        <v>107</v>
+      </c>
+      <c r="D34" s="243" t="s">
+        <v>63</v>
+      </c>
+      <c r="E34" s="243" t="s">
+        <v>89</v>
+      </c>
+      <c r="F34" s="243" t="s">
+        <v>97</v>
+      </c>
+      <c r="G34" s="243" t="s">
+        <v>52</v>
+      </c>
+      <c r="H34" s="243" t="s">
+        <v>102</v>
+      </c>
+      <c r="I34" s="243" t="s">
+        <v>73</v>
+      </c>
+      <c r="J34" s="243" t="s">
+        <v>51</v>
+      </c>
+      <c r="K34" s="243" t="s">
+        <v>87</v>
+      </c>
+      <c r="L34" s="243" t="s">
+        <v>46</v>
+      </c>
+      <c r="M34" s="298" t="s">
+        <v>81</v>
+      </c>
+      <c r="N34" s="110" t="s">
+        <v>59</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="P34" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q34" s="159" t="s">
+        <v>106</v>
+      </c>
+      <c r="R34" s="159" t="s">
+        <v>70</v>
+      </c>
       <c r="S34" s="51"/>
       <c r="T34" s="1"/>
     </row>
@@ -37492,7 +37544,7 @@
         <v>4</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C46" s="2">
         <v>1</v>
@@ -37509,7 +37561,7 @@
         <v>5</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C47" s="2">
         <v>4</v>
@@ -37577,7 +37629,7 @@
         <v>9</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C51" s="2">
         <v>2</v>
@@ -37594,7 +37646,7 @@
         <v>10</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C52" s="2">
         <v>6</v>
@@ -37611,7 +37663,7 @@
         <v>11</v>
       </c>
       <c r="B53" s="266" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C53" s="2">
         <v>6</v>
@@ -37628,7 +37680,7 @@
         <v>12</v>
       </c>
       <c r="B54" s="319" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C54" s="2">
         <v>1</v>
@@ -37707,7 +37759,7 @@
         <v>17</v>
       </c>
       <c r="B59" s="352" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="96"/>
@@ -37718,7 +37770,7 @@
         <v>18</v>
       </c>
       <c r="B60" s="352" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="96"/>
@@ -37751,7 +37803,7 @@
         <v>21</v>
       </c>
       <c r="B63" s="352" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="96"/>
@@ -37762,7 +37814,7 @@
         <v>22</v>
       </c>
       <c r="B64" s="413" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C64" s="441"/>
       <c r="D64" s="442"/>
@@ -37795,7 +37847,7 @@
         <v>25</v>
       </c>
       <c r="B67" s="352" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="96"/>
@@ -37806,7 +37858,7 @@
         <v>26</v>
       </c>
       <c r="B68" s="352" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="96"/>
@@ -37850,7 +37902,7 @@
         <v>30</v>
       </c>
       <c r="B72" s="352" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" s="96"/>
@@ -37872,7 +37924,7 @@
         <v>32</v>
       </c>
       <c r="B74" s="352" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" s="96"/>
@@ -37883,7 +37935,7 @@
         <v>33</v>
       </c>
       <c r="B75" s="413" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C75" s="441"/>
       <c r="D75" s="442"/>
@@ -38485,7 +38537,7 @@
         <v>144</v>
       </c>
       <c r="X4" s="60" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Y4" s="297">
         <f t="shared" si="0"/>
@@ -38650,13 +38702,13 @@
       <c r="K5" s="266"/>
       <c r="L5" s="269"/>
       <c r="M5" s="246" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N5" s="270"/>
       <c r="O5" s="270"/>
       <c r="P5" s="271"/>
       <c r="Q5" s="272" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R5" s="270"/>
       <c r="S5" s="270"/>
@@ -38898,7 +38950,7 @@
         <v>10</v>
       </c>
       <c r="AM6" s="337" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AN6" s="337" t="s">
         <v>30</v>
@@ -39522,7 +39574,7 @@
         <v>52</v>
       </c>
       <c r="R10" s="270" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S10" s="270"/>
       <c r="T10" s="270"/>
@@ -39702,10 +39754,10 @@
         <v>46</v>
       </c>
       <c r="R11" s="270" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S11" s="270" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T11" s="270"/>
       <c r="U11" s="273"/>
@@ -39881,7 +39933,7 @@
       <c r="Q12" s="272"/>
       <c r="R12" s="270"/>
       <c r="S12" s="270" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="T12" s="270"/>
       <c r="U12" s="273">
@@ -40047,13 +40099,13 @@
       <c r="K13" s="266"/>
       <c r="L13" s="269"/>
       <c r="M13" s="246" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N13" s="270" t="s">
         <v>140</v>
       </c>
       <c r="O13" s="270" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P13" s="271"/>
       <c r="Q13" s="272" t="s">
@@ -40236,7 +40288,7 @@
       <c r="P14" s="271"/>
       <c r="Q14" s="272"/>
       <c r="R14" s="270" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S14" s="270"/>
       <c r="T14" s="270"/>
@@ -40581,7 +40633,7 @@
         <v>46</v>
       </c>
       <c r="O16" s="58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P16" s="59"/>
       <c r="Q16" s="143"/>
@@ -40749,7 +40801,7 @@
       <c r="K17" s="24"/>
       <c r="L17" s="41"/>
       <c r="M17" s="57" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N17" s="58"/>
       <c r="O17" s="58"/>
@@ -40929,7 +40981,7 @@
       <c r="O18" s="58"/>
       <c r="P18" s="59"/>
       <c r="Q18" s="143" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R18" s="58" t="s">
         <v>140</v>
@@ -41097,7 +41149,7 @@
       <c r="K19" s="24"/>
       <c r="L19" s="41"/>
       <c r="M19" s="57" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N19" s="58" t="s">
         <v>46</v>
@@ -41106,7 +41158,7 @@
       <c r="P19" s="59"/>
       <c r="Q19" s="143"/>
       <c r="R19" s="58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S19" s="58"/>
       <c r="T19" s="58"/>
@@ -41210,7 +41262,7 @@
         <v>0</v>
       </c>
       <c r="BA19" s="20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="BB19" s="2">
         <f t="shared" si="8"/>
@@ -41539,7 +41591,7 @@
       <c r="O22" s="58"/>
       <c r="P22" s="59"/>
       <c r="Q22" s="143" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R22" s="58"/>
       <c r="S22" s="58"/>
@@ -41797,13 +41849,13 @@
       <c r="K24" s="24"/>
       <c r="L24" s="41"/>
       <c r="M24" s="57" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N24" s="58" t="s">
         <v>171</v>
       </c>
       <c r="O24" s="58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P24" s="59" t="s">
         <v>46</v>
@@ -42009,7 +42061,7 @@
       <c r="O26" s="58"/>
       <c r="P26" s="59"/>
       <c r="Q26" s="143" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R26" s="58" t="s">
         <v>143</v>
@@ -42205,20 +42257,20 @@
       <c r="K28" s="24"/>
       <c r="L28" s="41"/>
       <c r="M28" s="57" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N28" s="58" t="s">
         <v>114</v>
       </c>
       <c r="O28" s="58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P28" s="59" t="s">
         <v>54</v>
       </c>
       <c r="Q28" s="143"/>
       <c r="R28" s="58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S28" s="58" t="s">
         <v>54</v>
@@ -42320,7 +42372,7 @@
       <c r="O29" s="270"/>
       <c r="P29" s="271"/>
       <c r="Q29" s="272" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R29" s="270"/>
       <c r="S29" s="270"/>
@@ -42332,7 +42384,7 @@
         <v>168</v>
       </c>
       <c r="X29" s="329" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Y29" s="297">
         <f t="shared" si="0"/>
@@ -42424,7 +42476,7 @@
       <c r="T30" s="270"/>
       <c r="U30" s="273"/>
       <c r="V30" s="274" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="X30" s="329" t="s">
         <v>80</v>
@@ -42526,10 +42578,10 @@
       </c>
       <c r="R31" s="270"/>
       <c r="S31" s="270" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T31" s="270" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="U31" s="273"/>
       <c r="V31" s="274" t="s">
@@ -43019,7 +43071,7 @@
       <c r="O36" s="270"/>
       <c r="P36" s="271"/>
       <c r="Q36" s="272" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R36" s="270"/>
       <c r="S36" s="270"/>
@@ -43112,7 +43164,7 @@
       <c r="K37" s="266"/>
       <c r="L37" s="269"/>
       <c r="M37" s="246" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N37" s="270"/>
       <c r="O37" s="270"/>
@@ -43211,7 +43263,7 @@
       <c r="K38" s="266"/>
       <c r="L38" s="269"/>
       <c r="M38" s="275" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N38" s="270" t="s">
         <v>46</v>
@@ -44192,7 +44244,7 @@
         <v>97</v>
       </c>
       <c r="F2" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G2" s="243" t="s">
         <v>80</v>
@@ -44207,7 +44259,7 @@
         <v>143</v>
       </c>
       <c r="K2" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L2" s="243" t="s">
         <v>54</v>
@@ -44302,7 +44354,7 @@
         <v>97</v>
       </c>
       <c r="F3" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G3" s="243" t="s">
         <v>80</v>
@@ -44317,7 +44369,7 @@
         <v>143</v>
       </c>
       <c r="K3" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L3" s="243" t="s">
         <v>54</v>
@@ -44414,7 +44466,7 @@
         <v>97</v>
       </c>
       <c r="F4" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G4" s="243" t="s">
         <v>80</v>
@@ -44429,7 +44481,7 @@
         <v>143</v>
       </c>
       <c r="K4" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L4" s="243" t="s">
         <v>54</v>
@@ -44524,7 +44576,7 @@
         <v>97</v>
       </c>
       <c r="F5" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G5" s="243" t="s">
         <v>80</v>
@@ -44539,7 +44591,7 @@
         <v>143</v>
       </c>
       <c r="K5" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L5" s="243" t="s">
         <v>87</v>
@@ -44602,7 +44654,7 @@
         <v>97</v>
       </c>
       <c r="F6" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G6" s="243" t="s">
         <v>80</v>
@@ -44617,7 +44669,7 @@
         <v>143</v>
       </c>
       <c r="K6" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L6" s="243" t="s">
         <v>54</v>
@@ -44680,7 +44732,7 @@
         <v>97</v>
       </c>
       <c r="F7" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G7" s="243" t="s">
         <v>52</v>
@@ -44707,7 +44759,7 @@
         <v>80</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>156</v>
@@ -44758,7 +44810,7 @@
         <v>97</v>
       </c>
       <c r="F8" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G8" s="243" t="s">
         <v>80</v>
@@ -44770,7 +44822,7 @@
         <v>73</v>
       </c>
       <c r="J8" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K8" s="243" t="s">
         <v>140</v>
@@ -44816,7 +44868,7 @@
         <v>97</v>
       </c>
       <c r="F9" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G9" s="243" t="s">
         <v>52</v>
@@ -44828,7 +44880,7 @@
         <v>73</v>
       </c>
       <c r="J9" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K9" s="243" t="s">
         <v>140</v>
@@ -44874,7 +44926,7 @@
         <v>97</v>
       </c>
       <c r="F10" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G10" s="243" t="s">
         <v>52</v>
@@ -44886,7 +44938,7 @@
         <v>73</v>
       </c>
       <c r="J10" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K10" s="243" t="s">
         <v>156</v>
@@ -44932,7 +44984,7 @@
         <v>97</v>
       </c>
       <c r="F11" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G11" s="243" t="s">
         <v>52</v>
@@ -44944,7 +44996,7 @@
         <v>73</v>
       </c>
       <c r="J11" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K11" s="243" t="s">
         <v>140</v>
@@ -44990,7 +45042,7 @@
         <v>97</v>
       </c>
       <c r="F12" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G12" s="243" t="s">
         <v>52</v>
@@ -45002,7 +45054,7 @@
         <v>73</v>
       </c>
       <c r="J12" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K12" s="243" t="s">
         <v>140</v>
@@ -45048,7 +45100,7 @@
         <v>97</v>
       </c>
       <c r="F13" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G13" s="243" t="s">
         <v>52</v>
@@ -45060,7 +45112,7 @@
         <v>73</v>
       </c>
       <c r="J13" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K13" s="243" t="s">
         <v>140</v>
@@ -45106,7 +45158,7 @@
         <v>97</v>
       </c>
       <c r="F14" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G14" s="243" t="s">
         <v>52</v>
@@ -45118,7 +45170,7 @@
         <v>73</v>
       </c>
       <c r="J14" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K14" s="243" t="s">
         <v>140</v>
@@ -45164,7 +45216,7 @@
         <v>97</v>
       </c>
       <c r="F15" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G15" s="243" t="s">
         <v>52</v>
@@ -45176,7 +45228,7 @@
         <v>73</v>
       </c>
       <c r="J15" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K15" s="243" t="s">
         <v>140</v>
@@ -45222,7 +45274,7 @@
         <v>97</v>
       </c>
       <c r="F16" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G16" s="243" t="s">
         <v>52</v>
@@ -45234,7 +45286,7 @@
         <v>73</v>
       </c>
       <c r="J16" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K16" s="243" t="s">
         <v>140</v>
@@ -45280,7 +45332,7 @@
         <v>97</v>
       </c>
       <c r="F17" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G17" s="243" t="s">
         <v>52</v>
@@ -45292,7 +45344,7 @@
         <v>73</v>
       </c>
       <c r="J17" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K17" s="243" t="s">
         <v>140</v>
@@ -45338,7 +45390,7 @@
         <v>97</v>
       </c>
       <c r="F18" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G18" s="243" t="s">
         <v>52</v>
@@ -45350,7 +45402,7 @@
         <v>80</v>
       </c>
       <c r="J18" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K18" s="243" t="s">
         <v>140</v>
@@ -45396,7 +45448,7 @@
         <v>97</v>
       </c>
       <c r="F19" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G19" s="243" t="s">
         <v>52</v>
@@ -45408,7 +45460,7 @@
         <v>73</v>
       </c>
       <c r="J19" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K19" s="243" t="s">
         <v>143</v>
@@ -45454,7 +45506,7 @@
         <v>97</v>
       </c>
       <c r="F20" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G20" s="243" t="s">
         <v>52</v>
@@ -45466,7 +45518,7 @@
         <v>73</v>
       </c>
       <c r="J20" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K20" s="243" t="s">
         <v>140</v>
@@ -45524,7 +45576,7 @@
         <v>73</v>
       </c>
       <c r="J21" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K21" s="243" t="s">
         <v>140</v>
@@ -45582,7 +45634,7 @@
         <v>73</v>
       </c>
       <c r="J22" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K22" s="243" t="s">
         <v>140</v>
@@ -45628,7 +45680,7 @@
         <v>97</v>
       </c>
       <c r="F23" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G23" s="243" t="s">
         <v>52</v>
@@ -45640,7 +45692,7 @@
         <v>73</v>
       </c>
       <c r="J23" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K23" s="243" t="s">
         <v>156</v>
@@ -45684,7 +45736,7 @@
         <v>97</v>
       </c>
       <c r="F24" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G24" s="243" t="s">
         <v>52</v>
@@ -45696,7 +45748,7 @@
         <v>73</v>
       </c>
       <c r="J24" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K24" s="243" t="s">
         <v>140</v>
@@ -45744,7 +45796,7 @@
         <v>97</v>
       </c>
       <c r="F25" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G25" s="243" t="s">
         <v>87</v>
@@ -45756,7 +45808,7 @@
         <v>73</v>
       </c>
       <c r="J25" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K25" s="243" t="s">
         <v>140</v>
@@ -45802,7 +45854,7 @@
         <v>97</v>
       </c>
       <c r="F26" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G26" s="243" t="s">
         <v>87</v>
@@ -45814,7 +45866,7 @@
         <v>73</v>
       </c>
       <c r="J26" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K26" s="243" t="s">
         <v>156</v>
@@ -45860,7 +45912,7 @@
         <v>97</v>
       </c>
       <c r="F27" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G27" s="243" t="s">
         <v>52</v>
@@ -45872,7 +45924,7 @@
         <v>73</v>
       </c>
       <c r="J27" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K27" s="243" t="s">
         <v>92</v>
@@ -45918,7 +45970,7 @@
         <v>97</v>
       </c>
       <c r="F28" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G28" s="243" t="s">
         <v>52</v>
@@ -45930,7 +45982,7 @@
         <v>73</v>
       </c>
       <c r="J28" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K28" s="243" t="s">
         <v>92</v>
@@ -45976,7 +46028,7 @@
         <v>97</v>
       </c>
       <c r="F29" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G29" s="243" t="s">
         <v>52</v>
@@ -45988,7 +46040,7 @@
         <v>73</v>
       </c>
       <c r="J29" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K29" s="243" t="s">
         <v>140</v>
@@ -46034,7 +46086,7 @@
         <v>97</v>
       </c>
       <c r="F30" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G30" s="243" t="s">
         <v>52</v>
@@ -46046,7 +46098,7 @@
         <v>73</v>
       </c>
       <c r="J30" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K30" s="243" t="s">
         <v>140</v>
@@ -46092,7 +46144,7 @@
         <v>97</v>
       </c>
       <c r="F31" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G31" s="243" t="s">
         <v>99</v>
@@ -46104,7 +46156,7 @@
         <v>176</v>
       </c>
       <c r="J31" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K31" s="243" t="s">
         <v>140</v>
@@ -46150,7 +46202,7 @@
         <v>97</v>
       </c>
       <c r="F32" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G32" s="243" t="s">
         <v>99</v>
@@ -46206,7 +46258,7 @@
         <v>97</v>
       </c>
       <c r="F33" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G33" s="243" t="s">
         <v>99</v>
@@ -46218,7 +46270,7 @@
         <v>73</v>
       </c>
       <c r="J33" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K33" s="243" t="s">
         <v>140</v>
@@ -46264,7 +46316,7 @@
         <v>97</v>
       </c>
       <c r="F34" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G34" s="243" t="s">
         <v>87</v>
@@ -46276,7 +46328,7 @@
         <v>73</v>
       </c>
       <c r="J34" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K34" s="243" t="s">
         <v>140</v>
@@ -46322,7 +46374,7 @@
         <v>97</v>
       </c>
       <c r="F35" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G35" s="243" t="s">
         <v>87</v>
@@ -46334,7 +46386,7 @@
         <v>73</v>
       </c>
       <c r="J35" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K35" s="243" t="s">
         <v>156</v>
@@ -46380,7 +46432,7 @@
         <v>97</v>
       </c>
       <c r="F36" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G36" s="243" t="s">
         <v>80</v>
@@ -46392,7 +46444,7 @@
         <v>73</v>
       </c>
       <c r="J36" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K36" s="243" t="s">
         <v>87</v>
@@ -46434,7 +46486,7 @@
         <v>97</v>
       </c>
       <c r="F37" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G37" s="243" t="s">
         <v>80</v>
@@ -46446,7 +46498,7 @@
         <v>73</v>
       </c>
       <c r="J37" s="243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K37" s="243" t="s">
         <v>140</v>
@@ -46492,7 +46544,7 @@
         <v>97</v>
       </c>
       <c r="F38" s="243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G38" s="243" t="s">
         <v>80</v>
@@ -46522,7 +46574,7 @@
         <v>46</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q38" s="2" t="s">
         <v>140</v>
@@ -46639,7 +46691,7 @@
         <v>73</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>46</v>
@@ -46821,10 +46873,10 @@
         <v>34</v>
       </c>
       <c r="C2" s="249" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D2" s="249" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="2:4">
@@ -46832,7 +46884,7 @@
         <v>44</v>
       </c>
       <c r="C3" s="251" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D3" s="252"/>
     </row>
@@ -47486,7 +47538,7 @@
       <c r="U4" s="56"/>
       <c r="V4" s="192"/>
       <c r="X4" s="148" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Y4" s="153">
         <f t="shared" si="0"/>
@@ -47633,7 +47685,7 @@
       <c r="O5" s="15"/>
       <c r="P5" s="54"/>
       <c r="Q5" s="171" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R5" s="15"/>
       <c r="S5" s="15"/>
@@ -47753,7 +47805,7 @@
         <v>4</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E6" s="30" t="s">
         <v>45</v>
@@ -47777,7 +47829,7 @@
         <v>249</v>
       </c>
       <c r="L6" s="53" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M6" s="15" t="s">
         <v>166</v>
@@ -47938,7 +47990,7 @@
         <v>46</v>
       </c>
       <c r="N7" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O7" s="15"/>
       <c r="P7" s="54"/>
@@ -48059,7 +48111,7 @@
         <v>6</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E8" s="30" t="s">
         <v>45</v>
@@ -48365,7 +48417,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E10" s="30" t="s">
         <v>49</v>
@@ -48396,7 +48448,7 @@
       <c r="O10" s="15"/>
       <c r="P10" s="54"/>
       <c r="Q10" s="171" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R10" s="15"/>
       <c r="S10" s="15"/>
@@ -48623,7 +48675,7 @@
         <v>10</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E12" s="30" t="s">
         <v>45</v>
@@ -48661,10 +48713,10 @@
         <v>268</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S12" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T12" s="15"/>
       <c r="U12" s="56"/>
@@ -48800,7 +48852,7 @@
         <v>46</v>
       </c>
       <c r="M13" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N13" s="15"/>
       <c r="O13" s="15"/>
@@ -49085,7 +49137,7 @@
         <v>13</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E15" s="24" t="s">
         <v>49</v>
@@ -49631,7 +49683,7 @@
         <v>17</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E19" s="24" t="s">
         <v>49</v>
@@ -49919,7 +49971,7 @@
         <v>19</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E21" s="24" t="s">
         <v>49</v>
@@ -50063,7 +50115,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E22" s="24" t="s">
         <v>45</v>
@@ -50289,7 +50341,7 @@
         <v>0</v>
       </c>
       <c r="AJ23" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AK23" s="4" t="s">
         <v>30</v>
@@ -50808,7 +50860,7 @@
         <v>42</v>
       </c>
       <c r="AJ27" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="AK27" s="2">
         <f t="shared" si="18"/>
@@ -50858,7 +50910,7 @@
         <v>26</v>
       </c>
       <c r="D28" s="30" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E28" s="30" t="s">
         <v>49</v>
@@ -50989,7 +51041,7 @@
         <v>27</v>
       </c>
       <c r="D29" s="73" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E29" s="30" t="s">
         <v>49</v>
@@ -51120,7 +51172,7 @@
         <v>28</v>
       </c>
       <c r="D30" s="30" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E30" s="30" t="s">
         <v>45</v>
@@ -51199,7 +51251,7 @@
         <v>42</v>
       </c>
       <c r="AJ30" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AK30" s="2">
         <f t="shared" si="18"/>
@@ -51334,7 +51386,7 @@
         <v>42</v>
       </c>
       <c r="AJ31" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AK31" s="2">
         <f t="shared" si="18"/>
@@ -51590,7 +51642,7 @@
         <v>42</v>
       </c>
       <c r="AJ33" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AK33" s="2">
         <f t="shared" si="18"/>
@@ -51767,7 +51819,7 @@
         <v>33</v>
       </c>
       <c r="D35" s="73" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E35" s="30" t="s">
         <v>45</v>
@@ -51858,7 +51910,7 @@
         <v>34</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E36" s="24" t="s">
         <v>45</v>
@@ -51882,7 +51934,7 @@
         <v>273</v>
       </c>
       <c r="L36" s="57" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M36" s="58"/>
       <c r="N36" s="58"/>
@@ -52036,7 +52088,7 @@
         <v>36</v>
       </c>
       <c r="D38" s="73" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E38" s="24" t="s">
         <v>49</v>
@@ -52121,7 +52173,7 @@
         <v>37</v>
       </c>
       <c r="D39" s="24" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E39" s="24" t="s">
         <v>45</v>
@@ -52139,7 +52191,7 @@
       <c r="J39" s="24"/>
       <c r="K39" s="24"/>
       <c r="L39" s="57" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M39" s="58"/>
       <c r="N39" s="58"/>
@@ -52224,10 +52276,10 @@
       <c r="J40" s="238"/>
       <c r="K40" s="238"/>
       <c r="L40" s="226" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M40" s="227" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N40" s="227" t="s">
         <v>264</v>
@@ -52324,7 +52376,7 @@
       <c r="O41" s="129"/>
       <c r="P41" s="175"/>
       <c r="Q41" s="172" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R41" s="129"/>
       <c r="S41" s="129"/>
@@ -52942,7 +52994,7 @@
         <v>46</v>
       </c>
       <c r="L2" s="155" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M2" s="110" t="s">
         <v>271</v>
@@ -52996,7 +53048,7 @@
         <v>261</v>
       </c>
       <c r="AE2" s="110" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AF2" s="2" t="s">
         <v>54</v>
@@ -53049,7 +53101,7 @@
         <v>87</v>
       </c>
       <c r="M3" s="110" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>271</v>
@@ -53112,7 +53164,7 @@
         <v>46</v>
       </c>
       <c r="L4" s="155" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M4" s="110" t="s">
         <v>87</v>
@@ -53176,7 +53228,7 @@
         <v>271</v>
       </c>
       <c r="L5" s="155" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M5" s="110" t="s">
         <v>111</v>
@@ -53251,7 +53303,7 @@
         <v>87</v>
       </c>
       <c r="M6" s="110" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>170</v>
@@ -53320,7 +53372,7 @@
         <v>46</v>
       </c>
       <c r="L7" s="155" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M7" s="110" t="s">
         <v>93</v>
@@ -53404,7 +53456,7 @@
         <v>170</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q8" s="51"/>
     </row>
@@ -53443,7 +53495,7 @@
         <v>46</v>
       </c>
       <c r="L9" s="155" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M9" s="110" t="s">
         <v>280</v>
@@ -53497,7 +53549,7 @@
         <v>261</v>
       </c>
       <c r="M10" s="110" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>46</v>
@@ -53547,7 +53599,7 @@
         <v>46</v>
       </c>
       <c r="L11" s="155" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M11" s="110" t="s">
         <v>170</v>
@@ -53603,7 +53655,7 @@
         <v>87</v>
       </c>
       <c r="M12" s="110" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>272</v>
@@ -53647,7 +53699,7 @@
         <v>93</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K13" s="5" t="s">
         <v>46</v>
@@ -53812,7 +53864,7 @@
         <v>271</v>
       </c>
       <c r="L16" s="155" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M16" s="110" t="s">
         <v>143</v>
@@ -53871,7 +53923,7 @@
         <v>170</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>171</v>
@@ -53918,7 +53970,7 @@
         <v>271</v>
       </c>
       <c r="L18" s="155" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M18" s="110" t="s">
         <v>143</v>
@@ -54440,7 +54492,7 @@
         <v>143</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>189</v>
@@ -54481,7 +54533,7 @@
         <v>170</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K29" s="5" t="s">
         <v>46</v>
@@ -54534,7 +54586,7 @@
         <v>170</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K30" s="5" t="s">
         <v>46</v>
@@ -54587,7 +54639,7 @@
         <v>170</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K31" s="5" t="s">
         <v>143</v>
@@ -54652,7 +54704,7 @@
         <v>143</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>272</v>
@@ -54693,7 +54745,7 @@
         <v>170</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K33" s="5" t="s">
         <v>46</v>
@@ -54756,7 +54808,7 @@
         <v>87</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>111</v>
@@ -54800,7 +54852,7 @@
         <v>93</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L35" s="155" t="s">
         <v>92</v>
@@ -54853,7 +54905,7 @@
         <v>93</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L36" s="155" t="s">
         <v>46</v>

--- a/인천 2026 기록.xlsx
+++ b/인천 2026 기록.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://familyinter-my.sharepoint.com/personal/hwlee_familyinter_onmicrosoft_com/Documents/바탕 화면/프로젝트300/대시보드/인천 대시보드/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1210" documentId="11_0F6BF197949C94B063893377604B65CBEB673EAF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DDB606E-B619-4BAE-903E-6C3CD5BA9300}"/>
+  <xr:revisionPtr revIDLastSave="2420" documentId="11_0F6BF197949C94B063893377604B65CBEB673EAF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FB83256-7AE5-4F4E-B1C9-4A450BF7E091}"/>
   <bookViews>
     <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4961,6 +4961,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="기록표" displayName="기록표" ref="A42:E57" totalsRowShown="0" headerRowDxfId="84" headerRowBorderDxfId="83" tableBorderDxfId="82" totalsRowBorderDxfId="81">
   <tableColumns count="5">

--- a/인천 2026 기록.xlsx
+++ b/인천 2026 기록.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://familyinter-my.sharepoint.com/personal/hwlee_familyinter_onmicrosoft_com/Documents/바탕 화면/프로젝트300/대시보드/인천 대시보드/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2420" documentId="11_0F6BF197949C94B063893377604B65CBEB673EAF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FB83256-7AE5-4F4E-B1C9-4A450BF7E091}"/>
+  <xr:revisionPtr revIDLastSave="1235" documentId="11_ED78F197949CE43D6C65107960F9FD0C2CCB1E64" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B5AC954-68F7-4392-8E5F-ACDD773A42C8}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2660" yWindow="2660" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 토탈" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6134" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6159" uniqueCount="400">
   <si>
     <t>리그</t>
   </si>
@@ -1288,6 +1288,26 @@
   </si>
   <si>
     <t>10월 24일</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>11월 1일</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>11월 8일</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>11월 21일</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>11월 29일</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>12월 6일</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -4961,10 +4981,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="기록표" displayName="기록표" ref="A42:E57" totalsRowShown="0" headerRowDxfId="84" headerRowBorderDxfId="83" tableBorderDxfId="82" totalsRowBorderDxfId="81">
   <tableColumns count="5">
@@ -5330,7 +5346,7 @@
         <v>1</v>
       </c>
       <c r="BI1" s="478" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="BJ1" s="477"/>
       <c r="BK1" s="477"/>
@@ -6732,7 +6748,7 @@
         <v>6</v>
       </c>
       <c r="BJ8" s="471" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="BK8" s="471">
         <v>33</v>
@@ -10235,13 +10251,21 @@
       <c r="A36" s="367" t="s">
         <v>338</v>
       </c>
-      <c r="B36" s="396"/>
-      <c r="C36" s="397"/>
+      <c r="B36" s="396" t="s">
+        <v>393</v>
+      </c>
+      <c r="C36" s="397" t="s">
+        <v>348</v>
+      </c>
       <c r="D36" s="319">
         <v>34</v>
       </c>
-      <c r="E36" s="352"/>
-      <c r="F36" s="319"/>
+      <c r="E36" s="352" t="s">
+        <v>341</v>
+      </c>
+      <c r="F36" s="319" t="s">
+        <v>346</v>
+      </c>
       <c r="G36" s="319"/>
       <c r="H36" s="319"/>
       <c r="I36" s="398"/>
@@ -10314,13 +10338,21 @@
       <c r="A37" s="367" t="s">
         <v>338</v>
       </c>
-      <c r="B37" s="396"/>
-      <c r="C37" s="397"/>
+      <c r="B37" s="396" t="s">
+        <v>394</v>
+      </c>
+      <c r="C37" s="397" t="s">
+        <v>348</v>
+      </c>
       <c r="D37" s="319">
         <v>35</v>
       </c>
-      <c r="E37" s="352"/>
-      <c r="F37" s="319"/>
+      <c r="E37" s="352" t="s">
+        <v>353</v>
+      </c>
+      <c r="F37" s="319" t="s">
+        <v>346</v>
+      </c>
       <c r="G37" s="319"/>
       <c r="H37" s="319"/>
       <c r="I37" s="398"/>
@@ -10393,13 +10425,21 @@
       <c r="A38" s="367" t="s">
         <v>338</v>
       </c>
-      <c r="B38" s="396"/>
-      <c r="C38" s="397"/>
+      <c r="B38" s="396" t="s">
+        <v>395</v>
+      </c>
+      <c r="C38" s="397" t="s">
+        <v>340</v>
+      </c>
       <c r="D38" s="319">
         <v>36</v>
       </c>
-      <c r="E38" s="352"/>
-      <c r="F38" s="401"/>
+      <c r="E38" s="352" t="s">
+        <v>360</v>
+      </c>
+      <c r="F38" s="401" t="s">
+        <v>342</v>
+      </c>
       <c r="G38" s="319"/>
       <c r="H38" s="319"/>
       <c r="I38" s="398"/>
@@ -10472,13 +10512,21 @@
       <c r="A39" s="367" t="s">
         <v>338</v>
       </c>
-      <c r="B39" s="396"/>
-      <c r="C39" s="397"/>
+      <c r="B39" s="396" t="s">
+        <v>396</v>
+      </c>
+      <c r="C39" s="397" t="s">
+        <v>348</v>
+      </c>
       <c r="D39" s="319">
         <v>37</v>
       </c>
-      <c r="E39" s="352"/>
-      <c r="F39" s="401"/>
+      <c r="E39" s="352" t="s">
+        <v>369</v>
+      </c>
+      <c r="F39" s="401" t="s">
+        <v>342</v>
+      </c>
       <c r="G39" s="319"/>
       <c r="H39" s="319"/>
       <c r="I39" s="398"/>
@@ -10551,13 +10599,21 @@
       <c r="A40" s="411" t="s">
         <v>338</v>
       </c>
-      <c r="B40" s="429"/>
-      <c r="C40" s="430"/>
+      <c r="B40" s="429" t="s">
+        <v>397</v>
+      </c>
+      <c r="C40" s="430" t="s">
+        <v>348</v>
+      </c>
       <c r="D40" s="412">
         <v>38</v>
       </c>
-      <c r="E40" s="413"/>
-      <c r="F40" s="412"/>
+      <c r="E40" s="413" t="s">
+        <v>365</v>
+      </c>
+      <c r="F40" s="412" t="s">
+        <v>346</v>
+      </c>
       <c r="G40" s="412"/>
       <c r="H40" s="412"/>
       <c r="I40" s="414"/>
@@ -37354,7 +37410,9 @@
       <c r="A35" s="159">
         <v>34</v>
       </c>
-      <c r="B35" s="264"/>
+      <c r="B35" s="264" t="s">
+        <v>44</v>
+      </c>
       <c r="C35" s="297"/>
       <c r="D35" s="243"/>
       <c r="E35" s="243"/>
@@ -37378,7 +37436,9 @@
       <c r="A36" s="159">
         <v>35</v>
       </c>
-      <c r="B36" s="264"/>
+      <c r="B36" s="264" t="s">
+        <v>61</v>
+      </c>
       <c r="C36" s="297"/>
       <c r="D36" s="243"/>
       <c r="E36" s="243"/>
@@ -37402,7 +37462,9 @@
       <c r="A37" s="159">
         <v>36</v>
       </c>
-      <c r="B37" s="264"/>
+      <c r="B37" s="264" t="s">
+        <v>55</v>
+      </c>
       <c r="C37" s="297"/>
       <c r="D37" s="243"/>
       <c r="E37" s="243"/>
@@ -37426,7 +37488,9 @@
       <c r="A38" s="159">
         <v>37</v>
       </c>
-      <c r="B38" s="264"/>
+      <c r="B38" s="264" t="s">
+        <v>71</v>
+      </c>
       <c r="C38" s="297"/>
       <c r="D38" s="243"/>
       <c r="E38" s="243"/>
@@ -37450,7 +37514,9 @@
       <c r="A39" s="159">
         <v>38</v>
       </c>
-      <c r="B39" s="390"/>
+      <c r="B39" s="390" t="s">
+        <v>67</v>
+      </c>
       <c r="C39" s="297"/>
       <c r="D39" s="243"/>
       <c r="E39" s="243"/>

--- a/인천 2026 기록.xlsx
+++ b/인천 2026 기록.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://familyinter-my.sharepoint.com/personal/hwlee_familyinter_onmicrosoft_com/Documents/바탕 화면/프로젝트300/대시보드/인천 대시보드/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1235" documentId="11_ED78F197949CE43D6C65107960F9FD0C2CCB1E64" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B5AC954-68F7-4392-8E5F-ACDD773A42C8}"/>
+  <xr:revisionPtr revIDLastSave="2470" documentId="11_ED78F197949CE43D6C65107960F9FD0C2CCB1E64" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C788D65D-16B6-4CA7-8F0E-741122600F61}"/>
   <bookViews>
     <workbookView xWindow="2660" yWindow="2660" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4981,6 +4981,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="기록표" displayName="기록표" ref="A42:E57" totalsRowShown="0" headerRowDxfId="84" headerRowBorderDxfId="83" tableBorderDxfId="82" totalsRowBorderDxfId="81">
   <tableColumns count="5">
@@ -37411,7 +37415,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="264" t="s">
-        <v>44</v>
+        <v>341</v>
       </c>
       <c r="C35" s="297"/>
       <c r="D35" s="243"/>
@@ -37437,7 +37441,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="264" t="s">
-        <v>61</v>
+        <v>353</v>
       </c>
       <c r="C36" s="297"/>
       <c r="D36" s="243"/>
@@ -37463,7 +37467,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="264" t="s">
-        <v>55</v>
+        <v>360</v>
       </c>
       <c r="C37" s="297"/>
       <c r="D37" s="243"/>
@@ -37489,7 +37493,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="264" t="s">
-        <v>71</v>
+        <v>369</v>
       </c>
       <c r="C38" s="297"/>
       <c r="D38" s="243"/>
@@ -37515,7 +37519,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="390" t="s">
-        <v>67</v>
+        <v>365</v>
       </c>
       <c r="C39" s="297"/>
       <c r="D39" s="243"/>

--- a/인천 2026 기록.xlsx
+++ b/인천 2026 기록.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://familyinter-my.sharepoint.com/personal/hwlee_familyinter_onmicrosoft_com/Documents/바탕 화면/프로젝트300/대시보드/인천 대시보드/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2470" documentId="11_ED78F197949CE43D6C65107960F9FD0C2CCB1E64" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C788D65D-16B6-4CA7-8F0E-741122600F61}"/>
+  <xr:revisionPtr revIDLastSave="3705" documentId="11_ED78F197949CE43D6C65107960F9FD0C2CCB1E64" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FE95339-5A91-4706-BDF5-23C015A14BF3}"/>
   <bookViews>
     <workbookView xWindow="2660" yWindow="2660" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/인천 2026 기록.xlsx
+++ b/인천 2026 기록.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://familyinter-my.sharepoint.com/personal/hwlee_familyinter_onmicrosoft_com/Documents/바탕 화면/프로젝트300/대시보드/인천 대시보드/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3705" documentId="11_ED78F197949CE43D6C65107960F9FD0C2CCB1E64" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FE95339-5A91-4706-BDF5-23C015A14BF3}"/>
+  <xr:revisionPtr revIDLastSave="1233" documentId="11_10A4B6222FF4A958C0F3D5135F98E2F7B88C7189" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F65B49FF-8165-4B6D-BA51-072F50FE0AE5}"/>
   <bookViews>
-    <workbookView xWindow="2660" yWindow="2660" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21540" yWindow="6195" windowWidth="21600" windowHeight="9285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 토탈" sheetId="1" r:id="rId1"/>
@@ -4981,10 +4981,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="기록표" displayName="기록표" ref="A42:E57" totalsRowShown="0" headerRowDxfId="84" headerRowBorderDxfId="83" tableBorderDxfId="82" totalsRowBorderDxfId="81">
   <tableColumns count="5">
@@ -9088,9 +9084,7 @@
       <c r="R24" s="320"/>
       <c r="S24" s="320"/>
       <c r="T24" s="320"/>
-      <c r="U24" s="400">
-        <v>5274</v>
-      </c>
+      <c r="U24" s="400"/>
       <c r="V24" s="312" t="s">
         <v>86</v>
       </c>
@@ -10086,9 +10080,7 @@
       <c r="R34" s="270"/>
       <c r="S34" s="270"/>
       <c r="T34" s="270"/>
-      <c r="U34" s="273">
-        <v>5558</v>
-      </c>
+      <c r="U34" s="273"/>
       <c r="V34" s="274" t="s">
         <v>58</v>
       </c>
@@ -10926,15 +10918,15 @@
       </c>
       <c r="N44" s="2">
         <f>COUNT(U3:U40)</f>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O44" s="96">
         <f>SUMIFS(U3:U41,A3:A41,M44)</f>
-        <v>182548</v>
+        <v>171716</v>
       </c>
       <c r="P44" s="96">
         <f>O44/N44</f>
-        <v>9607.78947368421</v>
+        <v>10100.941176470587</v>
       </c>
       <c r="Q44" s="136">
         <v>19</v>
@@ -10947,7 +10939,7 @@
       </c>
       <c r="T44" s="165">
         <f>(P44-S44)/S44</f>
-        <v>-5.563315433880664E-2</v>
+        <v>-7.1603896858740673E-3</v>
       </c>
     </row>
     <row r="45" spans="1:36">
